--- a/research/traditional_assets/database/data/belgium/belgium_entertainment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtbr_kin" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.207</v>
+        <v>0.0633</v>
+      </c>
+      <c r="E2">
+        <v>-0.102</v>
       </c>
       <c r="G2">
-        <v>-0.2785234899328859</v>
+        <v>0.05622909698996655</v>
       </c>
       <c r="H2">
-        <v>-0.2785234899328859</v>
+        <v>0.05622909698996655</v>
       </c>
       <c r="I2">
-        <v>-1.049496644295302</v>
+        <v>0.1135033444816053</v>
       </c>
       <c r="J2">
-        <v>-1.049496644295302</v>
+        <v>0.08648277217590974</v>
       </c>
       <c r="K2">
-        <v>-100.7</v>
+        <v>30.6</v>
       </c>
       <c r="L2">
-        <v>-0.8447986577181208</v>
+        <v>0.06396321070234115</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +629,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>32.4</v>
+        <v>40.5</v>
       </c>
       <c r="V2">
-        <v>0.01933751119068934</v>
+        <v>0.03623512570457189</v>
       </c>
       <c r="W2">
-        <v>-0.5035000000000001</v>
+        <v>0.2884071630537229</v>
       </c>
       <c r="X2">
-        <v>0.09228582774954733</v>
+        <v>0.1636272835156201</v>
       </c>
       <c r="Y2">
-        <v>-0.5957858277495474</v>
+        <v>0.1247798795381029</v>
       </c>
       <c r="Z2">
-        <v>0.1212861212861213</v>
+        <v>0.4650981917168969</v>
       </c>
       <c r="AA2">
-        <v>-0.1272893772893773</v>
+        <v>0.04022298095367999</v>
       </c>
       <c r="AB2">
-        <v>0.06479834342920175</v>
+        <v>0.1104709540421144</v>
       </c>
       <c r="AC2">
-        <v>-0.192087720718579</v>
+        <v>-0.07024797308843445</v>
       </c>
       <c r="AD2">
-        <v>1152.3</v>
+        <v>932.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1152.3</v>
+        <v>932.4</v>
       </c>
       <c r="AG2">
-        <v>1119.9</v>
+        <v>891.9</v>
       </c>
       <c r="AH2">
-        <v>0.4074899214937407</v>
+        <v>0.4548070825813375</v>
       </c>
       <c r="AI2">
-        <v>0.9157593578637845</v>
+        <v>0.8561197318887155</v>
       </c>
       <c r="AJ2">
-        <v>0.4006224511697789</v>
+        <v>0.4438196656050956</v>
       </c>
       <c r="AK2">
-        <v>0.9135329145933599</v>
+        <v>0.8505626549685296</v>
       </c>
       <c r="AL2">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="AM2">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="AN2">
-        <v>-14.71647509578544</v>
+        <v>8.689655172413794</v>
       </c>
       <c r="AO2">
-        <v>-4.328719723183391</v>
+        <v>1.840677966101695</v>
       </c>
       <c r="AP2">
-        <v>-14.30268199233716</v>
+        <v>8.312208760484623</v>
       </c>
       <c r="AQ2">
-        <v>-4.328719723183391</v>
+        <v>1.840677966101695</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +721,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.207</v>
+        <v>0.0633</v>
+      </c>
+      <c r="E3">
+        <v>-0.102</v>
       </c>
       <c r="G3">
-        <v>-0.2785234899328859</v>
+        <v>0.05622909698996655</v>
       </c>
       <c r="H3">
-        <v>-0.2785234899328859</v>
+        <v>0.05622909698996655</v>
       </c>
       <c r="I3">
-        <v>-1.049496644295302</v>
+        <v>0.1135033444816053</v>
       </c>
       <c r="J3">
-        <v>-1.049496644295302</v>
+        <v>0.08648277217590974</v>
       </c>
       <c r="K3">
-        <v>-100.7</v>
+        <v>30.6</v>
       </c>
       <c r="L3">
-        <v>-0.8447986577181208</v>
+        <v>0.06396321070234115</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -743,7 +751,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -752,79 +760,8791 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>32.4</v>
+        <v>40.5</v>
       </c>
       <c r="V3">
-        <v>0.01933751119068934</v>
+        <v>0.03623512570457189</v>
       </c>
       <c r="W3">
-        <v>-0.5035000000000001</v>
+        <v>0.2884071630537229</v>
       </c>
       <c r="X3">
-        <v>0.09228582774954733</v>
+        <v>0.1636272835156201</v>
       </c>
       <c r="Y3">
-        <v>-0.5957858277495474</v>
+        <v>0.1247798795381029</v>
       </c>
       <c r="Z3">
-        <v>0.1212861212861213</v>
+        <v>0.4650981917168969</v>
       </c>
       <c r="AA3">
-        <v>-0.1272893772893773</v>
+        <v>0.04022298095367999</v>
       </c>
       <c r="AB3">
-        <v>0.06479834342920175</v>
+        <v>0.1104709540421144</v>
       </c>
       <c r="AC3">
-        <v>-0.192087720718579</v>
+        <v>-0.07024797308843445</v>
       </c>
       <c r="AD3">
-        <v>1152.3</v>
+        <v>932.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1152.3</v>
+        <v>932.4</v>
       </c>
       <c r="AG3">
-        <v>1119.9</v>
+        <v>891.9</v>
       </c>
       <c r="AH3">
-        <v>0.4074899214937407</v>
+        <v>0.4548070825813375</v>
       </c>
       <c r="AI3">
-        <v>0.9157593578637845</v>
+        <v>0.8561197318887155</v>
       </c>
       <c r="AJ3">
-        <v>0.4006224511697789</v>
+        <v>0.4438196656050956</v>
       </c>
       <c r="AK3">
-        <v>0.9135329145933599</v>
+        <v>0.8505626549685296</v>
       </c>
       <c r="AL3">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="AM3">
-        <v>28.9</v>
+        <v>29.5</v>
       </c>
       <c r="AN3">
-        <v>-14.71647509578544</v>
+        <v>8.689655172413794</v>
       </c>
       <c r="AO3">
-        <v>-4.328719723183391</v>
+        <v>1.840677966101695</v>
       </c>
       <c r="AP3">
-        <v>-14.30268199233716</v>
+        <v>8.312208760484623</v>
       </c>
       <c r="AQ3">
-        <v>-4.328719723183391</v>
+        <v>1.840677966101695</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kinepolis Group NV (ENXTBR:KIN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTBR:KIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.454807082581338</v>
+      </c>
+      <c r="F2">
+        <v>0.1</v>
+      </c>
+      <c r="G2">
+        <v>1117.7</v>
+      </c>
+      <c r="H2">
+        <v>1753.05208535215</v>
+      </c>
+      <c r="I2">
+        <v>2009.6</v>
+      </c>
+      <c r="J2">
+        <v>1917.56208535215</v>
+      </c>
+      <c r="K2">
+        <v>932.4</v>
+      </c>
+      <c r="L2">
+        <v>205.01</v>
+      </c>
+      <c r="M2">
+        <v>0.110470954042114</v>
+      </c>
+      <c r="N2">
+        <v>0.113910970509507</v>
+      </c>
+      <c r="O2">
+        <v>0.0467506307339449</v>
+      </c>
+      <c r="P2">
+        <v>0.04125</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.16362728351562</v>
+      </c>
+      <c r="T2">
+        <v>0.121984411677229</v>
+      </c>
+      <c r="U2">
+        <v>1.7963817993739</v>
+      </c>
+      <c r="V2">
+        <v>1.19710177871412</v>
+      </c>
+      <c r="W2">
+        <v>4.815729609642102</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1117.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>107.3</v>
+      </c>
+      <c r="AH2">
+        <v>53</v>
+      </c>
+      <c r="AI2">
+        <v>68.39999999999999</v>
+      </c>
+      <c r="AJ2">
+        <v>932.4</v>
+      </c>
+      <c r="AK2">
+        <v>932.4</v>
+      </c>
+      <c r="AL2">
+        <v>29.5</v>
+      </c>
+      <c r="AM2">
+        <v>932.4</v>
+      </c>
+      <c r="AN2">
+        <v>40.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1155856107789811</v>
+      </c>
+      <c r="C2">
+        <v>1916.241402352161</v>
+      </c>
+      <c r="D2">
+        <v>1875.741402352161</v>
+      </c>
+      <c r="E2">
+        <v>-932.4</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>40.5</v>
+      </c>
+      <c r="H2">
+        <v>1117.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>107.3</v>
+      </c>
+      <c r="K2">
+        <v>53</v>
+      </c>
+      <c r="L2">
+        <v>54.3</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>54.3</v>
+      </c>
+      <c r="O2">
+        <v>13.575</v>
+      </c>
+      <c r="P2">
+        <v>40.72499999999999</v>
+      </c>
+      <c r="Q2">
+        <v>93.72499999999999</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1155856107789811</v>
+      </c>
+      <c r="T2">
+        <v>1.105017026505343</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W2">
+        <v>0.034275</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1153483967520336</v>
+      </c>
+      <c r="C3">
+        <v>1901.553093282912</v>
+      </c>
+      <c r="D3">
+        <v>1881.554093282911</v>
+      </c>
+      <c r="E3">
+        <v>-911.899</v>
+      </c>
+      <c r="F3">
+        <v>20.501</v>
+      </c>
+      <c r="G3">
+        <v>40.5</v>
+      </c>
+      <c r="H3">
+        <v>1117.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>107.3</v>
+      </c>
+      <c r="K3">
+        <v>53</v>
+      </c>
+      <c r="L3">
+        <v>54.3</v>
+      </c>
+      <c r="M3">
+        <v>0.9368957000000001</v>
+      </c>
+      <c r="N3">
+        <v>53.3631043</v>
+      </c>
+      <c r="O3">
+        <v>13.340776075</v>
+      </c>
+      <c r="P3">
+        <v>40.022328225</v>
+      </c>
+      <c r="Q3">
+        <v>93.022328225</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1161673199515491</v>
+      </c>
+      <c r="T3">
+        <v>1.113388367615232</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W3">
+        <v>0.034275</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>57.95735854055044</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1151111827250862</v>
+      </c>
+      <c r="C4">
+        <v>1886.90092182217</v>
+      </c>
+      <c r="D4">
+        <v>1887.40292182217</v>
+      </c>
+      <c r="E4">
+        <v>-891.398</v>
+      </c>
+      <c r="F4">
+        <v>41.002</v>
+      </c>
+      <c r="G4">
+        <v>40.5</v>
+      </c>
+      <c r="H4">
+        <v>1117.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>107.3</v>
+      </c>
+      <c r="K4">
+        <v>53</v>
+      </c>
+      <c r="L4">
+        <v>54.3</v>
+      </c>
+      <c r="M4">
+        <v>1.8737914</v>
+      </c>
+      <c r="N4">
+        <v>52.4262086</v>
+      </c>
+      <c r="O4">
+        <v>13.10655215</v>
+      </c>
+      <c r="P4">
+        <v>39.31965644999999</v>
+      </c>
+      <c r="Q4">
+        <v>92.31965645</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1167609007398838</v>
+      </c>
+      <c r="T4">
+        <v>1.121930552421241</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W4">
+        <v>0.034275</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>28.97867927027522</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1148739686981387</v>
+      </c>
+      <c r="C5">
+        <v>1872.285226023065</v>
+      </c>
+      <c r="D5">
+        <v>1893.288226023065</v>
+      </c>
+      <c r="E5">
+        <v>-870.8969999999999</v>
+      </c>
+      <c r="F5">
+        <v>61.50299999999999</v>
+      </c>
+      <c r="G5">
+        <v>40.5</v>
+      </c>
+      <c r="H5">
+        <v>1117.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>107.3</v>
+      </c>
+      <c r="K5">
+        <v>53</v>
+      </c>
+      <c r="L5">
+        <v>54.3</v>
+      </c>
+      <c r="M5">
+        <v>2.8106871</v>
+      </c>
+      <c r="N5">
+        <v>51.48931289999999</v>
+      </c>
+      <c r="O5">
+        <v>12.872328225</v>
+      </c>
+      <c r="P5">
+        <v>38.61698467499999</v>
+      </c>
+      <c r="Q5">
+        <v>91.616984675</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1173667203073595</v>
+      </c>
+      <c r="T5">
+        <v>1.130648864749024</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W5">
+        <v>0.034275</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>19.31911951351682</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1146367546711912</v>
+      </c>
+      <c r="C6">
+        <v>1857.706348168381</v>
+      </c>
+      <c r="D6">
+        <v>1899.210348168381</v>
+      </c>
+      <c r="E6">
+        <v>-850.396</v>
+      </c>
+      <c r="F6">
+        <v>82.004</v>
+      </c>
+      <c r="G6">
+        <v>40.5</v>
+      </c>
+      <c r="H6">
+        <v>1117.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>107.3</v>
+      </c>
+      <c r="K6">
+        <v>53</v>
+      </c>
+      <c r="L6">
+        <v>54.3</v>
+      </c>
+      <c r="M6">
+        <v>3.7475828</v>
+      </c>
+      <c r="N6">
+        <v>50.55241719999999</v>
+      </c>
+      <c r="O6">
+        <v>12.6381043</v>
+      </c>
+      <c r="P6">
+        <v>37.91431289999999</v>
+      </c>
+      <c r="Q6">
+        <v>90.9143129</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1179851611158242</v>
+      </c>
+      <c r="T6">
+        <v>1.139548808583635</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W6">
+        <v>0.034275</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>14.48933963513761</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1144595406442438</v>
+      </c>
+      <c r="C7">
+        <v>1841.653785350965</v>
+      </c>
+      <c r="D7">
+        <v>1903.658785350965</v>
+      </c>
+      <c r="E7">
+        <v>-829.895</v>
+      </c>
+      <c r="F7">
+        <v>102.505</v>
+      </c>
+      <c r="G7">
+        <v>40.5</v>
+      </c>
+      <c r="H7">
+        <v>1117.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>107.3</v>
+      </c>
+      <c r="K7">
+        <v>53</v>
+      </c>
+      <c r="L7">
+        <v>54.3</v>
+      </c>
+      <c r="M7">
+        <v>4.8484865</v>
+      </c>
+      <c r="N7">
+        <v>49.4515135</v>
+      </c>
+      <c r="O7">
+        <v>12.362878375</v>
+      </c>
+      <c r="P7">
+        <v>37.088635125</v>
+      </c>
+      <c r="Q7">
+        <v>90.088635125</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.118616621730783</v>
+      </c>
+      <c r="T7">
+        <v>1.14863611965687</v>
+      </c>
+      <c r="U7">
+        <v>0.0473</v>
+      </c>
+      <c r="V7">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W7">
+        <v>0.03547499999999999</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>11.19937118521419</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1144053266172963</v>
+      </c>
+      <c r="C8">
+        <v>1822.517834790011</v>
+      </c>
+      <c r="D8">
+        <v>1905.023834790011</v>
+      </c>
+      <c r="E8">
+        <v>-809.394</v>
+      </c>
+      <c r="F8">
+        <v>123.006</v>
+      </c>
+      <c r="G8">
+        <v>40.5</v>
+      </c>
+      <c r="H8">
+        <v>1117.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>107.3</v>
+      </c>
+      <c r="K8">
+        <v>53</v>
+      </c>
+      <c r="L8">
+        <v>54.3</v>
+      </c>
+      <c r="M8">
+        <v>6.285606599999999</v>
+      </c>
+      <c r="N8">
+        <v>48.0143934</v>
+      </c>
+      <c r="O8">
+        <v>12.00359835</v>
+      </c>
+      <c r="P8">
+        <v>36.01079504999999</v>
+      </c>
+      <c r="Q8">
+        <v>89.01079504999998</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1192615176779748</v>
+      </c>
+      <c r="T8">
+        <v>1.157916777774216</v>
+      </c>
+      <c r="U8">
+        <v>0.0511</v>
+      </c>
+      <c r="V8">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W8">
+        <v>0.03832499999999999</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>8.63878436171936</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1143083625903489</v>
+      </c>
+      <c r="C9">
+        <v>1804.463170217178</v>
+      </c>
+      <c r="D9">
+        <v>1907.470170217178</v>
+      </c>
+      <c r="E9">
+        <v>-788.893</v>
+      </c>
+      <c r="F9">
+        <v>143.507</v>
+      </c>
+      <c r="G9">
+        <v>40.5</v>
+      </c>
+      <c r="H9">
+        <v>1117.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>107.3</v>
+      </c>
+      <c r="K9">
+        <v>53</v>
+      </c>
+      <c r="L9">
+        <v>54.3</v>
+      </c>
+      <c r="M9">
+        <v>7.605871000000001</v>
+      </c>
+      <c r="N9">
+        <v>46.694129</v>
+      </c>
+      <c r="O9">
+        <v>11.67353225</v>
+      </c>
+      <c r="P9">
+        <v>35.02059675</v>
+      </c>
+      <c r="Q9">
+        <v>88.02059675</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1199202823552139</v>
+      </c>
+      <c r="T9">
+        <v>1.167397019937096</v>
+      </c>
+      <c r="U9">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V9">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W9">
+        <v>0.03975</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>7.139221793269961</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1141258985634015</v>
+      </c>
+      <c r="C10">
+        <v>1788.582688460939</v>
+      </c>
+      <c r="D10">
+        <v>1912.090688460939</v>
+      </c>
+      <c r="E10">
+        <v>-768.3919999999999</v>
+      </c>
+      <c r="F10">
+        <v>164.008</v>
+      </c>
+      <c r="G10">
+        <v>40.5</v>
+      </c>
+      <c r="H10">
+        <v>1117.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>107.3</v>
+      </c>
+      <c r="K10">
+        <v>53</v>
+      </c>
+      <c r="L10">
+        <v>54.3</v>
+      </c>
+      <c r="M10">
+        <v>8.692424000000001</v>
+      </c>
+      <c r="N10">
+        <v>45.60757599999999</v>
+      </c>
+      <c r="O10">
+        <v>11.401894</v>
+      </c>
+      <c r="P10">
+        <v>34.20568199999999</v>
+      </c>
+      <c r="Q10">
+        <v>87.205682</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1205933680036972</v>
+      </c>
+      <c r="T10">
+        <v>1.177083354320909</v>
+      </c>
+      <c r="U10">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V10">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W10">
+        <v>0.03975</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>6.246819069111216</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.114078434536454</v>
+      </c>
+      <c r="C11">
+        <v>1769.287286379148</v>
+      </c>
+      <c r="D11">
+        <v>1913.296286379148</v>
+      </c>
+      <c r="E11">
+        <v>-747.891</v>
+      </c>
+      <c r="F11">
+        <v>184.509</v>
+      </c>
+      <c r="G11">
+        <v>40.5</v>
+      </c>
+      <c r="H11">
+        <v>1117.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>107.3</v>
+      </c>
+      <c r="K11">
+        <v>53</v>
+      </c>
+      <c r="L11">
+        <v>54.3</v>
+      </c>
+      <c r="M11">
+        <v>10.147995</v>
+      </c>
+      <c r="N11">
+        <v>44.152005</v>
+      </c>
+      <c r="O11">
+        <v>11.03800125</v>
+      </c>
+      <c r="P11">
+        <v>33.11400374999999</v>
+      </c>
+      <c r="Q11">
+        <v>86.11400374999999</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.121281246743356</v>
+      </c>
+      <c r="T11">
+        <v>1.186982575174695</v>
+      </c>
+      <c r="U11">
+        <v>0.055</v>
+      </c>
+      <c r="V11">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W11">
+        <v>0.04125</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>5.350810677380113</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1139109705095065</v>
+      </c>
+      <c r="C12">
+        <v>1753.05208535215</v>
+      </c>
+      <c r="D12">
+        <v>1917.56208535215</v>
+      </c>
+      <c r="E12">
+        <v>-727.39</v>
+      </c>
+      <c r="F12">
+        <v>205.01</v>
+      </c>
+      <c r="G12">
+        <v>40.5</v>
+      </c>
+      <c r="H12">
+        <v>1117.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>107.3</v>
+      </c>
+      <c r="K12">
+        <v>53</v>
+      </c>
+      <c r="L12">
+        <v>54.3</v>
+      </c>
+      <c r="M12">
+        <v>11.27555</v>
+      </c>
+      <c r="N12">
+        <v>43.02445</v>
+      </c>
+      <c r="O12">
+        <v>10.75611250000001</v>
+      </c>
+      <c r="P12">
+        <v>32.26833749999999</v>
+      </c>
+      <c r="Q12">
+        <v>85.2683375</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1219844116772295</v>
+      </c>
+      <c r="T12">
+        <v>1.197101778714121</v>
+      </c>
+      <c r="U12">
+        <v>0.055</v>
+      </c>
+      <c r="V12">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W12">
+        <v>0.04125</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>4.815729609642102</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1140570064825591</v>
+      </c>
+      <c r="C13">
+        <v>1728.830062445293</v>
+      </c>
+      <c r="D13">
+        <v>1913.841062445293</v>
+      </c>
+      <c r="E13">
+        <v>-706.889</v>
+      </c>
+      <c r="F13">
+        <v>225.511</v>
+      </c>
+      <c r="G13">
+        <v>40.5</v>
+      </c>
+      <c r="H13">
+        <v>1117.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>107.3</v>
+      </c>
+      <c r="K13">
+        <v>53</v>
+      </c>
+      <c r="L13">
+        <v>54.3</v>
+      </c>
+      <c r="M13">
+        <v>13.2600468</v>
+      </c>
+      <c r="N13">
+        <v>41.0399532</v>
+      </c>
+      <c r="O13">
+        <v>10.25998830000001</v>
+      </c>
+      <c r="P13">
+        <v>30.7799649</v>
+      </c>
+      <c r="Q13">
+        <v>83.7799649</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1227033780702911</v>
+      </c>
+      <c r="T13">
+        <v>1.207448380085894</v>
+      </c>
+      <c r="U13">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V13">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W13">
+        <v>0.0441</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>4.095008171464372</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1142960424556116</v>
+      </c>
+      <c r="C14">
+        <v>1702.269448646351</v>
+      </c>
+      <c r="D14">
+        <v>1907.781448646351</v>
+      </c>
+      <c r="E14">
+        <v>-686.388</v>
+      </c>
+      <c r="F14">
+        <v>246.012</v>
+      </c>
+      <c r="G14">
+        <v>40.5</v>
+      </c>
+      <c r="H14">
+        <v>1117.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>107.3</v>
+      </c>
+      <c r="K14">
+        <v>53</v>
+      </c>
+      <c r="L14">
+        <v>54.3</v>
+      </c>
+      <c r="M14">
+        <v>15.498756</v>
+      </c>
+      <c r="N14">
+        <v>38.801244</v>
+      </c>
+      <c r="O14">
+        <v>9.700311000000003</v>
+      </c>
+      <c r="P14">
+        <v>29.10093299999999</v>
+      </c>
+      <c r="Q14">
+        <v>82.100933</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1234386846086496</v>
+      </c>
+      <c r="T14">
+        <v>1.218030131488844</v>
+      </c>
+      <c r="U14">
+        <v>0.063</v>
+      </c>
+      <c r="V14">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W14">
+        <v>0.04724999999999999</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>3.503506991141741</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1169575784286642</v>
+      </c>
+      <c r="C15">
+        <v>1616.80188933913</v>
+      </c>
+      <c r="D15">
+        <v>1842.81488933913</v>
+      </c>
+      <c r="E15">
+        <v>-665.8869999999999</v>
+      </c>
+      <c r="F15">
+        <v>266.513</v>
+      </c>
+      <c r="G15">
+        <v>40.5</v>
+      </c>
+      <c r="H15">
+        <v>1117.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>107.3</v>
+      </c>
+      <c r="K15">
+        <v>53</v>
+      </c>
+      <c r="L15">
+        <v>54.3</v>
+      </c>
+      <c r="M15">
+        <v>24.3592882</v>
+      </c>
+      <c r="N15">
+        <v>29.9407118</v>
+      </c>
+      <c r="O15">
+        <v>7.485177950000002</v>
+      </c>
+      <c r="P15">
+        <v>22.45553384999999</v>
+      </c>
+      <c r="Q15">
+        <v>75.45553384999999</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.124190894745591</v>
+      </c>
+      <c r="T15">
+        <v>1.228855141544735</v>
+      </c>
+      <c r="U15">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V15">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W15">
+        <v>0.06855</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>2.229129174636556</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1170631144017167</v>
+      </c>
+      <c r="C16">
+        <v>1593.815896708964</v>
+      </c>
+      <c r="D16">
+        <v>1840.329896708964</v>
+      </c>
+      <c r="E16">
+        <v>-645.386</v>
+      </c>
+      <c r="F16">
+        <v>287.014</v>
+      </c>
+      <c r="G16">
+        <v>40.5</v>
+      </c>
+      <c r="H16">
+        <v>1117.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>107.3</v>
+      </c>
+      <c r="K16">
+        <v>53</v>
+      </c>
+      <c r="L16">
+        <v>54.3</v>
+      </c>
+      <c r="M16">
+        <v>26.2330796</v>
+      </c>
+      <c r="N16">
+        <v>28.06692039999999</v>
+      </c>
+      <c r="O16">
+        <v>7.016730100000002</v>
+      </c>
+      <c r="P16">
+        <v>21.05019029999999</v>
+      </c>
+      <c r="Q16">
+        <v>74.0501903</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1249605981415311</v>
+      </c>
+      <c r="T16">
+        <v>1.23993189602053</v>
+      </c>
+      <c r="U16">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W16">
+        <v>0.06855</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>2.069905662162516</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1195424003747693</v>
+      </c>
+      <c r="C17">
+        <v>1516.805502914356</v>
+      </c>
+      <c r="D17">
+        <v>1783.820502914356</v>
+      </c>
+      <c r="E17">
+        <v>-624.885</v>
+      </c>
+      <c r="F17">
+        <v>307.515</v>
+      </c>
+      <c r="G17">
+        <v>40.5</v>
+      </c>
+      <c r="H17">
+        <v>1117.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>107.3</v>
+      </c>
+      <c r="K17">
+        <v>53</v>
+      </c>
+      <c r="L17">
+        <v>54.3</v>
+      </c>
+      <c r="M17">
+        <v>34.5954375</v>
+      </c>
+      <c r="N17">
+        <v>19.70456249999999</v>
+      </c>
+      <c r="O17">
+        <v>4.926140625</v>
+      </c>
+      <c r="P17">
+        <v>14.77842187499999</v>
+      </c>
+      <c r="Q17">
+        <v>67.77842187499999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1257484122056109</v>
+      </c>
+      <c r="T17">
+        <v>1.251269280013403</v>
+      </c>
+      <c r="U17">
+        <v>0.1125</v>
+      </c>
+      <c r="V17">
+        <v>0.2500000000000001</v>
+      </c>
+      <c r="W17">
+        <v>0.08437499999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>1.5695711320315</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1316257884319168</v>
+      </c>
+      <c r="C18">
+        <v>1264.099684349098</v>
+      </c>
+      <c r="D18">
+        <v>1551.615684349098</v>
+      </c>
+      <c r="E18">
+        <v>-604.384</v>
+      </c>
+      <c r="F18">
+        <v>328.016</v>
+      </c>
+      <c r="G18">
+        <v>40.5</v>
+      </c>
+      <c r="H18">
+        <v>1117.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>107.3</v>
+      </c>
+      <c r="K18">
+        <v>53</v>
+      </c>
+      <c r="L18">
+        <v>54.3</v>
+      </c>
+      <c r="M18">
+        <v>64.4879456</v>
+      </c>
+      <c r="N18">
+        <v>-10.18794560000001</v>
+      </c>
+      <c r="O18">
+        <v>-2.546986400000003</v>
+      </c>
+      <c r="P18">
+        <v>-7.640959200000003</v>
+      </c>
+      <c r="Q18">
+        <v>45.3590408</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1271326388633032</v>
+      </c>
+      <c r="T18">
+        <v>1.271189601148769</v>
+      </c>
+      <c r="U18">
+        <v>0.1966</v>
+      </c>
+      <c r="V18">
+        <v>0.2105044574408028</v>
+      </c>
+      <c r="W18">
+        <v>0.1552148236671382</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.8420178297632107</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1363358452097534</v>
+      </c>
+      <c r="C19">
+        <v>1168.67035461607</v>
+      </c>
+      <c r="D19">
+        <v>1476.68735461607</v>
+      </c>
+      <c r="E19">
+        <v>-583.883</v>
+      </c>
+      <c r="F19">
+        <v>348.517</v>
+      </c>
+      <c r="G19">
+        <v>40.5</v>
+      </c>
+      <c r="H19">
+        <v>1117.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>107.3</v>
+      </c>
+      <c r="K19">
+        <v>53</v>
+      </c>
+      <c r="L19">
+        <v>54.3</v>
+      </c>
+      <c r="M19">
+        <v>74.51293459999999</v>
+      </c>
+      <c r="N19">
+        <v>-20.2129346</v>
+      </c>
+      <c r="O19">
+        <v>-5.053233650000002</v>
+      </c>
+      <c r="P19">
+        <v>-15.15970094999999</v>
+      </c>
+      <c r="Q19">
+        <v>37.84029905000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1284475583409774</v>
+      </c>
+      <c r="T19">
+        <v>1.290112526897135</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.1821831346849142</v>
+      </c>
+      <c r="W19">
+        <v>0.1748492458043653</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.7287325387396566</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1380858452097534</v>
+      </c>
+      <c r="C20">
+        <v>1122.141446356653</v>
+      </c>
+      <c r="D20">
+        <v>1450.659446356653</v>
+      </c>
+      <c r="E20">
+        <v>-563.3820000000001</v>
+      </c>
+      <c r="F20">
+        <v>369.018</v>
+      </c>
+      <c r="G20">
+        <v>40.5</v>
+      </c>
+      <c r="H20">
+        <v>1117.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>107.3</v>
+      </c>
+      <c r="K20">
+        <v>53</v>
+      </c>
+      <c r="L20">
+        <v>54.3</v>
+      </c>
+      <c r="M20">
+        <v>78.89604839999998</v>
+      </c>
+      <c r="N20">
+        <v>-24.59604839999999</v>
+      </c>
+      <c r="O20">
+        <v>-6.149012099999999</v>
+      </c>
+      <c r="P20">
+        <v>-18.44703629999999</v>
+      </c>
+      <c r="Q20">
+        <v>34.55296370000001</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1295408212475747</v>
+      </c>
+      <c r="T20">
+        <v>1.305845606493441</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.1720618494246413</v>
+      </c>
+      <c r="W20">
+        <v>0.1770131765930117</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.6882473976985647</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1398358452097534</v>
+      </c>
+      <c r="C21">
+        <v>1076.51417532033</v>
+      </c>
+      <c r="D21">
+        <v>1425.53317532033</v>
+      </c>
+      <c r="E21">
+        <v>-542.881</v>
+      </c>
+      <c r="F21">
+        <v>389.519</v>
+      </c>
+      <c r="G21">
+        <v>40.5</v>
+      </c>
+      <c r="H21">
+        <v>1117.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>107.3</v>
+      </c>
+      <c r="K21">
+        <v>53</v>
+      </c>
+      <c r="L21">
+        <v>54.3</v>
+      </c>
+      <c r="M21">
+        <v>83.2791622</v>
+      </c>
+      <c r="N21">
+        <v>-28.9791622</v>
+      </c>
+      <c r="O21">
+        <v>-7.244790550000005</v>
+      </c>
+      <c r="P21">
+        <v>-21.73437165</v>
+      </c>
+      <c r="Q21">
+        <v>31.26562835</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1306610783000139</v>
+      </c>
+      <c r="T21">
+        <v>1.321967157190892</v>
+      </c>
+      <c r="U21">
+        <v>0.2138</v>
+      </c>
+      <c r="V21">
+        <v>0.163005962612818</v>
+      </c>
+      <c r="W21">
+        <v>0.1789493251933795</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.6520238504512716</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1415858452097534</v>
+      </c>
+      <c r="C22">
+        <v>1031.742488517885</v>
+      </c>
+      <c r="D22">
+        <v>1401.262488517885</v>
+      </c>
+      <c r="E22">
+        <v>-522.38</v>
+      </c>
+      <c r="F22">
+        <v>410.02</v>
+      </c>
+      <c r="G22">
+        <v>40.5</v>
+      </c>
+      <c r="H22">
+        <v>1117.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>107.3</v>
+      </c>
+      <c r="K22">
+        <v>53</v>
+      </c>
+      <c r="L22">
+        <v>54.3</v>
+      </c>
+      <c r="M22">
+        <v>87.66227599999999</v>
+      </c>
+      <c r="N22">
+        <v>-33.36227599999999</v>
+      </c>
+      <c r="O22">
+        <v>-8.340569000000002</v>
+      </c>
+      <c r="P22">
+        <v>-25.02170699999999</v>
+      </c>
+      <c r="Q22">
+        <v>27.97829300000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1318093417787641</v>
+      </c>
+      <c r="T22">
+        <v>1.338491746655778</v>
+      </c>
+      <c r="U22">
+        <v>0.2138</v>
+      </c>
+      <c r="V22">
+        <v>0.1548556644821771</v>
+      </c>
+      <c r="W22">
+        <v>0.1806918589337105</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.6194226579287081</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1433358452097534</v>
+      </c>
+      <c r="C23">
+        <v>987.7834167915232</v>
+      </c>
+      <c r="D23">
+        <v>1377.804416791523</v>
+      </c>
+      <c r="E23">
+        <v>-501.879</v>
+      </c>
+      <c r="F23">
+        <v>430.521</v>
+      </c>
+      <c r="G23">
+        <v>40.5</v>
+      </c>
+      <c r="H23">
+        <v>1117.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>107.3</v>
+      </c>
+      <c r="K23">
+        <v>53</v>
+      </c>
+      <c r="L23">
+        <v>54.3</v>
+      </c>
+      <c r="M23">
+        <v>92.04538979999998</v>
+      </c>
+      <c r="N23">
+        <v>-37.74538979999998</v>
+      </c>
+      <c r="O23">
+        <v>-9.43634745</v>
+      </c>
+      <c r="P23">
+        <v>-28.30904234999998</v>
+      </c>
+      <c r="Q23">
+        <v>24.69095765000002</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1329866752190016</v>
+      </c>
+      <c r="T23">
+        <v>1.355434680157749</v>
+      </c>
+      <c r="U23">
+        <v>0.2138</v>
+      </c>
+      <c r="V23">
+        <v>0.1474815852211211</v>
+      </c>
+      <c r="W23">
+        <v>0.1822684370797243</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.589926340884484</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1450858452097534</v>
+      </c>
+      <c r="C24">
+        <v>944.5968209379378</v>
+      </c>
+      <c r="D24">
+        <v>1355.118820937938</v>
+      </c>
+      <c r="E24">
+        <v>-481.378</v>
+      </c>
+      <c r="F24">
+        <v>451.022</v>
+      </c>
+      <c r="G24">
+        <v>40.5</v>
+      </c>
+      <c r="H24">
+        <v>1117.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>107.3</v>
+      </c>
+      <c r="K24">
+        <v>53</v>
+      </c>
+      <c r="L24">
+        <v>54.3</v>
+      </c>
+      <c r="M24">
+        <v>96.4285036</v>
+      </c>
+      <c r="N24">
+        <v>-42.1285036</v>
+      </c>
+      <c r="O24">
+        <v>-10.53212590000001</v>
+      </c>
+      <c r="P24">
+        <v>-31.5963777</v>
+      </c>
+      <c r="Q24">
+        <v>21.4036223</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1341941966961683</v>
+      </c>
+      <c r="T24">
+        <v>1.37281204785208</v>
+      </c>
+      <c r="U24">
+        <v>0.2138</v>
+      </c>
+      <c r="V24">
+        <v>0.1407778768019792</v>
+      </c>
+      <c r="W24">
+        <v>0.1837016899397368</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.5631115072079165</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1468358452097534</v>
+      </c>
+      <c r="C25">
+        <v>902.1451625056628</v>
+      </c>
+      <c r="D25">
+        <v>1333.168162505663</v>
+      </c>
+      <c r="E25">
+        <v>-460.877</v>
+      </c>
+      <c r="F25">
+        <v>471.523</v>
+      </c>
+      <c r="G25">
+        <v>40.5</v>
+      </c>
+      <c r="H25">
+        <v>1117.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>107.3</v>
+      </c>
+      <c r="K25">
+        <v>53</v>
+      </c>
+      <c r="L25">
+        <v>54.3</v>
+      </c>
+      <c r="M25">
+        <v>100.8116174</v>
+      </c>
+      <c r="N25">
+        <v>-46.51161740000001</v>
+      </c>
+      <c r="O25">
+        <v>-11.62790435000001</v>
+      </c>
+      <c r="P25">
+        <v>-34.88371305</v>
+      </c>
+      <c r="Q25">
+        <v>18.11628695</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1354330823675471</v>
+      </c>
+      <c r="T25">
+        <v>1.390640775746263</v>
+      </c>
+      <c r="U25">
+        <v>0.2138</v>
+      </c>
+      <c r="V25">
+        <v>0.1346570995497192</v>
+      </c>
+      <c r="W25">
+        <v>0.18501031211627</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.5386283981988766</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1485858452097534</v>
+      </c>
+      <c r="C26">
+        <v>860.3932965135355</v>
+      </c>
+      <c r="D26">
+        <v>1311.917296513535</v>
+      </c>
+      <c r="E26">
+        <v>-440.376</v>
+      </c>
+      <c r="F26">
+        <v>492.0239999999999</v>
+      </c>
+      <c r="G26">
+        <v>40.5</v>
+      </c>
+      <c r="H26">
+        <v>1117.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>107.3</v>
+      </c>
+      <c r="K26">
+        <v>53</v>
+      </c>
+      <c r="L26">
+        <v>54.3</v>
+      </c>
+      <c r="M26">
+        <v>105.1947312</v>
+      </c>
+      <c r="N26">
+        <v>-50.89473119999998</v>
+      </c>
+      <c r="O26">
+        <v>-12.7236828</v>
+      </c>
+      <c r="P26">
+        <v>-38.17104839999998</v>
+      </c>
+      <c r="Q26">
+        <v>14.82895160000002</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1367045702934359</v>
+      </c>
+      <c r="T26">
+        <v>1.408938680690292</v>
+      </c>
+      <c r="U26">
+        <v>0.2138</v>
+      </c>
+      <c r="V26">
+        <v>0.1290463870684809</v>
+      </c>
+      <c r="W26">
+        <v>0.1862098824447588</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.5161855482739235</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1568348126883934</v>
+      </c>
+      <c r="C27">
+        <v>748.2077937204909</v>
+      </c>
+      <c r="D27">
+        <v>1220.232793720491</v>
+      </c>
+      <c r="E27">
+        <v>-419.875</v>
+      </c>
+      <c r="F27">
+        <v>512.525</v>
+      </c>
+      <c r="G27">
+        <v>40.5</v>
+      </c>
+      <c r="H27">
+        <v>1117.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>107.3</v>
+      </c>
+      <c r="K27">
+        <v>53</v>
+      </c>
+      <c r="L27">
+        <v>54.3</v>
+      </c>
+      <c r="M27">
+        <v>122.39097</v>
+      </c>
+      <c r="N27">
+        <v>-68.09097</v>
+      </c>
+      <c r="O27">
+        <v>-17.02274250000001</v>
+      </c>
+      <c r="P27">
+        <v>-51.06822749999999</v>
+      </c>
+      <c r="Q27">
+        <v>1.931772500000008</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1383419212022018</v>
+      </c>
+      <c r="T27">
+        <v>1.432501697435163</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.1109150454482059</v>
+      </c>
+      <c r="W27">
+        <v>0.2123134871469684</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.4436601817928234</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1588348126883934</v>
+      </c>
+      <c r="C28">
+        <v>707.3754787229296</v>
+      </c>
+      <c r="D28">
+        <v>1199.90147872293</v>
+      </c>
+      <c r="E28">
+        <v>-399.374</v>
+      </c>
+      <c r="F28">
+        <v>533.026</v>
+      </c>
+      <c r="G28">
+        <v>40.5</v>
+      </c>
+      <c r="H28">
+        <v>1117.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>107.3</v>
+      </c>
+      <c r="K28">
+        <v>53</v>
+      </c>
+      <c r="L28">
+        <v>54.3</v>
+      </c>
+      <c r="M28">
+        <v>127.2866088</v>
+      </c>
+      <c r="N28">
+        <v>-72.9866088</v>
+      </c>
+      <c r="O28">
+        <v>-18.24665220000001</v>
+      </c>
+      <c r="P28">
+        <v>-54.73995659999999</v>
+      </c>
+      <c r="Q28">
+        <v>-1.739956599999992</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1396870822995288</v>
+      </c>
+      <c r="T28">
+        <v>1.451859828481584</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.1066490821617364</v>
+      </c>
+      <c r="W28">
+        <v>0.2133321991797774</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.4265963286469456</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1608348126883934</v>
+      </c>
+      <c r="C29">
+        <v>667.2095740569669</v>
+      </c>
+      <c r="D29">
+        <v>1180.236574056967</v>
+      </c>
+      <c r="E29">
+        <v>-378.8729999999999</v>
+      </c>
+      <c r="F29">
+        <v>553.527</v>
+      </c>
+      <c r="G29">
+        <v>40.5</v>
+      </c>
+      <c r="H29">
+        <v>1117.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>107.3</v>
+      </c>
+      <c r="K29">
+        <v>53</v>
+      </c>
+      <c r="L29">
+        <v>54.3</v>
+      </c>
+      <c r="M29">
+        <v>132.1822476</v>
+      </c>
+      <c r="N29">
+        <v>-77.88224760000001</v>
+      </c>
+      <c r="O29">
+        <v>-19.47056190000001</v>
+      </c>
+      <c r="P29">
+        <v>-58.41168570000001</v>
+      </c>
+      <c r="Q29">
+        <v>-5.411685700000007</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1410690971255498</v>
+      </c>
+      <c r="T29">
+        <v>1.471748319282702</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.1026991161557462</v>
+      </c>
+      <c r="W29">
+        <v>0.2142754510620078</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.4107964646229846</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1628348126883934</v>
+      </c>
+      <c r="C30">
+        <v>627.6778431117439</v>
+      </c>
+      <c r="D30">
+        <v>1161.205843111744</v>
+      </c>
+      <c r="E30">
+        <v>-358.372</v>
+      </c>
+      <c r="F30">
+        <v>574.028</v>
+      </c>
+      <c r="G30">
+        <v>40.5</v>
+      </c>
+      <c r="H30">
+        <v>1117.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>107.3</v>
+      </c>
+      <c r="K30">
+        <v>53</v>
+      </c>
+      <c r="L30">
+        <v>54.3</v>
+      </c>
+      <c r="M30">
+        <v>137.0778864</v>
+      </c>
+      <c r="N30">
+        <v>-82.77788640000001</v>
+      </c>
+      <c r="O30">
+        <v>-20.69447160000001</v>
+      </c>
+      <c r="P30">
+        <v>-62.0834148</v>
+      </c>
+      <c r="Q30">
+        <v>-9.0834148</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1424895012522935</v>
+      </c>
+      <c r="T30">
+        <v>1.492189268161629</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.09903129057875526</v>
+      </c>
+      <c r="W30">
+        <v>0.2151513278097933</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.3961251623150209</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1648348126883934</v>
+      </c>
+      <c r="C31">
+        <v>588.7500954799976</v>
+      </c>
+      <c r="D31">
+        <v>1142.779095479998</v>
+      </c>
+      <c r="E31">
+        <v>-337.8710000000001</v>
+      </c>
+      <c r="F31">
+        <v>594.5289999999999</v>
+      </c>
+      <c r="G31">
+        <v>40.5</v>
+      </c>
+      <c r="H31">
+        <v>1117.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>107.3</v>
+      </c>
+      <c r="K31">
+        <v>53</v>
+      </c>
+      <c r="L31">
+        <v>54.3</v>
+      </c>
+      <c r="M31">
+        <v>141.9735252</v>
+      </c>
+      <c r="N31">
+        <v>-87.67352519999999</v>
+      </c>
+      <c r="O31">
+        <v>-21.91838130000001</v>
+      </c>
+      <c r="P31">
+        <v>-65.75514389999998</v>
+      </c>
+      <c r="Q31">
+        <v>-12.75514389999998</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1439499167628892</v>
+      </c>
+      <c r="T31">
+        <v>1.513206018417426</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.09561641848983268</v>
+      </c>
+      <c r="W31">
+        <v>0.215966799264628</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.3824656739593306</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1668348126883934</v>
+      </c>
+      <c r="C32">
+        <v>550.3980271418691</v>
+      </c>
+      <c r="D32">
+        <v>1124.928027141869</v>
+      </c>
+      <c r="E32">
+        <v>-317.37</v>
+      </c>
+      <c r="F32">
+        <v>615.03</v>
+      </c>
+      <c r="G32">
+        <v>40.5</v>
+      </c>
+      <c r="H32">
+        <v>1117.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>107.3</v>
+      </c>
+      <c r="K32">
+        <v>53</v>
+      </c>
+      <c r="L32">
+        <v>54.3</v>
+      </c>
+      <c r="M32">
+        <v>146.869164</v>
+      </c>
+      <c r="N32">
+        <v>-92.56916400000001</v>
+      </c>
+      <c r="O32">
+        <v>-23.14229100000001</v>
+      </c>
+      <c r="P32">
+        <v>-69.426873</v>
+      </c>
+      <c r="Q32">
+        <v>-16.426873</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1454520584309305</v>
+      </c>
+      <c r="T32">
+        <v>1.534823247251961</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.09242920454017158</v>
+      </c>
+      <c r="W32">
+        <v>0.216727905955807</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.3697168181606861</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1688348126883934</v>
+      </c>
+      <c r="C33">
+        <v>512.5950753970301</v>
+      </c>
+      <c r="D33">
+        <v>1107.62607539703</v>
+      </c>
+      <c r="E33">
+        <v>-296.869</v>
+      </c>
+      <c r="F33">
+        <v>635.5309999999999</v>
+      </c>
+      <c r="G33">
+        <v>40.5</v>
+      </c>
+      <c r="H33">
+        <v>1117.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>107.3</v>
+      </c>
+      <c r="K33">
+        <v>53</v>
+      </c>
+      <c r="L33">
+        <v>54.3</v>
+      </c>
+      <c r="M33">
+        <v>151.7648028</v>
+      </c>
+      <c r="N33">
+        <v>-97.46480279999999</v>
+      </c>
+      <c r="O33">
+        <v>-24.36620070000001</v>
+      </c>
+      <c r="P33">
+        <v>-73.09860209999998</v>
+      </c>
+      <c r="Q33">
+        <v>-20.09860209999998</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1469977404371758</v>
+      </c>
+      <c r="T33">
+        <v>1.557067062429526</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.08944761729694026</v>
+      </c>
+      <c r="W33">
+        <v>0.2174399089894907</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.3577904691877608</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1708348126883934</v>
+      </c>
+      <c r="C34">
+        <v>475.3162869813181</v>
+      </c>
+      <c r="D34">
+        <v>1090.848286981318</v>
+      </c>
+      <c r="E34">
+        <v>-276.3679999999999</v>
+      </c>
+      <c r="F34">
+        <v>656.032</v>
+      </c>
+      <c r="G34">
+        <v>40.5</v>
+      </c>
+      <c r="H34">
+        <v>1117.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>107.3</v>
+      </c>
+      <c r="K34">
+        <v>53</v>
+      </c>
+      <c r="L34">
+        <v>54.3</v>
+      </c>
+      <c r="M34">
+        <v>156.6604416</v>
+      </c>
+      <c r="N34">
+        <v>-102.3604416</v>
+      </c>
+      <c r="O34">
+        <v>-25.59011040000001</v>
+      </c>
+      <c r="P34">
+        <v>-76.7703312</v>
+      </c>
+      <c r="Q34">
+        <v>-23.7703312</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.148588883678899</v>
+      </c>
+      <c r="T34">
+        <v>1.579965107465254</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.08665237925641085</v>
+      </c>
+      <c r="W34">
+        <v>0.2181074118335691</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.3466095170256432</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1728348126883934</v>
+      </c>
+      <c r="C35">
+        <v>438.5381979907535</v>
+      </c>
+      <c r="D35">
+        <v>1074.571197990753</v>
+      </c>
+      <c r="E35">
+        <v>-255.867</v>
+      </c>
+      <c r="F35">
+        <v>676.533</v>
+      </c>
+      <c r="G35">
+        <v>40.5</v>
+      </c>
+      <c r="H35">
+        <v>1117.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>107.3</v>
+      </c>
+      <c r="K35">
+        <v>53</v>
+      </c>
+      <c r="L35">
+        <v>54.3</v>
+      </c>
+      <c r="M35">
+        <v>161.5560804</v>
+      </c>
+      <c r="N35">
+        <v>-107.2560804</v>
+      </c>
+      <c r="O35">
+        <v>-26.81402010000001</v>
+      </c>
+      <c r="P35">
+        <v>-80.44206030000001</v>
+      </c>
+      <c r="Q35">
+        <v>-27.44206030000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1502275237338079</v>
+      </c>
+      <c r="T35">
+        <v>1.603546676233392</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.08402654958197417</v>
+      </c>
+      <c r="W35">
+        <v>0.2187344599598246</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.3361061983278965</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1748348126883935</v>
+      </c>
+      <c r="C36">
+        <v>402.2387243977884</v>
+      </c>
+      <c r="D36">
+        <v>1058.772724397788</v>
+      </c>
+      <c r="E36">
+        <v>-235.366</v>
+      </c>
+      <c r="F36">
+        <v>697.034</v>
+      </c>
+      <c r="G36">
+        <v>40.5</v>
+      </c>
+      <c r="H36">
+        <v>1117.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>107.3</v>
+      </c>
+      <c r="K36">
+        <v>53</v>
+      </c>
+      <c r="L36">
+        <v>54.3</v>
+      </c>
+      <c r="M36">
+        <v>166.4517192</v>
+      </c>
+      <c r="N36">
+        <v>-112.1517192</v>
+      </c>
+      <c r="O36">
+        <v>-28.03792980000002</v>
+      </c>
+      <c r="P36">
+        <v>-84.1137894</v>
+      </c>
+      <c r="Q36">
+        <v>-31.1137894</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1519158195479566</v>
+      </c>
+      <c r="T36">
+        <v>1.627842837994504</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.08155518047662198</v>
+      </c>
+      <c r="W36">
+        <v>0.2193246229021827</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.3262207219064878</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1768348126883935</v>
+      </c>
+      <c r="C37">
+        <v>366.3970620854784</v>
+      </c>
+      <c r="D37">
+        <v>1043.432062085478</v>
+      </c>
+      <c r="E37">
+        <v>-214.8649999999999</v>
+      </c>
+      <c r="F37">
+        <v>717.5350000000001</v>
+      </c>
+      <c r="G37">
+        <v>40.5</v>
+      </c>
+      <c r="H37">
+        <v>1117.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>107.3</v>
+      </c>
+      <c r="K37">
+        <v>53</v>
+      </c>
+      <c r="L37">
+        <v>54.3</v>
+      </c>
+      <c r="M37">
+        <v>171.347358</v>
+      </c>
+      <c r="N37">
+        <v>-117.047358</v>
+      </c>
+      <c r="O37">
+        <v>-29.26183950000003</v>
+      </c>
+      <c r="P37">
+        <v>-87.78551850000002</v>
+      </c>
+      <c r="Q37">
+        <v>-34.78551850000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1536560629256174</v>
+      </c>
+      <c r="T37">
+        <v>1.65288657396365</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07922503246300421</v>
+      </c>
+      <c r="W37">
+        <v>0.2198810622478346</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3169001298520167</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1788348126883934</v>
+      </c>
+      <c r="C38">
+        <v>330.9935954480246</v>
+      </c>
+      <c r="D38">
+        <v>1028.529595448025</v>
+      </c>
+      <c r="E38">
+        <v>-194.364</v>
+      </c>
+      <c r="F38">
+        <v>738.0359999999999</v>
+      </c>
+      <c r="G38">
+        <v>40.5</v>
+      </c>
+      <c r="H38">
+        <v>1117.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>107.3</v>
+      </c>
+      <c r="K38">
+        <v>53</v>
+      </c>
+      <c r="L38">
+        <v>54.3</v>
+      </c>
+      <c r="M38">
+        <v>176.2429968</v>
+      </c>
+      <c r="N38">
+        <v>-121.9429968</v>
+      </c>
+      <c r="O38">
+        <v>-30.48574920000001</v>
+      </c>
+      <c r="P38">
+        <v>-91.45724759999997</v>
+      </c>
+      <c r="Q38">
+        <v>-38.45724759999997</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1554506889088302</v>
+      </c>
+      <c r="T38">
+        <v>1.678712926681832</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07702433711680966</v>
+      </c>
+      <c r="W38">
+        <v>0.2204065882965059</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3080973484672385</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1808348126883934</v>
+      </c>
+      <c r="C39">
+        <v>296.0098137133167</v>
+      </c>
+      <c r="D39">
+        <v>1014.046813713317</v>
+      </c>
+      <c r="E39">
+        <v>-173.8630000000001</v>
+      </c>
+      <c r="F39">
+        <v>758.5369999999999</v>
+      </c>
+      <c r="G39">
+        <v>40.5</v>
+      </c>
+      <c r="H39">
+        <v>1117.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>107.3</v>
+      </c>
+      <c r="K39">
+        <v>53</v>
+      </c>
+      <c r="L39">
+        <v>54.3</v>
+      </c>
+      <c r="M39">
+        <v>181.1386356</v>
+      </c>
+      <c r="N39">
+        <v>-126.8386356</v>
+      </c>
+      <c r="O39">
+        <v>-31.70965890000001</v>
+      </c>
+      <c r="P39">
+        <v>-95.12897669999998</v>
+      </c>
+      <c r="Q39">
+        <v>-42.12897669999998</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1573022871454783</v>
+      </c>
+      <c r="T39">
+        <v>1.70535916361329</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.0749425982758148</v>
+      </c>
+      <c r="W39">
+        <v>0.2209037075317354</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.299770393103259</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1828348126883934</v>
+      </c>
+      <c r="C40">
+        <v>261.4282342369215</v>
+      </c>
+      <c r="D40">
+        <v>999.9662342369215</v>
+      </c>
+      <c r="E40">
+        <v>-153.362</v>
+      </c>
+      <c r="F40">
+        <v>779.038</v>
+      </c>
+      <c r="G40">
+        <v>40.5</v>
+      </c>
+      <c r="H40">
+        <v>1117.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>107.3</v>
+      </c>
+      <c r="K40">
+        <v>53</v>
+      </c>
+      <c r="L40">
+        <v>54.3</v>
+      </c>
+      <c r="M40">
+        <v>186.0342744</v>
+      </c>
+      <c r="N40">
+        <v>-131.7342744</v>
+      </c>
+      <c r="O40">
+        <v>-32.93356860000002</v>
+      </c>
+      <c r="P40">
+        <v>-98.80070579999999</v>
+      </c>
+      <c r="Q40">
+        <v>-45.80070579999999</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1592136143575021</v>
+      </c>
+      <c r="T40">
+        <v>1.732864956574794</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.07297042463697756</v>
+      </c>
+      <c r="W40">
+        <v>0.2213746625966898</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2918816985479102</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1848348126883934</v>
+      </c>
+      <c r="C41">
+        <v>227.2323320991602</v>
+      </c>
+      <c r="D41">
+        <v>986.2713320991603</v>
+      </c>
+      <c r="E41">
+        <v>-132.861</v>
+      </c>
+      <c r="F41">
+        <v>799.539</v>
+      </c>
+      <c r="G41">
+        <v>40.5</v>
+      </c>
+      <c r="H41">
+        <v>1117.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>107.3</v>
+      </c>
+      <c r="K41">
+        <v>53</v>
+      </c>
+      <c r="L41">
+        <v>54.3</v>
+      </c>
+      <c r="M41">
+        <v>190.9299132</v>
+      </c>
+      <c r="N41">
+        <v>-136.6299132</v>
+      </c>
+      <c r="O41">
+        <v>-34.15747830000002</v>
+      </c>
+      <c r="P41">
+        <v>-102.4724349</v>
+      </c>
+      <c r="Q41">
+        <v>-49.47243490000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.161187608035494</v>
+      </c>
+      <c r="T41">
+        <v>1.761272578813726</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.07109938810782429</v>
+      </c>
+      <c r="W41">
+        <v>0.2218214661198516</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2843975524312969</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1868348126883935</v>
+      </c>
+      <c r="C42">
+        <v>193.4064754091975</v>
+      </c>
+      <c r="D42">
+        <v>972.9464754091974</v>
+      </c>
+      <c r="E42">
+        <v>-112.36</v>
+      </c>
+      <c r="F42">
+        <v>820.04</v>
+      </c>
+      <c r="G42">
+        <v>40.5</v>
+      </c>
+      <c r="H42">
+        <v>1117.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>107.3</v>
+      </c>
+      <c r="K42">
+        <v>53</v>
+      </c>
+      <c r="L42">
+        <v>54.3</v>
+      </c>
+      <c r="M42">
+        <v>195.825552</v>
+      </c>
+      <c r="N42">
+        <v>-141.525552</v>
+      </c>
+      <c r="O42">
+        <v>-35.38138800000002</v>
+      </c>
+      <c r="P42">
+        <v>-106.144164</v>
+      </c>
+      <c r="Q42">
+        <v>-53.14416399999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1632274015027522</v>
+      </c>
+      <c r="T42">
+        <v>1.790627121793954</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06932190340512868</v>
+      </c>
+      <c r="W42">
+        <v>0.2222459294668553</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2772876136205146</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1888348126883934</v>
+      </c>
+      <c r="C43">
+        <v>159.9358657835982</v>
+      </c>
+      <c r="D43">
+        <v>959.9768657835982</v>
+      </c>
+      <c r="E43">
+        <v>-91.85899999999992</v>
+      </c>
+      <c r="F43">
+        <v>840.5410000000001</v>
+      </c>
+      <c r="G43">
+        <v>40.5</v>
+      </c>
+      <c r="H43">
+        <v>1117.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>107.3</v>
+      </c>
+      <c r="K43">
+        <v>53</v>
+      </c>
+      <c r="L43">
+        <v>54.3</v>
+      </c>
+      <c r="M43">
+        <v>200.7211908</v>
+      </c>
+      <c r="N43">
+        <v>-146.4211908</v>
+      </c>
+      <c r="O43">
+        <v>-36.60529770000002</v>
+      </c>
+      <c r="P43">
+        <v>-109.8158931</v>
+      </c>
+      <c r="Q43">
+        <v>-56.81589310000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1653363405112734</v>
+      </c>
+      <c r="T43">
+        <v>1.82097673402775</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06763112527329627</v>
+      </c>
+      <c r="W43">
+        <v>0.2226496872847369</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2705245010931849</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1908348126883934</v>
+      </c>
+      <c r="C44">
+        <v>126.8064835228703</v>
+      </c>
+      <c r="D44">
+        <v>947.3484835228702</v>
+      </c>
+      <c r="E44">
+        <v>-71.35800000000006</v>
+      </c>
+      <c r="F44">
+        <v>861.0419999999999</v>
+      </c>
+      <c r="G44">
+        <v>40.5</v>
+      </c>
+      <c r="H44">
+        <v>1117.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>107.3</v>
+      </c>
+      <c r="K44">
+        <v>53</v>
+      </c>
+      <c r="L44">
+        <v>54.3</v>
+      </c>
+      <c r="M44">
+        <v>205.6168296</v>
+      </c>
+      <c r="N44">
+        <v>-151.3168296</v>
+      </c>
+      <c r="O44">
+        <v>-37.82920740000002</v>
+      </c>
+      <c r="P44">
+        <v>-113.4876222</v>
+      </c>
+      <c r="Q44">
+        <v>-60.48762219999999</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1675180015545712</v>
+      </c>
+      <c r="T44">
+        <v>1.852372884614435</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06602086038583685</v>
+      </c>
+      <c r="W44">
+        <v>0.2230342185398622</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.2640834415433472</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1928348126883934</v>
+      </c>
+      <c r="C45">
+        <v>94.0050370590011</v>
+      </c>
+      <c r="D45">
+        <v>935.048037059001</v>
+      </c>
+      <c r="E45">
+        <v>-50.85700000000008</v>
+      </c>
+      <c r="F45">
+        <v>881.5429999999999</v>
+      </c>
+      <c r="G45">
+        <v>40.5</v>
+      </c>
+      <c r="H45">
+        <v>1117.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>107.3</v>
+      </c>
+      <c r="K45">
+        <v>53</v>
+      </c>
+      <c r="L45">
+        <v>54.3</v>
+      </c>
+      <c r="M45">
+        <v>210.5124684</v>
+      </c>
+      <c r="N45">
+        <v>-156.2124684</v>
+      </c>
+      <c r="O45">
+        <v>-39.05311710000001</v>
+      </c>
+      <c r="P45">
+        <v>-117.1593513</v>
+      </c>
+      <c r="Q45">
+        <v>-64.15935129999997</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1697762121081602</v>
+      </c>
+      <c r="T45">
+        <v>1.884870654519952</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.06448549153965459</v>
+      </c>
+      <c r="W45">
+        <v>0.2234008646203305</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.2579419661586183</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1948348126883934</v>
+      </c>
+      <c r="C46">
+        <v>61.51891629077431</v>
+      </c>
+      <c r="D46">
+        <v>923.0629162907743</v>
+      </c>
+      <c r="E46">
+        <v>-30.35599999999999</v>
+      </c>
+      <c r="F46">
+        <v>902.044</v>
+      </c>
+      <c r="G46">
+        <v>40.5</v>
+      </c>
+      <c r="H46">
+        <v>1117.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>107.3</v>
+      </c>
+      <c r="K46">
+        <v>53</v>
+      </c>
+      <c r="L46">
+        <v>54.3</v>
+      </c>
+      <c r="M46">
+        <v>215.4081072</v>
+      </c>
+      <c r="N46">
+        <v>-161.1081072</v>
+      </c>
+      <c r="O46">
+        <v>-40.27702680000002</v>
+      </c>
+      <c r="P46">
+        <v>-120.8310804</v>
+      </c>
+      <c r="Q46">
+        <v>-67.83108039999999</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1721150730386631</v>
+      </c>
+      <c r="T46">
+        <v>1.918529059064951</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.06301991218648062</v>
+      </c>
+      <c r="W46">
+        <v>0.2237508449698684</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.2520796487459225</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1968348126883934</v>
+      </c>
+      <c r="C47">
+        <v>29.33614946246382</v>
+      </c>
+      <c r="D47">
+        <v>911.3811494624638</v>
+      </c>
+      <c r="E47">
+        <v>-9.855000000000018</v>
+      </c>
+      <c r="F47">
+        <v>922.545</v>
+      </c>
+      <c r="G47">
+        <v>40.5</v>
+      </c>
+      <c r="H47">
+        <v>1117.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>107.3</v>
+      </c>
+      <c r="K47">
+        <v>53</v>
+      </c>
+      <c r="L47">
+        <v>54.3</v>
+      </c>
+      <c r="M47">
+        <v>220.303746</v>
+      </c>
+      <c r="N47">
+        <v>-166.003746</v>
+      </c>
+      <c r="O47">
+        <v>-41.50093650000002</v>
+      </c>
+      <c r="P47">
+        <v>-124.5028095</v>
+      </c>
+      <c r="Q47">
+        <v>-71.50280949999996</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1745389834575478</v>
+      </c>
+      <c r="T47">
+        <v>1.953411405593404</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.06161946969344773</v>
+      </c>
+      <c r="W47">
+        <v>0.2240852706372047</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.2464778787737909</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1988348126883935</v>
+      </c>
+      <c r="C48">
+        <v>-2.554636724083593</v>
+      </c>
+      <c r="D48">
+        <v>899.9913632759165</v>
+      </c>
+      <c r="E48">
+        <v>10.64600000000007</v>
+      </c>
+      <c r="F48">
+        <v>943.046</v>
+      </c>
+      <c r="G48">
+        <v>40.5</v>
+      </c>
+      <c r="H48">
+        <v>1117.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>107.3</v>
+      </c>
+      <c r="K48">
+        <v>53</v>
+      </c>
+      <c r="L48">
+        <v>54.3</v>
+      </c>
+      <c r="M48">
+        <v>225.1993848</v>
+      </c>
+      <c r="N48">
+        <v>-170.8993848</v>
+      </c>
+      <c r="O48">
+        <v>-42.72484620000002</v>
+      </c>
+      <c r="P48">
+        <v>-128.1745386</v>
+      </c>
+      <c r="Q48">
+        <v>-75.17453859999998</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1770526683363913</v>
+      </c>
+      <c r="T48">
+        <v>1.989585690882171</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.06027991600445973</v>
+      </c>
+      <c r="W48">
+        <v>0.224405156058135</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.2411196640178389</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2008348126883934</v>
+      </c>
+      <c r="C49">
+        <v>-34.16425404333415</v>
+      </c>
+      <c r="D49">
+        <v>888.8827459566659</v>
+      </c>
+      <c r="E49">
+        <v>31.14700000000005</v>
+      </c>
+      <c r="F49">
+        <v>963.547</v>
+      </c>
+      <c r="G49">
+        <v>40.5</v>
+      </c>
+      <c r="H49">
+        <v>1117.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>107.3</v>
+      </c>
+      <c r="K49">
+        <v>53</v>
+      </c>
+      <c r="L49">
+        <v>54.3</v>
+      </c>
+      <c r="M49">
+        <v>230.0950236</v>
+      </c>
+      <c r="N49">
+        <v>-175.7950236</v>
+      </c>
+      <c r="O49">
+        <v>-43.94875590000003</v>
+      </c>
+      <c r="P49">
+        <v>-131.8462677</v>
+      </c>
+      <c r="Q49">
+        <v>-78.8462677</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1796612092483987</v>
+      </c>
+      <c r="T49">
+        <v>2.027125043540325</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05899736460010952</v>
+      </c>
+      <c r="W49">
+        <v>0.2247114293334939</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.2359894584004379</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2028348126883934</v>
+      </c>
+      <c r="C50">
+        <v>-65.50298697805226</v>
+      </c>
+      <c r="D50">
+        <v>878.0450130219476</v>
+      </c>
+      <c r="E50">
+        <v>51.64799999999991</v>
+      </c>
+      <c r="F50">
+        <v>984.0479999999999</v>
+      </c>
+      <c r="G50">
+        <v>40.5</v>
+      </c>
+      <c r="H50">
+        <v>1117.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>107.3</v>
+      </c>
+      <c r="K50">
+        <v>53</v>
+      </c>
+      <c r="L50">
+        <v>54.3</v>
+      </c>
+      <c r="M50">
+        <v>234.9906624</v>
+      </c>
+      <c r="N50">
+        <v>-180.6906624</v>
+      </c>
+      <c r="O50">
+        <v>-45.17266560000002</v>
+      </c>
+      <c r="P50">
+        <v>-135.5179968</v>
+      </c>
+      <c r="Q50">
+        <v>-82.51799679999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1823700786570218</v>
+      </c>
+      <c r="T50">
+        <v>2.066108217454563</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05776825283760725</v>
+      </c>
+      <c r="W50">
+        <v>0.2250049412223794</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.2310730113504288</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2048348126883934</v>
+      </c>
+      <c r="C51">
+        <v>-96.58062447719919</v>
+      </c>
+      <c r="D51">
+        <v>867.4683755228008</v>
+      </c>
+      <c r="E51">
+        <v>72.149</v>
+      </c>
+      <c r="F51">
+        <v>1004.549</v>
+      </c>
+      <c r="G51">
+        <v>40.5</v>
+      </c>
+      <c r="H51">
+        <v>1117.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>107.3</v>
+      </c>
+      <c r="K51">
+        <v>53</v>
+      </c>
+      <c r="L51">
+        <v>54.3</v>
+      </c>
+      <c r="M51">
+        <v>239.8863012</v>
+      </c>
+      <c r="N51">
+        <v>-185.5863012</v>
+      </c>
+      <c r="O51">
+        <v>-46.39657530000003</v>
+      </c>
+      <c r="P51">
+        <v>-139.1897259</v>
+      </c>
+      <c r="Q51">
+        <v>-86.18972590000001</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.185185178238532</v>
+      </c>
+      <c r="T51">
+        <v>2.106620143287005</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.05658930890214587</v>
+      </c>
+      <c r="W51">
+        <v>0.2252864730341676</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2263572356085833</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2068348126883934</v>
+      </c>
+      <c r="C52">
+        <v>-127.4064894458824</v>
+      </c>
+      <c r="D52">
+        <v>857.1435105541176</v>
+      </c>
+      <c r="E52">
+        <v>92.64999999999998</v>
+      </c>
+      <c r="F52">
+        <v>1025.05</v>
+      </c>
+      <c r="G52">
+        <v>40.5</v>
+      </c>
+      <c r="H52">
+        <v>1117.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>107.3</v>
+      </c>
+      <c r="K52">
+        <v>53</v>
+      </c>
+      <c r="L52">
+        <v>54.3</v>
+      </c>
+      <c r="M52">
+        <v>244.78194</v>
+      </c>
+      <c r="N52">
+        <v>-190.48194</v>
+      </c>
+      <c r="O52">
+        <v>-47.62048500000002</v>
+      </c>
+      <c r="P52">
+        <v>-142.861455</v>
+      </c>
+      <c r="Q52">
+        <v>-89.86145499999998</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1881128818033027</v>
+      </c>
+      <c r="T52">
+        <v>2.148752546152745</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05545752272410296</v>
+      </c>
+      <c r="W52">
+        <v>0.2255567435734842</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2218300908964117</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2088348126883934</v>
+      </c>
+      <c r="C53">
+        <v>-157.9894661540862</v>
+      </c>
+      <c r="D53">
+        <v>847.0615338459137</v>
+      </c>
+      <c r="E53">
+        <v>113.151</v>
+      </c>
+      <c r="F53">
+        <v>1045.551</v>
+      </c>
+      <c r="G53">
+        <v>40.5</v>
+      </c>
+      <c r="H53">
+        <v>1117.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>107.3</v>
+      </c>
+      <c r="K53">
+        <v>53</v>
+      </c>
+      <c r="L53">
+        <v>54.3</v>
+      </c>
+      <c r="M53">
+        <v>249.6775788</v>
+      </c>
+      <c r="N53">
+        <v>-195.3775788</v>
+      </c>
+      <c r="O53">
+        <v>-48.84439470000002</v>
+      </c>
+      <c r="P53">
+        <v>-146.5331841</v>
+      </c>
+      <c r="Q53">
+        <v>-93.53318409999997</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1911600834727578</v>
+      </c>
+      <c r="T53">
+        <v>2.192604638931372</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05437012031774799</v>
+      </c>
+      <c r="W53">
+        <v>0.2258164152681218</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.217480481270992</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2108348126883934</v>
+      </c>
+      <c r="C54">
+        <v>-188.3380257335556</v>
+      </c>
+      <c r="D54">
+        <v>837.2139742664443</v>
+      </c>
+      <c r="E54">
+        <v>133.6519999999999</v>
+      </c>
+      <c r="F54">
+        <v>1066.052</v>
+      </c>
+      <c r="G54">
+        <v>40.5</v>
+      </c>
+      <c r="H54">
+        <v>1117.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>107.3</v>
+      </c>
+      <c r="K54">
+        <v>53</v>
+      </c>
+      <c r="L54">
+        <v>54.3</v>
+      </c>
+      <c r="M54">
+        <v>254.5732176</v>
+      </c>
+      <c r="N54">
+        <v>-200.2732176</v>
+      </c>
+      <c r="O54">
+        <v>-50.06830440000002</v>
+      </c>
+      <c r="P54">
+        <v>-150.2049132</v>
+      </c>
+      <c r="Q54">
+        <v>-97.20491319999999</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1943342518784402</v>
+      </c>
+      <c r="T54">
+        <v>2.238283902242443</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.05332454108086822</v>
+      </c>
+      <c r="W54">
+        <v>0.2260660995898887</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2132981643234727</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2128348126883934</v>
+      </c>
+      <c r="C55">
+        <v>-218.4602499166218</v>
+      </c>
+      <c r="D55">
+        <v>827.5927500833783</v>
+      </c>
+      <c r="E55">
+        <v>154.1530000000001</v>
+      </c>
+      <c r="F55">
+        <v>1086.553</v>
+      </c>
+      <c r="G55">
+        <v>40.5</v>
+      </c>
+      <c r="H55">
+        <v>1117.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>107.3</v>
+      </c>
+      <c r="K55">
+        <v>53</v>
+      </c>
+      <c r="L55">
+        <v>54.3</v>
+      </c>
+      <c r="M55">
+        <v>259.4688564</v>
+      </c>
+      <c r="N55">
+        <v>-205.1688564</v>
+      </c>
+      <c r="O55">
+        <v>-51.29221410000003</v>
+      </c>
+      <c r="P55">
+        <v>-153.8766423</v>
+      </c>
+      <c r="Q55">
+        <v>-100.8766423</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1976434912801092</v>
+      </c>
+      <c r="T55">
+        <v>2.285906963992282</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.05231841766424806</v>
+      </c>
+      <c r="W55">
+        <v>0.2263063618617776</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2092736706569922</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2148348126883934</v>
+      </c>
+      <c r="C56">
+        <v>-248.3638531567926</v>
+      </c>
+      <c r="D56">
+        <v>818.1901468432075</v>
+      </c>
+      <c r="E56">
+        <v>174.6540000000001</v>
+      </c>
+      <c r="F56">
+        <v>1107.054</v>
+      </c>
+      <c r="G56">
+        <v>40.5</v>
+      </c>
+      <c r="H56">
+        <v>1117.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>107.3</v>
+      </c>
+      <c r="K56">
+        <v>53</v>
+      </c>
+      <c r="L56">
+        <v>54.3</v>
+      </c>
+      <c r="M56">
+        <v>264.3644952</v>
+      </c>
+      <c r="N56">
+        <v>-210.0644952</v>
+      </c>
+      <c r="O56">
+        <v>-52.51612380000002</v>
+      </c>
+      <c r="P56">
+        <v>-157.5483714</v>
+      </c>
+      <c r="Q56">
+        <v>-104.5483714</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2010966106557638</v>
+      </c>
+      <c r="T56">
+        <v>2.335600593644288</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.0513495580778731</v>
+      </c>
+      <c r="W56">
+        <v>0.2265377255310039</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2053982323114923</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2168348126883934</v>
+      </c>
+      <c r="C57">
+        <v>-278.0562032583623</v>
+      </c>
+      <c r="D57">
+        <v>808.9987967416378</v>
+      </c>
+      <c r="E57">
+        <v>195.1550000000001</v>
+      </c>
+      <c r="F57">
+        <v>1127.555</v>
+      </c>
+      <c r="G57">
+        <v>40.5</v>
+      </c>
+      <c r="H57">
+        <v>1117.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>107.3</v>
+      </c>
+      <c r="K57">
+        <v>53</v>
+      </c>
+      <c r="L57">
+        <v>54.3</v>
+      </c>
+      <c r="M57">
+        <v>269.2601340000001</v>
+      </c>
+      <c r="N57">
+        <v>-214.960134</v>
+      </c>
+      <c r="O57">
+        <v>-53.74003350000003</v>
+      </c>
+      <c r="P57">
+        <v>-161.2201005</v>
+      </c>
+      <c r="Q57">
+        <v>-108.2201005</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2047032020036696</v>
+      </c>
+      <c r="T57">
+        <v>2.387502829058606</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05041592974918449</v>
+      </c>
+      <c r="W57">
+        <v>0.2267606759758947</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.201663718996738</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2188348126883934</v>
+      </c>
+      <c r="C58">
+        <v>-307.5443406309755</v>
+      </c>
+      <c r="D58">
+        <v>800.0116593690245</v>
+      </c>
+      <c r="E58">
+        <v>215.6560000000001</v>
+      </c>
+      <c r="F58">
+        <v>1148.056</v>
+      </c>
+      <c r="G58">
+        <v>40.5</v>
+      </c>
+      <c r="H58">
+        <v>1117.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>107.3</v>
+      </c>
+      <c r="K58">
+        <v>53</v>
+      </c>
+      <c r="L58">
+        <v>54.3</v>
+      </c>
+      <c r="M58">
+        <v>274.1557728</v>
+      </c>
+      <c r="N58">
+        <v>-219.8557728</v>
+      </c>
+      <c r="O58">
+        <v>-54.96394320000002</v>
+      </c>
+      <c r="P58">
+        <v>-164.8918296</v>
+      </c>
+      <c r="Q58">
+        <v>-111.8918296</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2084737293219348</v>
+      </c>
+      <c r="T58">
+        <v>2.441764256991756</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04951564528937763</v>
+      </c>
+      <c r="W58">
+        <v>0.2269756639048966</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1980625811575105</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2208348126883934</v>
+      </c>
+      <c r="C59">
+        <v>-336.8349962749043</v>
+      </c>
+      <c r="D59">
+        <v>791.2220037250958</v>
+      </c>
+      <c r="E59">
+        <v>236.157</v>
+      </c>
+      <c r="F59">
+        <v>1168.557</v>
+      </c>
+      <c r="G59">
+        <v>40.5</v>
+      </c>
+      <c r="H59">
+        <v>1117.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>107.3</v>
+      </c>
+      <c r="K59">
+        <v>53</v>
+      </c>
+      <c r="L59">
+        <v>54.3</v>
+      </c>
+      <c r="M59">
+        <v>279.0514116</v>
+      </c>
+      <c r="N59">
+        <v>-224.7514116</v>
+      </c>
+      <c r="O59">
+        <v>-56.18785290000002</v>
+      </c>
+      <c r="P59">
+        <v>-168.5635587</v>
+      </c>
+      <c r="Q59">
+        <v>-115.5635587</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2124196300038403</v>
+      </c>
+      <c r="T59">
+        <v>2.498549472270634</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04864694975798504</v>
+      </c>
+      <c r="W59">
+        <v>0.2271831083977932</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1945877990319401</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2228348126883934</v>
+      </c>
+      <c r="C60">
+        <v>-365.9346085935938</v>
+      </c>
+      <c r="D60">
+        <v>782.623391406406</v>
+      </c>
+      <c r="E60">
+        <v>256.6579999999998</v>
+      </c>
+      <c r="F60">
+        <v>1189.058</v>
+      </c>
+      <c r="G60">
+        <v>40.5</v>
+      </c>
+      <c r="H60">
+        <v>1117.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>107.3</v>
+      </c>
+      <c r="K60">
+        <v>53</v>
+      </c>
+      <c r="L60">
+        <v>54.3</v>
+      </c>
+      <c r="M60">
+        <v>283.9470504</v>
+      </c>
+      <c r="N60">
+        <v>-229.6470504</v>
+      </c>
+      <c r="O60">
+        <v>-57.41176260000002</v>
+      </c>
+      <c r="P60">
+        <v>-172.2352877999999</v>
+      </c>
+      <c r="Q60">
+        <v>-119.2352877999999</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2165534307182174</v>
+      </c>
+      <c r="T60">
+        <v>2.558038745419935</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04780820924491634</v>
+      </c>
+      <c r="W60">
+        <v>0.227383399632314</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1912328369796653</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2248348126883934</v>
+      </c>
+      <c r="C61">
+        <v>-394.8493391217323</v>
+      </c>
+      <c r="D61">
+        <v>774.2096608782676</v>
+      </c>
+      <c r="E61">
+        <v>277.159</v>
+      </c>
+      <c r="F61">
+        <v>1209.559</v>
+      </c>
+      <c r="G61">
+        <v>40.5</v>
+      </c>
+      <c r="H61">
+        <v>1117.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>107.3</v>
+      </c>
+      <c r="K61">
+        <v>53</v>
+      </c>
+      <c r="L61">
+        <v>54.3</v>
+      </c>
+      <c r="M61">
+        <v>288.8426892</v>
+      </c>
+      <c r="N61">
+        <v>-234.5426892</v>
+      </c>
+      <c r="O61">
+        <v>-58.63567230000002</v>
+      </c>
+      <c r="P61">
+        <v>-175.9070169</v>
+      </c>
+      <c r="Q61">
+        <v>-122.9070169</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.22088888024793</v>
+      </c>
+      <c r="T61">
+        <v>2.620429934332616</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04699790061364657</v>
+      </c>
+      <c r="W61">
+        <v>0.2275769013334612</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1879916024545862</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2268348126883935</v>
+      </c>
+      <c r="C62">
+        <v>-423.585087249583</v>
+      </c>
+      <c r="D62">
+        <v>765.9749127504169</v>
+      </c>
+      <c r="E62">
+        <v>297.66</v>
+      </c>
+      <c r="F62">
+        <v>1230.06</v>
+      </c>
+      <c r="G62">
+        <v>40.5</v>
+      </c>
+      <c r="H62">
+        <v>1117.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>107.3</v>
+      </c>
+      <c r="K62">
+        <v>53</v>
+      </c>
+      <c r="L62">
+        <v>54.3</v>
+      </c>
+      <c r="M62">
+        <v>293.738328</v>
+      </c>
+      <c r="N62">
+        <v>-239.438328</v>
+      </c>
+      <c r="O62">
+        <v>-59.85958200000003</v>
+      </c>
+      <c r="P62">
+        <v>-179.578746</v>
+      </c>
+      <c r="Q62">
+        <v>-126.578746</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2254411022541283</v>
+      </c>
+      <c r="T62">
+        <v>2.685940682690931</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04621460227008579</v>
+      </c>
+      <c r="W62">
+        <v>0.2277639529779035</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1848584090803431</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2288348126883934</v>
+      </c>
+      <c r="C63">
+        <v>-452.1475040175347</v>
+      </c>
+      <c r="D63">
+        <v>757.9134959824652</v>
+      </c>
+      <c r="E63">
+        <v>318.1609999999999</v>
+      </c>
+      <c r="F63">
+        <v>1250.561</v>
+      </c>
+      <c r="G63">
+        <v>40.5</v>
+      </c>
+      <c r="H63">
+        <v>1117.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>107.3</v>
+      </c>
+      <c r="K63">
+        <v>53</v>
+      </c>
+      <c r="L63">
+        <v>54.3</v>
+      </c>
+      <c r="M63">
+        <v>298.6339668</v>
+      </c>
+      <c r="N63">
+        <v>-244.3339668</v>
+      </c>
+      <c r="O63">
+        <v>-61.08349170000002</v>
+      </c>
+      <c r="P63">
+        <v>-183.2504751</v>
+      </c>
+      <c r="Q63">
+        <v>-130.2504751</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2302267715426957</v>
+      </c>
+      <c r="T63">
+        <v>2.754810956606083</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04545698583942865</v>
+      </c>
+      <c r="W63">
+        <v>0.2279448717815444</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1818279433577146</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2308348126883935</v>
+      </c>
+      <c r="C64">
+        <v>-480.5420050486454</v>
+      </c>
+      <c r="D64">
+        <v>750.0199949513545</v>
+      </c>
+      <c r="E64">
+        <v>338.6619999999999</v>
+      </c>
+      <c r="F64">
+        <v>1271.062</v>
+      </c>
+      <c r="G64">
+        <v>40.5</v>
+      </c>
+      <c r="H64">
+        <v>1117.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>107.3</v>
+      </c>
+      <c r="K64">
+        <v>53</v>
+      </c>
+      <c r="L64">
+        <v>54.3</v>
+      </c>
+      <c r="M64">
+        <v>303.5296056</v>
+      </c>
+      <c r="N64">
+        <v>-249.2296056</v>
+      </c>
+      <c r="O64">
+        <v>-62.30740140000002</v>
+      </c>
+      <c r="P64">
+        <v>-186.9222042</v>
+      </c>
+      <c r="Q64">
+        <v>-133.9222042</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2352643181622403</v>
+      </c>
+      <c r="T64">
+        <v>2.827305981779928</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04472380864847013</v>
+      </c>
+      <c r="W64">
+        <v>0.2281199544947453</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1788952345938805</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2328348126883935</v>
+      </c>
+      <c r="C65">
+        <v>-508.773782681377</v>
+      </c>
+      <c r="D65">
+        <v>742.2892173186228</v>
+      </c>
+      <c r="E65">
+        <v>359.1629999999999</v>
+      </c>
+      <c r="F65">
+        <v>1291.563</v>
+      </c>
+      <c r="G65">
+        <v>40.5</v>
+      </c>
+      <c r="H65">
+        <v>1117.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>107.3</v>
+      </c>
+      <c r="K65">
+        <v>53</v>
+      </c>
+      <c r="L65">
+        <v>54.3</v>
+      </c>
+      <c r="M65">
+        <v>308.4252444</v>
+      </c>
+      <c r="N65">
+        <v>-254.1252444</v>
+      </c>
+      <c r="O65">
+        <v>-63.53131110000002</v>
+      </c>
+      <c r="P65">
+        <v>-190.5939332999999</v>
+      </c>
+      <c r="Q65">
+        <v>-137.5939332999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2405741645990576</v>
+      </c>
+      <c r="T65">
+        <v>2.903719656963169</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04401390692389123</v>
+      </c>
+      <c r="W65">
+        <v>0.2282894790265748</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1760556276955649</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2348348126883934</v>
+      </c>
+      <c r="C66">
+        <v>-536.8478173596465</v>
+      </c>
+      <c r="D66">
+        <v>734.7161826403536</v>
+      </c>
+      <c r="E66">
+        <v>379.6640000000001</v>
+      </c>
+      <c r="F66">
+        <v>1312.064</v>
+      </c>
+      <c r="G66">
+        <v>40.5</v>
+      </c>
+      <c r="H66">
+        <v>1117.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>107.3</v>
+      </c>
+      <c r="K66">
+        <v>53</v>
+      </c>
+      <c r="L66">
+        <v>54.3</v>
+      </c>
+      <c r="M66">
+        <v>313.3208832</v>
+      </c>
+      <c r="N66">
+        <v>-259.0208832</v>
+      </c>
+      <c r="O66">
+        <v>-64.75522080000003</v>
+      </c>
+      <c r="P66">
+        <v>-194.2656624</v>
+      </c>
+      <c r="Q66">
+        <v>-141.2656624</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.246179002504587</v>
+      </c>
+      <c r="T66">
+        <v>2.984378536323257</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04332618962820543</v>
+      </c>
+      <c r="W66">
+        <v>0.2284537059167845</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1733047585128217</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2368348126883935</v>
+      </c>
+      <c r="C67">
+        <v>-564.7688883326874</v>
+      </c>
+      <c r="D67">
+        <v>727.2961116673126</v>
+      </c>
+      <c r="E67">
+        <v>400.1650000000001</v>
+      </c>
+      <c r="F67">
+        <v>1332.565</v>
+      </c>
+      <c r="G67">
+        <v>40.5</v>
+      </c>
+      <c r="H67">
+        <v>1117.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>107.3</v>
+      </c>
+      <c r="K67">
+        <v>53</v>
+      </c>
+      <c r="L67">
+        <v>54.3</v>
+      </c>
+      <c r="M67">
+        <v>318.2165220000001</v>
+      </c>
+      <c r="N67">
+        <v>-263.916522</v>
+      </c>
+      <c r="O67">
+        <v>-65.97913050000004</v>
+      </c>
+      <c r="P67">
+        <v>-197.9373915</v>
+      </c>
+      <c r="Q67">
+        <v>-144.9373915</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.252104116861861</v>
+      </c>
+      <c r="T67">
+        <v>3.069646494503922</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.04265963286469458</v>
+      </c>
+      <c r="W67">
+        <v>0.228612879671911</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1706385314587783</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2388348126883935</v>
+      </c>
+      <c r="C68">
+        <v>-592.5415837130336</v>
+      </c>
+      <c r="D68">
+        <v>720.0244162869665</v>
+      </c>
+      <c r="E68">
+        <v>420.6660000000001</v>
+      </c>
+      <c r="F68">
+        <v>1353.066</v>
+      </c>
+      <c r="G68">
+        <v>40.5</v>
+      </c>
+      <c r="H68">
+        <v>1117.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>107.3</v>
+      </c>
+      <c r="K68">
+        <v>53</v>
+      </c>
+      <c r="L68">
+        <v>54.3</v>
+      </c>
+      <c r="M68">
+        <v>323.1121608</v>
+      </c>
+      <c r="N68">
+        <v>-268.8121608</v>
+      </c>
+      <c r="O68">
+        <v>-67.20304020000003</v>
+      </c>
+      <c r="P68">
+        <v>-201.6091206</v>
+      </c>
+      <c r="Q68">
+        <v>-148.6091206</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.258377767357798</v>
+      </c>
+      <c r="T68">
+        <v>3.159930214930508</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.04201327479098708</v>
+      </c>
+      <c r="W68">
+        <v>0.2287672299799123</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1680530991639483</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2408348126883934</v>
+      </c>
+      <c r="C69">
+        <v>-620.1703099371025</v>
+      </c>
+      <c r="D69">
+        <v>712.8966900628975</v>
+      </c>
+      <c r="E69">
+        <v>441.167</v>
+      </c>
+      <c r="F69">
+        <v>1373.567</v>
+      </c>
+      <c r="G69">
+        <v>40.5</v>
+      </c>
+      <c r="H69">
+        <v>1117.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>107.3</v>
+      </c>
+      <c r="K69">
+        <v>53</v>
+      </c>
+      <c r="L69">
+        <v>54.3</v>
+      </c>
+      <c r="M69">
+        <v>328.0077996</v>
+      </c>
+      <c r="N69">
+        <v>-273.7077996</v>
+      </c>
+      <c r="O69">
+        <v>-68.42694990000003</v>
+      </c>
+      <c r="P69">
+        <v>-205.2808497</v>
+      </c>
+      <c r="Q69">
+        <v>-152.2808497</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2650316390959131</v>
+      </c>
+      <c r="T69">
+        <v>3.255685675989008</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04138621098813653</v>
+      </c>
+      <c r="W69">
+        <v>0.228916972816033</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1655448439525461</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2428348126883935</v>
+      </c>
+      <c r="C70">
+        <v>-647.6593006693669</v>
+      </c>
+      <c r="D70">
+        <v>705.9086993306331</v>
+      </c>
+      <c r="E70">
+        <v>461.668</v>
+      </c>
+      <c r="F70">
+        <v>1394.068</v>
+      </c>
+      <c r="G70">
+        <v>40.5</v>
+      </c>
+      <c r="H70">
+        <v>1117.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>107.3</v>
+      </c>
+      <c r="K70">
+        <v>53</v>
+      </c>
+      <c r="L70">
+        <v>54.3</v>
+      </c>
+      <c r="M70">
+        <v>332.9034384</v>
+      </c>
+      <c r="N70">
+        <v>-278.6034384</v>
+      </c>
+      <c r="O70">
+        <v>-69.65085960000003</v>
+      </c>
+      <c r="P70">
+        <v>-208.9525788</v>
+      </c>
+      <c r="Q70">
+        <v>-155.9525788</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2721013778176604</v>
+      </c>
+      <c r="T70">
+        <v>3.357425853363665</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04077759023831099</v>
+      </c>
+      <c r="W70">
+        <v>0.2290623114510913</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1631103609532439</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2448348126883935</v>
+      </c>
+      <c r="C71">
+        <v>-675.0126251879253</v>
+      </c>
+      <c r="D71">
+        <v>699.0563748120746</v>
+      </c>
+      <c r="E71">
+        <v>482.169</v>
+      </c>
+      <c r="F71">
+        <v>1414.569</v>
+      </c>
+      <c r="G71">
+        <v>40.5</v>
+      </c>
+      <c r="H71">
+        <v>1117.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>107.3</v>
+      </c>
+      <c r="K71">
+        <v>53</v>
+      </c>
+      <c r="L71">
+        <v>54.3</v>
+      </c>
+      <c r="M71">
+        <v>337.7990772</v>
+      </c>
+      <c r="N71">
+        <v>-283.4990772</v>
+      </c>
+      <c r="O71">
+        <v>-70.87476930000003</v>
+      </c>
+      <c r="P71">
+        <v>-212.6243079</v>
+      </c>
+      <c r="Q71">
+        <v>-159.6243079</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2796272287150043</v>
+      </c>
+      <c r="T71">
+        <v>3.46572991314959</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04018661066963982</v>
+      </c>
+      <c r="W71">
+        <v>0.22920343737209</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1607464426785592</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2468348126883935</v>
+      </c>
+      <c r="C72">
+        <v>-702.2341962863712</v>
+      </c>
+      <c r="D72">
+        <v>692.3358037136289</v>
+      </c>
+      <c r="E72">
+        <v>502.6700000000002</v>
+      </c>
+      <c r="F72">
+        <v>1435.07</v>
+      </c>
+      <c r="G72">
+        <v>40.5</v>
+      </c>
+      <c r="H72">
+        <v>1117.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>107.3</v>
+      </c>
+      <c r="K72">
+        <v>53</v>
+      </c>
+      <c r="L72">
+        <v>54.3</v>
+      </c>
+      <c r="M72">
+        <v>342.6947160000001</v>
+      </c>
+      <c r="N72">
+        <v>-288.3947160000001</v>
+      </c>
+      <c r="O72">
+        <v>-72.09867900000005</v>
+      </c>
+      <c r="P72">
+        <v>-216.296037</v>
+      </c>
+      <c r="Q72">
+        <v>-163.296037</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2876548030055045</v>
+      </c>
+      <c r="T72">
+        <v>3.581254243587909</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.0396125162315021</v>
+      </c>
+      <c r="W72">
+        <v>0.2293405311239173</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1584500649260083</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2488348126883934</v>
+      </c>
+      <c r="C73">
+        <v>-729.3277777241992</v>
+      </c>
+      <c r="D73">
+        <v>685.7432222758007</v>
+      </c>
+      <c r="E73">
+        <v>523.1709999999999</v>
+      </c>
+      <c r="F73">
+        <v>1455.571</v>
+      </c>
+      <c r="G73">
+        <v>40.5</v>
+      </c>
+      <c r="H73">
+        <v>1117.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>107.3</v>
+      </c>
+      <c r="K73">
+        <v>53</v>
+      </c>
+      <c r="L73">
+        <v>54.3</v>
+      </c>
+      <c r="M73">
+        <v>347.5903548</v>
+      </c>
+      <c r="N73">
+        <v>-293.2903548</v>
+      </c>
+      <c r="O73">
+        <v>-73.32258870000003</v>
+      </c>
+      <c r="P73">
+        <v>-219.9677660999999</v>
+      </c>
+      <c r="Q73">
+        <v>-166.9677660999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2962360031091425</v>
+      </c>
+      <c r="T73">
+        <v>3.704745769228871</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03905459346767813</v>
+      </c>
+      <c r="W73">
+        <v>0.2294737630799185</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1562183738707125</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2508348126883935</v>
+      </c>
+      <c r="C74">
+        <v>-756.2969912555648</v>
+      </c>
+      <c r="D74">
+        <v>679.2750087444351</v>
+      </c>
+      <c r="E74">
+        <v>543.6719999999999</v>
+      </c>
+      <c r="F74">
+        <v>1476.072</v>
+      </c>
+      <c r="G74">
+        <v>40.5</v>
+      </c>
+      <c r="H74">
+        <v>1117.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>107.3</v>
+      </c>
+      <c r="K74">
+        <v>53</v>
+      </c>
+      <c r="L74">
+        <v>54.3</v>
+      </c>
+      <c r="M74">
+        <v>352.4859936</v>
+      </c>
+      <c r="N74">
+        <v>-298.1859936</v>
+      </c>
+      <c r="O74">
+        <v>-74.54649840000002</v>
+      </c>
+      <c r="P74">
+        <v>-223.6394951999999</v>
+      </c>
+      <c r="Q74">
+        <v>-170.6394951999999</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3054301460773262</v>
+      </c>
+      <c r="T74">
+        <v>3.837058118129902</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03851216855840483</v>
+      </c>
+      <c r="W74">
+        <v>0.229603294148253</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1540486742336193</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2528348126883934</v>
+      </c>
+      <c r="C75">
+        <v>-783.1453232639642</v>
+      </c>
+      <c r="D75">
+        <v>672.9276767360357</v>
+      </c>
+      <c r="E75">
+        <v>564.1729999999999</v>
+      </c>
+      <c r="F75">
+        <v>1496.573</v>
+      </c>
+      <c r="G75">
+        <v>40.5</v>
+      </c>
+      <c r="H75">
+        <v>1117.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>107.3</v>
+      </c>
+      <c r="K75">
+        <v>53</v>
+      </c>
+      <c r="L75">
+        <v>54.3</v>
+      </c>
+      <c r="M75">
+        <v>357.3816324</v>
+      </c>
+      <c r="N75">
+        <v>-303.0816324</v>
+      </c>
+      <c r="O75">
+        <v>-75.77040810000003</v>
+      </c>
+      <c r="P75">
+        <v>-227.3112243</v>
+      </c>
+      <c r="Q75">
+        <v>-174.3112243</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3153053366727827</v>
+      </c>
+      <c r="T75">
+        <v>3.979171381764342</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03798460460554996</v>
+      </c>
+      <c r="W75">
+        <v>0.2297292764201947</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1519384184221998</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2548348126883934</v>
+      </c>
+      <c r="C76">
+        <v>-809.8761310283882</v>
+      </c>
+      <c r="D76">
+        <v>666.6978689716117</v>
+      </c>
+      <c r="E76">
+        <v>584.6739999999999</v>
+      </c>
+      <c r="F76">
+        <v>1517.074</v>
+      </c>
+      <c r="G76">
+        <v>40.5</v>
+      </c>
+      <c r="H76">
+        <v>1117.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>107.3</v>
+      </c>
+      <c r="K76">
+        <v>53</v>
+      </c>
+      <c r="L76">
+        <v>54.3</v>
+      </c>
+      <c r="M76">
+        <v>362.2772712</v>
+      </c>
+      <c r="N76">
+        <v>-307.9772712</v>
+      </c>
+      <c r="O76">
+        <v>-76.99431780000002</v>
+      </c>
+      <c r="P76">
+        <v>-230.9829533999999</v>
+      </c>
+      <c r="Q76">
+        <v>-177.9829533999999</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3259401573140435</v>
+      </c>
+      <c r="T76">
+        <v>4.132216434909125</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.0374712991379074</v>
+      </c>
+      <c r="W76">
+        <v>0.2298518537658677</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1498851965516296</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2568348126883935</v>
+      </c>
+      <c r="C77">
+        <v>-836.4926486445999</v>
+      </c>
+      <c r="D77">
+        <v>660.5823513554</v>
+      </c>
+      <c r="E77">
+        <v>605.1749999999998</v>
+      </c>
+      <c r="F77">
+        <v>1537.575</v>
+      </c>
+      <c r="G77">
+        <v>40.5</v>
+      </c>
+      <c r="H77">
+        <v>1117.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>107.3</v>
+      </c>
+      <c r="K77">
+        <v>53</v>
+      </c>
+      <c r="L77">
+        <v>54.3</v>
+      </c>
+      <c r="M77">
+        <v>367.17291</v>
+      </c>
+      <c r="N77">
+        <v>-312.87291</v>
+      </c>
+      <c r="O77">
+        <v>-78.21822750000003</v>
+      </c>
+      <c r="P77">
+        <v>-234.6546825</v>
+      </c>
+      <c r="Q77">
+        <v>-181.6546825</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3374257636066053</v>
+      </c>
+      <c r="T77">
+        <v>4.29750509230549</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03697168181606863</v>
+      </c>
+      <c r="W77">
+        <v>0.2299711623823228</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1478867272642745</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2588348126883934</v>
+      </c>
+      <c r="C78">
+        <v>-862.9979926234856</v>
+      </c>
+      <c r="D78">
+        <v>654.5780073765144</v>
+      </c>
+      <c r="E78">
+        <v>625.676</v>
+      </c>
+      <c r="F78">
+        <v>1558.076</v>
+      </c>
+      <c r="G78">
+        <v>40.5</v>
+      </c>
+      <c r="H78">
+        <v>1117.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>107.3</v>
+      </c>
+      <c r="K78">
+        <v>53</v>
+      </c>
+      <c r="L78">
+        <v>54.3</v>
+      </c>
+      <c r="M78">
+        <v>372.0685488</v>
+      </c>
+      <c r="N78">
+        <v>-317.7685488</v>
+      </c>
+      <c r="O78">
+        <v>-79.44213720000003</v>
+      </c>
+      <c r="P78">
+        <v>-238.3264116</v>
+      </c>
+      <c r="Q78">
+        <v>-185.3264116</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3498685037568804</v>
+      </c>
+      <c r="T78">
+        <v>4.476567804484885</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03648521231848878</v>
+      </c>
+      <c r="W78">
+        <v>0.2300873312983449</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1459408492739551</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2608348126883935</v>
+      </c>
+      <c r="C79">
+        <v>-889.3951671868427</v>
+      </c>
+      <c r="D79">
+        <v>648.6818328131573</v>
+      </c>
+      <c r="E79">
+        <v>646.177</v>
+      </c>
+      <c r="F79">
+        <v>1578.577</v>
+      </c>
+      <c r="G79">
+        <v>40.5</v>
+      </c>
+      <c r="H79">
+        <v>1117.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>107.3</v>
+      </c>
+      <c r="K79">
+        <v>53</v>
+      </c>
+      <c r="L79">
+        <v>54.3</v>
+      </c>
+      <c r="M79">
+        <v>376.9641876</v>
+      </c>
+      <c r="N79">
+        <v>-322.6641876</v>
+      </c>
+      <c r="O79">
+        <v>-80.66604690000004</v>
+      </c>
+      <c r="P79">
+        <v>-241.9981407</v>
+      </c>
+      <c r="Q79">
+        <v>-188.9981407</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3633932213115275</v>
+      </c>
+      <c r="T79">
+        <v>4.671201187288577</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03601137839227464</v>
+      </c>
+      <c r="W79">
+        <v>0.2302004828399248</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1440455135690986</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2628348126883934</v>
+      </c>
+      <c r="C80">
+        <v>-915.6870692795044</v>
+      </c>
+      <c r="D80">
+        <v>642.8909307204956</v>
+      </c>
+      <c r="E80">
+        <v>666.678</v>
+      </c>
+      <c r="F80">
+        <v>1599.078</v>
+      </c>
+      <c r="G80">
+        <v>40.5</v>
+      </c>
+      <c r="H80">
+        <v>1117.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>107.3</v>
+      </c>
+      <c r="K80">
+        <v>53</v>
+      </c>
+      <c r="L80">
+        <v>54.3</v>
+      </c>
+      <c r="M80">
+        <v>381.8598264</v>
+      </c>
+      <c r="N80">
+        <v>-327.5598264</v>
+      </c>
+      <c r="O80">
+        <v>-81.88995660000005</v>
+      </c>
+      <c r="P80">
+        <v>-245.6698698</v>
+      </c>
+      <c r="Q80">
+        <v>-192.6698698</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3781474586438697</v>
+      </c>
+      <c r="T80">
+        <v>4.883528513983512</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03554969405391215</v>
+      </c>
+      <c r="W80">
+        <v>0.2303107330599258</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1421987762156486</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2648348126883935</v>
+      </c>
+      <c r="C81">
+        <v>-941.8764933153786</v>
+      </c>
+      <c r="D81">
+        <v>637.2025066846213</v>
+      </c>
+      <c r="E81">
+        <v>687.179</v>
+      </c>
+      <c r="F81">
+        <v>1619.579</v>
+      </c>
+      <c r="G81">
+        <v>40.5</v>
+      </c>
+      <c r="H81">
+        <v>1117.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>107.3</v>
+      </c>
+      <c r="K81">
+        <v>53</v>
+      </c>
+      <c r="L81">
+        <v>54.3</v>
+      </c>
+      <c r="M81">
+        <v>386.7554652</v>
+      </c>
+      <c r="N81">
+        <v>-332.4554652</v>
+      </c>
+      <c r="O81">
+        <v>-83.11386630000004</v>
+      </c>
+      <c r="P81">
+        <v>-249.3415989</v>
+      </c>
+      <c r="Q81">
+        <v>-196.3415989</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3943068614364349</v>
+      </c>
+      <c r="T81">
+        <v>5.11607749083987</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03509969792664744</v>
+      </c>
+      <c r="W81">
+        <v>0.2304181921351166</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1403987917065898</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2668348126883935</v>
+      </c>
+      <c r="C82">
+        <v>-967.9661356737309</v>
+      </c>
+      <c r="D82">
+        <v>631.613864326269</v>
+      </c>
+      <c r="E82">
+        <v>707.6799999999999</v>
+      </c>
+      <c r="F82">
+        <v>1640.08</v>
+      </c>
+      <c r="G82">
+        <v>40.5</v>
+      </c>
+      <c r="H82">
+        <v>1117.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>107.3</v>
+      </c>
+      <c r="K82">
+        <v>53</v>
+      </c>
+      <c r="L82">
+        <v>54.3</v>
+      </c>
+      <c r="M82">
+        <v>391.651104</v>
+      </c>
+      <c r="N82">
+        <v>-337.351104</v>
+      </c>
+      <c r="O82">
+        <v>-84.33777600000003</v>
+      </c>
+      <c r="P82">
+        <v>-253.0133279999999</v>
+      </c>
+      <c r="Q82">
+        <v>-200.0133279999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4120822045082567</v>
+      </c>
+      <c r="T82">
+        <v>5.371881365381864</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03466095170256434</v>
+      </c>
+      <c r="W82">
+        <v>0.2305229647334276</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1386438068102573</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2688348126883934</v>
+      </c>
+      <c r="C83">
+        <v>-993.9585989609147</v>
+      </c>
+      <c r="D83">
+        <v>626.1224010390854</v>
+      </c>
+      <c r="E83">
+        <v>728.1810000000002</v>
+      </c>
+      <c r="F83">
+        <v>1660.581</v>
+      </c>
+      <c r="G83">
+        <v>40.5</v>
+      </c>
+      <c r="H83">
+        <v>1117.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>107.3</v>
+      </c>
+      <c r="K83">
+        <v>53</v>
+      </c>
+      <c r="L83">
+        <v>54.3</v>
+      </c>
+      <c r="M83">
+        <v>396.5467428000001</v>
+      </c>
+      <c r="N83">
+        <v>-342.2467428</v>
+      </c>
+      <c r="O83">
+        <v>-85.56168570000006</v>
+      </c>
+      <c r="P83">
+        <v>-256.6850571</v>
+      </c>
+      <c r="Q83">
+        <v>-203.6850571</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4317286363244807</v>
+      </c>
+      <c r="T83">
+        <v>5.654611963559857</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03423303871858206</v>
+      </c>
+      <c r="W83">
+        <v>0.2306251503540026</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1369321548743282</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2708348126883934</v>
+      </c>
+      <c r="C84">
+        <v>-1019.856396051702</v>
+      </c>
+      <c r="D84">
+        <v>620.7256039482977</v>
+      </c>
+      <c r="E84">
+        <v>748.6820000000001</v>
+      </c>
+      <c r="F84">
+        <v>1681.082</v>
+      </c>
+      <c r="G84">
+        <v>40.5</v>
+      </c>
+      <c r="H84">
+        <v>1117.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>107.3</v>
+      </c>
+      <c r="K84">
+        <v>53</v>
+      </c>
+      <c r="L84">
+        <v>54.3</v>
+      </c>
+      <c r="M84">
+        <v>401.4423816</v>
+      </c>
+      <c r="N84">
+        <v>-347.1423816</v>
+      </c>
+      <c r="O84">
+        <v>-86.78559540000005</v>
+      </c>
+      <c r="P84">
+        <v>-260.3567862</v>
+      </c>
+      <c r="Q84">
+        <v>-207.3567862</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4535580050091741</v>
+      </c>
+      <c r="T84">
+        <v>5.968757072646516</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.03381556263664814</v>
+      </c>
+      <c r="W84">
+        <v>0.2307248436423684</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1352622505465926</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2728348126883935</v>
+      </c>
+      <c r="C85">
+        <v>-1045.661953923396</v>
+      </c>
+      <c r="D85">
+        <v>615.4210460766037</v>
+      </c>
+      <c r="E85">
+        <v>769.1830000000001</v>
+      </c>
+      <c r="F85">
+        <v>1701.583</v>
+      </c>
+      <c r="G85">
+        <v>40.5</v>
+      </c>
+      <c r="H85">
+        <v>1117.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>107.3</v>
+      </c>
+      <c r="K85">
+        <v>53</v>
+      </c>
+      <c r="L85">
+        <v>54.3</v>
+      </c>
+      <c r="M85">
+        <v>406.3380204000001</v>
+      </c>
+      <c r="N85">
+        <v>-352.0380204000001</v>
+      </c>
+      <c r="O85">
+        <v>-88.00950510000006</v>
+      </c>
+      <c r="P85">
+        <v>-264.0285153</v>
+      </c>
+      <c r="Q85">
+        <v>-211.0285153</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4779555347155962</v>
+      </c>
+      <c r="T85">
+        <v>6.319860429861018</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03340814621933912</v>
+      </c>
+      <c r="W85">
+        <v>0.2308221346828218</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1336325848773565</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2748348126883934</v>
+      </c>
+      <c r="C86">
+        <v>-1071.377617295015</v>
+      </c>
+      <c r="D86">
+        <v>610.2063827049847</v>
+      </c>
+      <c r="E86">
+        <v>789.6839999999999</v>
+      </c>
+      <c r="F86">
+        <v>1722.084</v>
+      </c>
+      <c r="G86">
+        <v>40.5</v>
+      </c>
+      <c r="H86">
+        <v>1117.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>107.3</v>
+      </c>
+      <c r="K86">
+        <v>53</v>
+      </c>
+      <c r="L86">
+        <v>54.3</v>
+      </c>
+      <c r="M86">
+        <v>411.2336592</v>
+      </c>
+      <c r="N86">
+        <v>-356.9336592</v>
+      </c>
+      <c r="O86">
+        <v>-89.23341480000003</v>
+      </c>
+      <c r="P86">
+        <v>-267.7002443999999</v>
+      </c>
+      <c r="Q86">
+        <v>-214.7002443999999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5054027556353207</v>
+      </c>
+      <c r="T86">
+        <v>6.714851706727328</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03301043019291842</v>
+      </c>
+      <c r="W86">
+        <v>0.2309171092699311</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1320417207716736</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2768348126883934</v>
+      </c>
+      <c r="C87">
+        <v>-1097.005652083022</v>
+      </c>
+      <c r="D87">
+        <v>605.0793479169782</v>
+      </c>
+      <c r="E87">
+        <v>810.1849999999998</v>
+      </c>
+      <c r="F87">
+        <v>1742.585</v>
+      </c>
+      <c r="G87">
+        <v>40.5</v>
+      </c>
+      <c r="H87">
+        <v>1117.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>107.3</v>
+      </c>
+      <c r="K87">
+        <v>53</v>
+      </c>
+      <c r="L87">
+        <v>54.3</v>
+      </c>
+      <c r="M87">
+        <v>416.1292979999999</v>
+      </c>
+      <c r="N87">
+        <v>-361.8292979999999</v>
+      </c>
+      <c r="O87">
+        <v>-90.45732450000003</v>
+      </c>
+      <c r="P87">
+        <v>-271.3719734999999</v>
+      </c>
+      <c r="Q87">
+        <v>-218.3719734999999</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5365096060110088</v>
+      </c>
+      <c r="T87">
+        <v>7.162508487175817</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.0326220721906488</v>
+      </c>
+      <c r="W87">
+        <v>0.2310098491608731</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1304882887625952</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2788348126883934</v>
+      </c>
+      <c r="C88">
+        <v>-1122.548248684282</v>
+      </c>
+      <c r="D88">
+        <v>600.037751315718</v>
+      </c>
+      <c r="E88">
+        <v>830.6859999999998</v>
+      </c>
+      <c r="F88">
+        <v>1763.086</v>
+      </c>
+      <c r="G88">
+        <v>40.5</v>
+      </c>
+      <c r="H88">
+        <v>1117.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>107.3</v>
+      </c>
+      <c r="K88">
+        <v>53</v>
+      </c>
+      <c r="L88">
+        <v>54.3</v>
+      </c>
+      <c r="M88">
+        <v>421.0249368</v>
+      </c>
+      <c r="N88">
+        <v>-366.7249368</v>
+      </c>
+      <c r="O88">
+        <v>-91.68123420000003</v>
+      </c>
+      <c r="P88">
+        <v>-275.0437026</v>
+      </c>
+      <c r="Q88">
+        <v>-222.0437026</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5720602921546523</v>
+      </c>
+      <c r="T88">
+        <v>7.674116236259803</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.0322427457698273</v>
+      </c>
+      <c r="W88">
+        <v>0.2311004323101652</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1289709830793092</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2808348126883934</v>
+      </c>
+      <c r="C89">
+        <v>-1148.007525096264</v>
+      </c>
+      <c r="D89">
+        <v>595.0794749037358</v>
+      </c>
+      <c r="E89">
+        <v>851.187</v>
+      </c>
+      <c r="F89">
+        <v>1783.587</v>
+      </c>
+      <c r="G89">
+        <v>40.5</v>
+      </c>
+      <c r="H89">
+        <v>1117.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>107.3</v>
+      </c>
+      <c r="K89">
+        <v>53</v>
+      </c>
+      <c r="L89">
+        <v>54.3</v>
+      </c>
+      <c r="M89">
+        <v>425.9205756</v>
+      </c>
+      <c r="N89">
+        <v>-371.6205756</v>
+      </c>
+      <c r="O89">
+        <v>-92.90514390000004</v>
+      </c>
+      <c r="P89">
+        <v>-278.7154317</v>
+      </c>
+      <c r="Q89">
+        <v>-225.7154317</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.613080314628087</v>
+      </c>
+      <c r="T89">
+        <v>8.264432869818251</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.03187213949661089</v>
+      </c>
+      <c r="W89">
+        <v>0.2311889330882093</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1274885579864435</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2828348126883934</v>
+      </c>
+      <c r="C90">
+        <v>-1173.385529883803</v>
+      </c>
+      <c r="D90">
+        <v>590.2024701161967</v>
+      </c>
+      <c r="E90">
+        <v>871.688</v>
+      </c>
+      <c r="F90">
+        <v>1804.088</v>
+      </c>
+      <c r="G90">
+        <v>40.5</v>
+      </c>
+      <c r="H90">
+        <v>1117.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>107.3</v>
+      </c>
+      <c r="K90">
+        <v>53</v>
+      </c>
+      <c r="L90">
+        <v>54.3</v>
+      </c>
+      <c r="M90">
+        <v>430.8162144</v>
+      </c>
+      <c r="N90">
+        <v>-376.5162144</v>
+      </c>
+      <c r="O90">
+        <v>-94.12905360000005</v>
+      </c>
+      <c r="P90">
+        <v>-282.3871607999999</v>
+      </c>
+      <c r="Q90">
+        <v>-229.3871607999999</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6609370075137608</v>
+      </c>
+      <c r="T90">
+        <v>8.95313560896977</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03150995609324031</v>
+      </c>
+      <c r="W90">
+        <v>0.2312754224849342</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1260398243729612</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2848348126883934</v>
+      </c>
+      <c r="C91">
+        <v>-1198.684245001165</v>
+      </c>
+      <c r="D91">
+        <v>585.4047549988347</v>
+      </c>
+      <c r="E91">
+        <v>892.189</v>
+      </c>
+      <c r="F91">
+        <v>1824.589</v>
+      </c>
+      <c r="G91">
+        <v>40.5</v>
+      </c>
+      <c r="H91">
+        <v>1117.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>107.3</v>
+      </c>
+      <c r="K91">
+        <v>53</v>
+      </c>
+      <c r="L91">
+        <v>54.3</v>
+      </c>
+      <c r="M91">
+        <v>435.7118532</v>
+      </c>
+      <c r="N91">
+        <v>-381.4118532</v>
+      </c>
+      <c r="O91">
+        <v>-95.35296330000004</v>
+      </c>
+      <c r="P91">
+        <v>-286.0588898999999</v>
+      </c>
+      <c r="Q91">
+        <v>-233.0588898999999</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7174949172877394</v>
+      </c>
+      <c r="T91">
+        <v>9.767057027967025</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03115591164275447</v>
+      </c>
+      <c r="W91">
+        <v>0.2313599682997103</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1246236465710179</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2868348126883934</v>
+      </c>
+      <c r="C92">
+        <v>-1223.905588477581</v>
+      </c>
+      <c r="D92">
+        <v>580.6844115224189</v>
+      </c>
+      <c r="E92">
+        <v>912.6899999999999</v>
+      </c>
+      <c r="F92">
+        <v>1845.09</v>
+      </c>
+      <c r="G92">
+        <v>40.5</v>
+      </c>
+      <c r="H92">
+        <v>1117.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>107.3</v>
+      </c>
+      <c r="K92">
+        <v>53</v>
+      </c>
+      <c r="L92">
+        <v>54.3</v>
+      </c>
+      <c r="M92">
+        <v>440.607492</v>
+      </c>
+      <c r="N92">
+        <v>-386.307492</v>
+      </c>
+      <c r="O92">
+        <v>-96.57687300000003</v>
+      </c>
+      <c r="P92">
+        <v>-289.7306189999999</v>
+      </c>
+      <c r="Q92">
+        <v>-236.7306189999999</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7853644090165133</v>
+      </c>
+      <c r="T92">
+        <v>10.74376273076373</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03080973484672386</v>
+      </c>
+      <c r="W92">
+        <v>0.2314426353186023</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.1232389393868955</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2888348126883934</v>
+      </c>
+      <c r="C93">
+        <v>-1249.051416973892</v>
+      </c>
+      <c r="D93">
+        <v>576.0395830261079</v>
+      </c>
+      <c r="E93">
+        <v>933.1909999999999</v>
+      </c>
+      <c r="F93">
+        <v>1865.591</v>
+      </c>
+      <c r="G93">
+        <v>40.5</v>
+      </c>
+      <c r="H93">
+        <v>1117.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>107.3</v>
+      </c>
+      <c r="K93">
+        <v>53</v>
+      </c>
+      <c r="L93">
+        <v>54.3</v>
+      </c>
+      <c r="M93">
+        <v>445.5031308</v>
+      </c>
+      <c r="N93">
+        <v>-391.2031308</v>
+      </c>
+      <c r="O93">
+        <v>-97.80078270000004</v>
+      </c>
+      <c r="P93">
+        <v>-293.4023480999999</v>
+      </c>
+      <c r="Q93">
+        <v>-240.4023480999999</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8683160100183482</v>
+      </c>
+      <c r="T93">
+        <v>11.93751414529303</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.0304711663319247</v>
+      </c>
+      <c r="W93">
+        <v>0.2315234854799364</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1218846653276988</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2908348126883934</v>
+      </c>
+      <c r="C94">
+        <v>-1274.123528217467</v>
+      </c>
+      <c r="D94">
+        <v>571.468471782533</v>
+      </c>
+      <c r="E94">
+        <v>953.6920000000001</v>
+      </c>
+      <c r="F94">
+        <v>1886.092</v>
+      </c>
+      <c r="G94">
+        <v>40.5</v>
+      </c>
+      <c r="H94">
+        <v>1117.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>107.3</v>
+      </c>
+      <c r="K94">
+        <v>53</v>
+      </c>
+      <c r="L94">
+        <v>54.3</v>
+      </c>
+      <c r="M94">
+        <v>450.3987696</v>
+      </c>
+      <c r="N94">
+        <v>-396.0987696</v>
+      </c>
+      <c r="O94">
+        <v>-99.02469240000005</v>
+      </c>
+      <c r="P94">
+        <v>-297.0740772</v>
+      </c>
+      <c r="Q94">
+        <v>-244.0740772</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9720055112706421</v>
+      </c>
+      <c r="T94">
+        <v>13.42970341345466</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03013995800222986</v>
+      </c>
+      <c r="W94">
+        <v>0.2316025780290675</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1205598320089194</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2928348126883935</v>
+      </c>
+      <c r="C95">
+        <v>-1299.123663322099</v>
+      </c>
+      <c r="D95">
+        <v>566.9693366779006</v>
+      </c>
+      <c r="E95">
+        <v>974.1930000000001</v>
+      </c>
+      <c r="F95">
+        <v>1906.593</v>
+      </c>
+      <c r="G95">
+        <v>40.5</v>
+      </c>
+      <c r="H95">
+        <v>1117.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>107.3</v>
+      </c>
+      <c r="K95">
+        <v>53</v>
+      </c>
+      <c r="L95">
+        <v>54.3</v>
+      </c>
+      <c r="M95">
+        <v>455.2944084000001</v>
+      </c>
+      <c r="N95">
+        <v>-400.9944084000001</v>
+      </c>
+      <c r="O95">
+        <v>-100.2486021000001</v>
+      </c>
+      <c r="P95">
+        <v>-300.7458063</v>
+      </c>
+      <c r="Q95">
+        <v>-247.7458063</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.105320584309305</v>
+      </c>
+      <c r="T95">
+        <v>15.34823247251962</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02981587243231341</v>
+      </c>
+      <c r="W95">
+        <v>0.2316799696631636</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1192634897292536</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2948348126883934</v>
+      </c>
+      <c r="C96">
+        <v>-1324.053508999175</v>
+      </c>
+      <c r="D96">
+        <v>562.5404910008253</v>
+      </c>
+      <c r="E96">
+        <v>994.6940000000001</v>
+      </c>
+      <c r="F96">
+        <v>1927.094</v>
+      </c>
+      <c r="G96">
+        <v>40.5</v>
+      </c>
+      <c r="H96">
+        <v>1117.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>107.3</v>
+      </c>
+      <c r="K96">
+        <v>53</v>
+      </c>
+      <c r="L96">
+        <v>54.3</v>
+      </c>
+      <c r="M96">
+        <v>460.1900472</v>
+      </c>
+      <c r="N96">
+        <v>-405.8900472</v>
+      </c>
+      <c r="O96">
+        <v>-101.4725118</v>
+      </c>
+      <c r="P96">
+        <v>-304.4175354</v>
+      </c>
+      <c r="Q96">
+        <v>-251.4175354</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.283074015027523</v>
+      </c>
+      <c r="T96">
+        <v>17.90627121793956</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02949868230005476</v>
+      </c>
+      <c r="W96">
+        <v>0.2317557146667469</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.117994729200219</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2968348126883935</v>
+      </c>
+      <c r="C97">
+        <v>-1348.914699666007</v>
+      </c>
+      <c r="D97">
+        <v>558.1803003339933</v>
+      </c>
+      <c r="E97">
+        <v>1015.195</v>
+      </c>
+      <c r="F97">
+        <v>1947.595</v>
+      </c>
+      <c r="G97">
+        <v>40.5</v>
+      </c>
+      <c r="H97">
+        <v>1117.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>107.3</v>
+      </c>
+      <c r="K97">
+        <v>53</v>
+      </c>
+      <c r="L97">
+        <v>54.3</v>
+      </c>
+      <c r="M97">
+        <v>465.085686</v>
+      </c>
+      <c r="N97">
+        <v>-410.785686</v>
+      </c>
+      <c r="O97">
+        <v>-102.6964215</v>
+      </c>
+      <c r="P97">
+        <v>-308.0892645</v>
+      </c>
+      <c r="Q97">
+        <v>-255.0892645</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.531928818033029</v>
+      </c>
+      <c r="T97">
+        <v>21.48752546152748</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02918816985479103</v>
+      </c>
+      <c r="W97">
+        <v>0.2318298650386759</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1167526794191641</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2988348126883934</v>
+      </c>
+      <c r="C98">
+        <v>-1373.708819456877</v>
+      </c>
+      <c r="D98">
+        <v>553.8871805431223</v>
+      </c>
+      <c r="E98">
+        <v>1035.696</v>
+      </c>
+      <c r="F98">
+        <v>1968.096</v>
+      </c>
+      <c r="G98">
+        <v>40.5</v>
+      </c>
+      <c r="H98">
+        <v>1117.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>107.3</v>
+      </c>
+      <c r="K98">
+        <v>53</v>
+      </c>
+      <c r="L98">
+        <v>54.3</v>
+      </c>
+      <c r="M98">
+        <v>469.9813248</v>
+      </c>
+      <c r="N98">
+        <v>-415.6813248</v>
+      </c>
+      <c r="O98">
+        <v>-103.9203312</v>
+      </c>
+      <c r="P98">
+        <v>-311.7609935999999</v>
+      </c>
+      <c r="Q98">
+        <v>-258.7609935999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.905211022541281</v>
+      </c>
+      <c r="T98">
+        <v>26.85940682690929</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02888412641880362</v>
+      </c>
+      <c r="W98">
+        <v>0.2319024706111897</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1155365056752145</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3008348126883935</v>
+      </c>
+      <c r="C99">
+        <v>-1398.437404141984</v>
+      </c>
+      <c r="D99">
+        <v>549.6595958580157</v>
+      </c>
+      <c r="E99">
+        <v>1056.197</v>
+      </c>
+      <c r="F99">
+        <v>1988.597</v>
+      </c>
+      <c r="G99">
+        <v>40.5</v>
+      </c>
+      <c r="H99">
+        <v>1117.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>107.3</v>
+      </c>
+      <c r="K99">
+        <v>53</v>
+      </c>
+      <c r="L99">
+        <v>54.3</v>
+      </c>
+      <c r="M99">
+        <v>474.8769636</v>
+      </c>
+      <c r="N99">
+        <v>-420.5769635999999</v>
+      </c>
+      <c r="O99">
+        <v>-105.1442409</v>
+      </c>
+      <c r="P99">
+        <v>-315.4327226999999</v>
+      </c>
+      <c r="Q99">
+        <v>-262.4327226999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.527348030055042</v>
+      </c>
+      <c r="T99">
+        <v>35.81254243587906</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.0285863519196407</v>
+      </c>
+      <c r="W99">
+        <v>0.2319735791615898</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1143454076785628</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3028348126883935</v>
+      </c>
+      <c r="C100">
+        <v>-1423.101942959168</v>
+      </c>
+      <c r="D100">
+        <v>545.4960570408315</v>
+      </c>
+      <c r="E100">
+        <v>1076.698</v>
+      </c>
+      <c r="F100">
+        <v>2009.098</v>
+      </c>
+      <c r="G100">
+        <v>40.5</v>
+      </c>
+      <c r="H100">
+        <v>1117.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>107.3</v>
+      </c>
+      <c r="K100">
+        <v>53</v>
+      </c>
+      <c r="L100">
+        <v>54.3</v>
+      </c>
+      <c r="M100">
+        <v>479.7726024</v>
+      </c>
+      <c r="N100">
+        <v>-425.4726024</v>
+      </c>
+      <c r="O100">
+        <v>-106.3681506</v>
+      </c>
+      <c r="P100">
+        <v>-319.1044518</v>
+      </c>
+      <c r="Q100">
+        <v>-266.1044518</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.771622045082563</v>
+      </c>
+      <c r="T100">
+        <v>53.71881365381859</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02829465445107293</v>
+      </c>
+      <c r="W100">
+        <v>0.2320432365170838</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1131786178042917</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3048348126883934</v>
+      </c>
+      <c r="C101">
+        <v>-1447.703880363024</v>
+      </c>
+      <c r="D101">
+        <v>541.3951196369757</v>
+      </c>
+      <c r="E101">
+        <v>1097.199</v>
+      </c>
+      <c r="F101">
+        <v>2029.599</v>
+      </c>
+      <c r="G101">
+        <v>40.5</v>
+      </c>
+      <c r="H101">
+        <v>1117.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>107.3</v>
+      </c>
+      <c r="K101">
+        <v>53</v>
+      </c>
+      <c r="L101">
+        <v>54.3</v>
+      </c>
+      <c r="M101">
+        <v>484.6682412</v>
+      </c>
+      <c r="N101">
+        <v>-430.3682412</v>
+      </c>
+      <c r="O101">
+        <v>-107.5920603</v>
+      </c>
+      <c r="P101">
+        <v>-322.7761809</v>
+      </c>
+      <c r="Q101">
+        <v>-269.7761809</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.504444090165125</v>
+      </c>
+      <c r="T101">
+        <v>107.4376273076372</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02800884986065806</v>
+      </c>
+      <c r="W101">
+        <v>0.2321114866532749</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1120353994426322</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_entertainment.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_entertainment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09800190222331298</v>
+        <v>0.09779064746775469</v>
       </c>
       <c r="C2">
-        <v>1698.41614184752</v>
+        <v>1685.643375198368</v>
       </c>
       <c r="D2">
-        <v>1648.21614184752</v>
+        <v>1654.913375198368</v>
       </c>
       <c r="E2">
-        <v>-856.7</v>
+        <v>-837.23</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>19.47</v>
       </c>
       <c r="G2">
         <v>50.2</v>
@@ -1451,28 +1451,28 @@
         <v>115.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.9793409999999999</v>
       </c>
       <c r="N2">
-        <v>115.75</v>
+        <v>114.770659</v>
       </c>
       <c r="O2">
-        <v>28.9375</v>
+        <v>28.69266475</v>
       </c>
       <c r="P2">
-        <v>86.8125</v>
+        <v>86.07799424999999</v>
       </c>
       <c r="Q2">
-        <v>144.8125</v>
+        <v>144.07799425</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09800190222331298</v>
+        <v>0.09839737117955019</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.025220663724927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.1917228013532</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09779064746775469</v>
+        <v>0.09757939271219641</v>
       </c>
       <c r="C3">
-        <v>1685.643375198368</v>
+        <v>1672.925256636817</v>
       </c>
       <c r="D3">
-        <v>1654.913375198368</v>
+        <v>1661.665256636817</v>
       </c>
       <c r="E3">
-        <v>-837.23</v>
+        <v>-817.76</v>
       </c>
       <c r="F3">
-        <v>19.47</v>
+        <v>38.94</v>
       </c>
       <c r="G3">
         <v>50.2</v>
@@ -1533,28 +1533,28 @@
         <v>115.75</v>
       </c>
       <c r="M3">
-        <v>0.9793409999999999</v>
+        <v>1.958682</v>
       </c>
       <c r="N3">
-        <v>114.770659</v>
+        <v>113.791318</v>
       </c>
       <c r="O3">
-        <v>28.69266475</v>
+        <v>28.4478295</v>
       </c>
       <c r="P3">
-        <v>86.07799424999999</v>
+        <v>85.34348850000001</v>
       </c>
       <c r="Q3">
-        <v>144.07799425</v>
+        <v>143.3434885</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09839737117955019</v>
+        <v>0.09880091093081267</v>
       </c>
       <c r="T3">
-        <v>1.025220663724927</v>
+        <v>1.033086404585177</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.1917228013532</v>
+        <v>59.09586140067658</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09757939271219641</v>
+        <v>0.09736813795663811</v>
       </c>
       <c r="C4">
-        <v>1672.925256636817</v>
+        <v>1660.26245777923</v>
       </c>
       <c r="D4">
-        <v>1661.665256636817</v>
+        <v>1668.47245777923</v>
       </c>
       <c r="E4">
-        <v>-817.76</v>
+        <v>-798.2900000000001</v>
       </c>
       <c r="F4">
-        <v>38.94</v>
+        <v>58.41</v>
       </c>
       <c r="G4">
         <v>50.2</v>
@@ -1615,28 +1615,28 @@
         <v>115.75</v>
       </c>
       <c r="M4">
-        <v>1.958682</v>
+        <v>2.938023</v>
       </c>
       <c r="N4">
-        <v>113.791318</v>
+        <v>112.811977</v>
       </c>
       <c r="O4">
-        <v>28.4478295</v>
+        <v>28.20299425</v>
       </c>
       <c r="P4">
-        <v>85.34348850000001</v>
+        <v>84.60898275</v>
       </c>
       <c r="Q4">
-        <v>143.3434885</v>
+        <v>142.60898275</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09880091093081267</v>
+        <v>0.09921277108931764</v>
       </c>
       <c r="T4">
-        <v>1.033086404585177</v>
+        <v>1.041114325669349</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.09586140067658</v>
+        <v>39.39724093378439</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09736813795663811</v>
+        <v>0.09715688320107983</v>
       </c>
       <c r="C5">
-        <v>1660.26245777923</v>
+        <v>1647.655661292648</v>
       </c>
       <c r="D5">
-        <v>1668.47245777923</v>
+        <v>1675.335661292648</v>
       </c>
       <c r="E5">
-        <v>-798.2900000000001</v>
+        <v>-778.8200000000001</v>
       </c>
       <c r="F5">
-        <v>58.41</v>
+        <v>77.88</v>
       </c>
       <c r="G5">
         <v>50.2</v>
@@ -1697,28 +1697,28 @@
         <v>115.75</v>
       </c>
       <c r="M5">
-        <v>2.938023</v>
+        <v>3.917364</v>
       </c>
       <c r="N5">
-        <v>112.811977</v>
+        <v>111.832636</v>
       </c>
       <c r="O5">
-        <v>28.20299425</v>
+        <v>27.958159</v>
       </c>
       <c r="P5">
-        <v>84.60898275</v>
+        <v>83.874477</v>
       </c>
       <c r="Q5">
-        <v>142.60898275</v>
+        <v>141.874477</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09921277108931764</v>
+        <v>0.0996332116677915</v>
       </c>
       <c r="T5">
-        <v>1.041114325669349</v>
+        <v>1.049309495109441</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.39724093378439</v>
+        <v>29.54793070033829</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09715688320107983</v>
+        <v>0.09694562844552157</v>
       </c>
       <c r="C6">
-        <v>1647.655661292648</v>
+        <v>1635.10556112302</v>
       </c>
       <c r="D6">
-        <v>1675.335661292648</v>
+        <v>1682.25556112302</v>
       </c>
       <c r="E6">
-        <v>-778.8200000000001</v>
+        <v>-759.35</v>
       </c>
       <c r="F6">
-        <v>77.88</v>
+        <v>97.35000000000001</v>
       </c>
       <c r="G6">
         <v>50.2</v>
@@ -1779,28 +1779,28 @@
         <v>115.75</v>
       </c>
       <c r="M6">
-        <v>3.917364</v>
+        <v>4.896705</v>
       </c>
       <c r="N6">
-        <v>111.832636</v>
+        <v>110.853295</v>
       </c>
       <c r="O6">
-        <v>27.958159</v>
+        <v>27.71332375</v>
       </c>
       <c r="P6">
-        <v>83.874477</v>
+        <v>83.13997125</v>
       </c>
       <c r="Q6">
-        <v>141.874477</v>
+        <v>141.13997125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0996332116677915</v>
+        <v>0.1000625036268648</v>
       </c>
       <c r="T6">
-        <v>1.049309495109441</v>
+        <v>1.057677194432483</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.54793070033829</v>
+        <v>23.63834456027063</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09694562844552157</v>
+        <v>0.09673437368996327</v>
       </c>
       <c r="C7">
-        <v>1635.10556112302</v>
+        <v>1622.6128627291</v>
       </c>
       <c r="D7">
-        <v>1682.25556112302</v>
+        <v>1689.2328627291</v>
       </c>
       <c r="E7">
-        <v>-759.35</v>
+        <v>-739.88</v>
       </c>
       <c r="F7">
-        <v>97.35000000000001</v>
+        <v>116.82</v>
       </c>
       <c r="G7">
         <v>50.2</v>
@@ -1861,28 +1861,28 @@
         <v>115.75</v>
       </c>
       <c r="M7">
-        <v>4.896705</v>
+        <v>5.876046</v>
       </c>
       <c r="N7">
-        <v>110.853295</v>
+        <v>109.873954</v>
       </c>
       <c r="O7">
-        <v>27.71332375</v>
+        <v>27.4684885</v>
       </c>
       <c r="P7">
-        <v>83.13997125</v>
+        <v>82.40546549999999</v>
       </c>
       <c r="Q7">
-        <v>141.13997125</v>
+        <v>140.4054655</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1000625036268648</v>
+        <v>0.1005009294574077</v>
       </c>
       <c r="T7">
-        <v>1.057677194432483</v>
+        <v>1.066222929911334</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.63834456027063</v>
+        <v>19.69862046689219</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09673437368996327</v>
+        <v>0.09652311893440499</v>
       </c>
       <c r="C8">
-        <v>1622.6128627291</v>
+        <v>1610.178283322189</v>
       </c>
       <c r="D8">
-        <v>1689.2328627291</v>
+        <v>1696.268283322189</v>
       </c>
       <c r="E8">
-        <v>-739.8800000000001</v>
+        <v>-720.4100000000001</v>
       </c>
       <c r="F8">
-        <v>116.82</v>
+        <v>136.29</v>
       </c>
       <c r="G8">
         <v>50.2</v>
@@ -1943,28 +1943,28 @@
         <v>115.75</v>
       </c>
       <c r="M8">
-        <v>5.876046</v>
+        <v>6.855386999999999</v>
       </c>
       <c r="N8">
-        <v>109.873954</v>
+        <v>108.894613</v>
       </c>
       <c r="O8">
-        <v>27.4684885</v>
+        <v>27.22365325</v>
       </c>
       <c r="P8">
-        <v>82.40546549999999</v>
+        <v>81.67095975000001</v>
       </c>
       <c r="Q8">
-        <v>140.4054655</v>
+        <v>139.67095975</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1005009294574077</v>
+        <v>0.1009487838004355</v>
       </c>
       <c r="T8">
-        <v>1.066222929911334</v>
+        <v>1.074952444647795</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.69862046689219</v>
+        <v>16.88453182876474</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09652311893440498</v>
+        <v>0.09631186417884671</v>
       </c>
       <c r="C9">
-        <v>1610.17828332219</v>
+        <v>1597.802552111908</v>
       </c>
       <c r="D9">
-        <v>1696.26828332219</v>
+        <v>1703.362552111908</v>
       </c>
       <c r="E9">
-        <v>-720.4100000000001</v>
+        <v>-700.9400000000001</v>
       </c>
       <c r="F9">
-        <v>136.29</v>
+        <v>155.76</v>
       </c>
       <c r="G9">
         <v>50.2</v>
@@ -2025,28 +2025,28 @@
         <v>115.75</v>
       </c>
       <c r="M9">
-        <v>6.855387</v>
+        <v>7.834727999999999</v>
       </c>
       <c r="N9">
-        <v>108.894613</v>
+        <v>107.915272</v>
       </c>
       <c r="O9">
-        <v>27.22365325</v>
+        <v>26.978818</v>
       </c>
       <c r="P9">
-        <v>81.67095974999999</v>
+        <v>80.936454</v>
       </c>
       <c r="Q9">
-        <v>139.67095975</v>
+        <v>138.936454</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1009487838004355</v>
+        <v>0.1014063741074421</v>
       </c>
       <c r="T9">
-        <v>1.074952444647795</v>
+        <v>1.083871731443744</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.88453182876474</v>
+        <v>14.77396535016915</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09631186417884671</v>
+        <v>0.09610060942328844</v>
       </c>
       <c r="C10">
-        <v>1597.802552111908</v>
+        <v>1585.486410558142</v>
       </c>
       <c r="D10">
-        <v>1703.362552111908</v>
+        <v>1710.516410558142</v>
       </c>
       <c r="E10">
-        <v>-700.9400000000001</v>
+        <v>-681.47</v>
       </c>
       <c r="F10">
-        <v>155.76</v>
+        <v>175.23</v>
       </c>
       <c r="G10">
         <v>50.2</v>
@@ -2107,28 +2107,28 @@
         <v>115.75</v>
       </c>
       <c r="M10">
-        <v>7.834727999999999</v>
+        <v>8.814069</v>
       </c>
       <c r="N10">
-        <v>107.915272</v>
+        <v>106.935931</v>
       </c>
       <c r="O10">
-        <v>26.978818</v>
+        <v>26.73398275</v>
       </c>
       <c r="P10">
-        <v>80.936454</v>
+        <v>80.20194825</v>
       </c>
       <c r="Q10">
-        <v>138.936454</v>
+        <v>138.20194825</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1014063741074421</v>
+        <v>0.101874021344273</v>
       </c>
       <c r="T10">
-        <v>1.083871731443744</v>
+        <v>1.092987046520923</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.77396535016915</v>
+        <v>13.13241364459479</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09610060942328844</v>
+        <v>0.09600185466773015</v>
       </c>
       <c r="C11">
-        <v>1585.486410558142</v>
+        <v>1569.381258951118</v>
       </c>
       <c r="D11">
-        <v>1710.516410558142</v>
+        <v>1713.881258951118</v>
       </c>
       <c r="E11">
-        <v>-681.47</v>
+        <v>-662</v>
       </c>
       <c r="F11">
-        <v>175.23</v>
+        <v>194.7</v>
       </c>
       <c r="G11">
         <v>50.2</v>
@@ -2189,45 +2189,45 @@
         <v>115.75</v>
       </c>
       <c r="M11">
-        <v>8.814069</v>
+        <v>10.08546</v>
       </c>
       <c r="N11">
-        <v>106.935931</v>
+        <v>105.66454</v>
       </c>
       <c r="O11">
-        <v>26.73398275</v>
+        <v>26.416135</v>
       </c>
       <c r="P11">
-        <v>80.20194825</v>
+        <v>79.24840500000001</v>
       </c>
       <c r="Q11">
-        <v>138.20194825</v>
+        <v>137.248405</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.101874021344273</v>
+        <v>0.1023520607419224</v>
       </c>
       <c r="T11">
-        <v>1.092987046520923</v>
+        <v>1.102304924155373</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.13241364459479</v>
+        <v>11.47691825657927</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09600185466773015</v>
+        <v>0.09580184991217187</v>
       </c>
       <c r="C12">
-        <v>1569.381258951118</v>
+        <v>1556.766693357135</v>
       </c>
       <c r="D12">
-        <v>1713.881258951118</v>
+        <v>1720.736693357135</v>
       </c>
       <c r="E12">
-        <v>-662</v>
+        <v>-642.5300000000001</v>
       </c>
       <c r="F12">
-        <v>194.7</v>
+        <v>214.17</v>
       </c>
       <c r="G12">
         <v>50.2</v>
@@ -2271,28 +2271,28 @@
         <v>115.75</v>
       </c>
       <c r="M12">
-        <v>10.08546</v>
+        <v>11.094006</v>
       </c>
       <c r="N12">
-        <v>105.66454</v>
+        <v>104.655994</v>
       </c>
       <c r="O12">
-        <v>26.416135</v>
+        <v>26.1639985</v>
       </c>
       <c r="P12">
-        <v>79.24840500000001</v>
+        <v>78.4919955</v>
       </c>
       <c r="Q12">
-        <v>137.248405</v>
+        <v>136.4919955</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1023520607419224</v>
+        <v>0.1028408425979459</v>
       </c>
       <c r="T12">
-        <v>1.102304924155373</v>
+        <v>1.111832192298462</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.47691825657927</v>
+        <v>10.43356205143571</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09580184991217187</v>
+        <v>0.09575484515661359</v>
       </c>
       <c r="C13">
-        <v>1556.766693357135</v>
+        <v>1538.915811730896</v>
       </c>
       <c r="D13">
-        <v>1720.736693357135</v>
+        <v>1722.355811730896</v>
       </c>
       <c r="E13">
-        <v>-642.5300000000001</v>
+        <v>-623.0600000000001</v>
       </c>
       <c r="F13">
-        <v>214.17</v>
+        <v>233.64</v>
       </c>
       <c r="G13">
         <v>50.2</v>
@@ -2353,45 +2353,45 @@
         <v>115.75</v>
       </c>
       <c r="M13">
-        <v>11.094006</v>
+        <v>12.49974</v>
       </c>
       <c r="N13">
-        <v>104.655994</v>
+        <v>103.25026</v>
       </c>
       <c r="O13">
-        <v>26.1639985</v>
+        <v>25.812565</v>
       </c>
       <c r="P13">
-        <v>78.4919955</v>
+        <v>77.43769499999999</v>
       </c>
       <c r="Q13">
-        <v>136.4919955</v>
+        <v>135.437695</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1028408425979459</v>
+        <v>0.1033407331325154</v>
       </c>
       <c r="T13">
-        <v>1.111832192298462</v>
+        <v>1.121575989262984</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.43356205143571</v>
+        <v>9.26019261200633</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09575484515661359</v>
+        <v>0.09556759040105529</v>
       </c>
       <c r="C14">
-        <v>1538.915811730896</v>
+        <v>1525.926320710957</v>
       </c>
       <c r="D14">
-        <v>1722.355811730896</v>
+        <v>1728.836320710957</v>
       </c>
       <c r="E14">
-        <v>-623.0600000000001</v>
+        <v>-603.59</v>
       </c>
       <c r="F14">
-        <v>233.64</v>
+        <v>253.11</v>
       </c>
       <c r="G14">
         <v>50.2</v>
@@ -2435,28 +2435,28 @@
         <v>115.75</v>
       </c>
       <c r="M14">
-        <v>12.49974</v>
+        <v>13.541385</v>
       </c>
       <c r="N14">
-        <v>103.25026</v>
+        <v>102.208615</v>
       </c>
       <c r="O14">
-        <v>25.812565</v>
+        <v>25.55215375</v>
       </c>
       <c r="P14">
-        <v>77.43769499999999</v>
+        <v>76.65646124999999</v>
       </c>
       <c r="Q14">
-        <v>135.437695</v>
+        <v>134.65646125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1033407331325154</v>
+        <v>0.1038521154035118</v>
       </c>
       <c r="T14">
-        <v>1.121575989262984</v>
+        <v>1.131543781560024</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.26019261200633</v>
+        <v>8.547870103390458</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09556759040105529</v>
+        <v>0.095380335645497</v>
       </c>
       <c r="C15">
-        <v>1525.926320710957</v>
+        <v>1512.985780796701</v>
       </c>
       <c r="D15">
-        <v>1728.836320710957</v>
+        <v>1735.365780796701</v>
       </c>
       <c r="E15">
-        <v>-603.59</v>
+        <v>-584.12</v>
       </c>
       <c r="F15">
-        <v>253.11</v>
+        <v>272.58</v>
       </c>
       <c r="G15">
         <v>50.2</v>
@@ -2517,28 +2517,28 @@
         <v>115.75</v>
       </c>
       <c r="M15">
-        <v>13.541385</v>
+        <v>14.58303</v>
       </c>
       <c r="N15">
-        <v>102.208615</v>
+        <v>101.16697</v>
       </c>
       <c r="O15">
-        <v>25.55215375</v>
+        <v>25.2917425</v>
       </c>
       <c r="P15">
-        <v>76.65646124999999</v>
+        <v>75.87522749999999</v>
       </c>
       <c r="Q15">
-        <v>134.65646125</v>
+        <v>133.8752275</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1038521154035118</v>
+        <v>0.1043753902854616</v>
       </c>
       <c r="T15">
-        <v>1.131543781560024</v>
+        <v>1.141743382980252</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.547870103390458</v>
+        <v>7.937307953148281</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.095380335645497</v>
+        <v>0.09528308088993873</v>
       </c>
       <c r="C16">
-        <v>1512.985780796701</v>
+        <v>1496.926493544983</v>
       </c>
       <c r="D16">
-        <v>1735.365780796701</v>
+        <v>1738.776493544983</v>
       </c>
       <c r="E16">
-        <v>-584.12</v>
+        <v>-564.65</v>
       </c>
       <c r="F16">
-        <v>272.58</v>
+        <v>292.0500000000001</v>
       </c>
       <c r="G16">
         <v>50.2</v>
@@ -2599,45 +2599,45 @@
         <v>115.75</v>
       </c>
       <c r="M16">
-        <v>14.58303</v>
+        <v>15.858315</v>
       </c>
       <c r="N16">
-        <v>101.16697</v>
+        <v>99.891685</v>
       </c>
       <c r="O16">
-        <v>25.2917425</v>
+        <v>24.97292125</v>
       </c>
       <c r="P16">
-        <v>75.87522749999999</v>
+        <v>74.91876375</v>
       </c>
       <c r="Q16">
-        <v>133.8752275</v>
+        <v>132.91876375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1043753902854616</v>
+        <v>0.104910977517575</v>
       </c>
       <c r="T16">
-        <v>1.141743382980252</v>
+        <v>1.152182975022132</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.25</v>
       </c>
       <c r="W16">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.937307953148281</v>
+        <v>7.299010014620088</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09528308088993873</v>
+        <v>0.09510182613438044</v>
       </c>
       <c r="C17">
-        <v>1496.926493544983</v>
+        <v>1483.848985122251</v>
       </c>
       <c r="D17">
-        <v>1738.776493544983</v>
+        <v>1745.168985122251</v>
       </c>
       <c r="E17">
-        <v>-564.6500000000001</v>
+        <v>-545.1800000000001</v>
       </c>
       <c r="F17">
-        <v>292.05</v>
+        <v>311.52</v>
       </c>
       <c r="G17">
         <v>50.2</v>
@@ -2681,28 +2681,28 @@
         <v>115.75</v>
       </c>
       <c r="M17">
-        <v>15.858315</v>
+        <v>16.915536</v>
       </c>
       <c r="N17">
-        <v>99.891685</v>
+        <v>98.834464</v>
       </c>
       <c r="O17">
-        <v>24.97292125</v>
+        <v>24.708616</v>
       </c>
       <c r="P17">
-        <v>74.91876375</v>
+        <v>74.12584799999999</v>
       </c>
       <c r="Q17">
-        <v>132.91876375</v>
+        <v>132.125848</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.104910977517575</v>
+        <v>0.1054593168266434</v>
       </c>
       <c r="T17">
-        <v>1.152182975022132</v>
+        <v>1.162871128779294</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.29901001462009</v>
+        <v>6.842821888706335</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09510182613438044</v>
+        <v>0.09492057137882218</v>
       </c>
       <c r="C18">
-        <v>1483.848985122251</v>
+        <v>1470.818653247581</v>
       </c>
       <c r="D18">
-        <v>1745.168985122251</v>
+        <v>1751.608653247581</v>
       </c>
       <c r="E18">
-        <v>-545.1800000000001</v>
+        <v>-525.71</v>
       </c>
       <c r="F18">
-        <v>311.52</v>
+        <v>330.99</v>
       </c>
       <c r="G18">
         <v>50.2</v>
@@ -2763,28 +2763,28 @@
         <v>115.75</v>
       </c>
       <c r="M18">
-        <v>16.915536</v>
+        <v>17.972757</v>
       </c>
       <c r="N18">
-        <v>98.834464</v>
+        <v>97.777243</v>
       </c>
       <c r="O18">
-        <v>24.708616</v>
+        <v>24.44431075</v>
       </c>
       <c r="P18">
-        <v>74.12584799999999</v>
+        <v>73.33293225</v>
       </c>
       <c r="Q18">
-        <v>132.125848</v>
+        <v>131.33293225</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1054593168266434</v>
+        <v>0.1060208691311111</v>
       </c>
       <c r="T18">
-        <v>1.162871128779294</v>
+        <v>1.173816828410124</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.842821888706335</v>
+        <v>6.44030295407655</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09492057137882218</v>
+        <v>0.09487431662326389</v>
       </c>
       <c r="C19">
-        <v>1470.818653247581</v>
+        <v>1452.999623361169</v>
       </c>
       <c r="D19">
-        <v>1751.608653247581</v>
+        <v>1753.259623361169</v>
       </c>
       <c r="E19">
-        <v>-525.71</v>
+        <v>-506.24</v>
       </c>
       <c r="F19">
-        <v>330.99</v>
+        <v>350.46</v>
       </c>
       <c r="G19">
         <v>50.2</v>
@@ -2845,45 +2845,45 @@
         <v>115.75</v>
       </c>
       <c r="M19">
-        <v>17.972757</v>
+        <v>19.380438</v>
       </c>
       <c r="N19">
-        <v>97.777243</v>
+        <v>96.369562</v>
       </c>
       <c r="O19">
-        <v>24.44431075</v>
+        <v>24.0923905</v>
       </c>
       <c r="P19">
-        <v>73.33293225</v>
+        <v>72.27717150000001</v>
       </c>
       <c r="Q19">
-        <v>131.33293225</v>
+        <v>130.2771715</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1060208691311111</v>
+        <v>0.1065961178332486</v>
       </c>
       <c r="T19">
-        <v>1.173816828410124</v>
+        <v>1.185029496324632</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.44030295407655</v>
+        <v>5.972517236194558</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09487431662326389</v>
+        <v>0.09470056186770563</v>
       </c>
       <c r="C20">
-        <v>1452.999623361169</v>
+        <v>1439.759351316268</v>
       </c>
       <c r="D20">
-        <v>1753.259623361169</v>
+        <v>1759.489351316268</v>
       </c>
       <c r="E20">
-        <v>-506.2400000000001</v>
+        <v>-486.77</v>
       </c>
       <c r="F20">
-        <v>350.46</v>
+        <v>369.93</v>
       </c>
       <c r="G20">
         <v>50.2</v>
@@ -2927,28 +2927,28 @@
         <v>115.75</v>
       </c>
       <c r="M20">
-        <v>19.380438</v>
+        <v>20.457129</v>
       </c>
       <c r="N20">
-        <v>96.369562</v>
+        <v>95.29287099999999</v>
       </c>
       <c r="O20">
-        <v>24.0923905</v>
+        <v>23.82321775</v>
       </c>
       <c r="P20">
-        <v>72.27717150000001</v>
+        <v>71.46965324999999</v>
       </c>
       <c r="Q20">
-        <v>130.2771715</v>
+        <v>129.46965325</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1065961178332486</v>
+        <v>0.107185570207044</v>
       </c>
       <c r="T20">
-        <v>1.185029496324632</v>
+        <v>1.196519020237029</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.972517236194559</v>
+        <v>5.658174223763266</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09470056186770563</v>
+        <v>0.09452680711214732</v>
       </c>
       <c r="C21">
-        <v>1439.759351316268</v>
+        <v>1426.563508402772</v>
       </c>
       <c r="D21">
-        <v>1759.489351316268</v>
+        <v>1765.763508402772</v>
       </c>
       <c r="E21">
-        <v>-486.77</v>
+        <v>-467.3</v>
       </c>
       <c r="F21">
-        <v>369.93</v>
+        <v>389.4</v>
       </c>
       <c r="G21">
         <v>50.2</v>
@@ -3009,28 +3009,28 @@
         <v>115.75</v>
       </c>
       <c r="M21">
-        <v>20.457129</v>
+        <v>21.53382</v>
       </c>
       <c r="N21">
-        <v>95.29287099999999</v>
+        <v>94.21617999999999</v>
       </c>
       <c r="O21">
-        <v>23.82321775</v>
+        <v>23.554045</v>
       </c>
       <c r="P21">
-        <v>71.46965324999999</v>
+        <v>70.66213499999999</v>
       </c>
       <c r="Q21">
-        <v>129.46965325</v>
+        <v>128.662135</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.107185570207044</v>
+        <v>0.1077897588901841</v>
       </c>
       <c r="T21">
-        <v>1.196519020237029</v>
+        <v>1.208295782247236</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.658174223763266</v>
+        <v>5.375265512575102</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09452680711214732</v>
+        <v>0.09435305235658904</v>
       </c>
       <c r="C22">
-        <v>1426.563508402772</v>
+        <v>1413.412571610641</v>
       </c>
       <c r="D22">
-        <v>1765.763508402772</v>
+        <v>1772.082571610641</v>
       </c>
       <c r="E22">
-        <v>-467.3</v>
+        <v>-447.83</v>
       </c>
       <c r="F22">
-        <v>389.4</v>
+        <v>408.8700000000001</v>
       </c>
       <c r="G22">
         <v>50.2</v>
@@ -3091,28 +3091,28 @@
         <v>115.75</v>
       </c>
       <c r="M22">
-        <v>21.53382</v>
+        <v>22.610511</v>
       </c>
       <c r="N22">
-        <v>94.21617999999999</v>
+        <v>93.139489</v>
       </c>
       <c r="O22">
-        <v>23.554045</v>
+        <v>23.28487225</v>
       </c>
       <c r="P22">
-        <v>70.66213499999999</v>
+        <v>69.85461674999999</v>
       </c>
       <c r="Q22">
-        <v>128.662135</v>
+        <v>127.85461675</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1077897588901841</v>
+        <v>0.1084092434893532</v>
       </c>
       <c r="T22">
-        <v>1.208295782247236</v>
+        <v>1.220370690131119</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.375265512575102</v>
+        <v>5.119300488166764</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09435305235658904</v>
+        <v>0.09417929760103076</v>
       </c>
       <c r="C23">
-        <v>1413.412571610641</v>
+        <v>1400.307024782295</v>
       </c>
       <c r="D23">
-        <v>1772.082571610641</v>
+        <v>1778.447024782295</v>
       </c>
       <c r="E23">
-        <v>-447.83</v>
+        <v>-428.3600000000001</v>
       </c>
       <c r="F23">
-        <v>408.87</v>
+        <v>428.34</v>
       </c>
       <c r="G23">
         <v>50.2</v>
@@ -3173,28 +3173,28 @@
         <v>115.75</v>
       </c>
       <c r="M23">
-        <v>22.610511</v>
+        <v>23.687202</v>
       </c>
       <c r="N23">
-        <v>93.139489</v>
+        <v>92.062798</v>
       </c>
       <c r="O23">
-        <v>23.28487225</v>
+        <v>23.0156995</v>
       </c>
       <c r="P23">
-        <v>69.85461674999999</v>
+        <v>69.0470985</v>
       </c>
       <c r="Q23">
-        <v>127.85461675</v>
+        <v>127.0470985</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1084092434893532</v>
+        <v>0.1090446123090138</v>
       </c>
       <c r="T23">
-        <v>1.220370690131119</v>
+        <v>1.232755211037665</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.119300488166764</v>
+        <v>4.886605011431912</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09417929760103076</v>
+        <v>0.09400554284547247</v>
       </c>
       <c r="C24">
-        <v>1400.307024782295</v>
+        <v>1387.247358736111</v>
       </c>
       <c r="D24">
-        <v>1778.447024782295</v>
+        <v>1784.85735873611</v>
       </c>
       <c r="E24">
-        <v>-428.3600000000001</v>
+        <v>-408.89</v>
       </c>
       <c r="F24">
-        <v>428.34</v>
+        <v>447.81</v>
       </c>
       <c r="G24">
         <v>50.2</v>
@@ -3255,28 +3255,28 @@
         <v>115.75</v>
       </c>
       <c r="M24">
-        <v>23.687202</v>
+        <v>24.763893</v>
       </c>
       <c r="N24">
-        <v>92.062798</v>
+        <v>90.986107</v>
       </c>
       <c r="O24">
-        <v>23.0156995</v>
+        <v>22.74652675</v>
       </c>
       <c r="P24">
-        <v>69.0470985</v>
+        <v>68.23958025</v>
       </c>
       <c r="Q24">
-        <v>127.0470985</v>
+        <v>126.23958025</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1090446123090138</v>
+        <v>0.1096964842148993</v>
       </c>
       <c r="T24">
-        <v>1.232755211037665</v>
+        <v>1.245461407811915</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.886605011431912</v>
+        <v>4.674143923978351</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09400554284547247</v>
+        <v>0.09428178808991419</v>
       </c>
       <c r="C25">
-        <v>1387.247358736111</v>
+        <v>1357.607388180502</v>
       </c>
       <c r="D25">
-        <v>1784.85735873611</v>
+        <v>1774.687388180502</v>
       </c>
       <c r="E25">
-        <v>-408.89</v>
+        <v>-389.42</v>
       </c>
       <c r="F25">
-        <v>447.81</v>
+        <v>467.28</v>
       </c>
       <c r="G25">
         <v>50.2</v>
@@ -3337,45 +3337,45 @@
         <v>115.75</v>
       </c>
       <c r="M25">
-        <v>24.763893</v>
+        <v>27.008784</v>
       </c>
       <c r="N25">
-        <v>90.986107</v>
+        <v>88.74121599999999</v>
       </c>
       <c r="O25">
-        <v>22.74652675</v>
+        <v>22.185304</v>
       </c>
       <c r="P25">
-        <v>68.23958025</v>
+        <v>66.55591199999999</v>
       </c>
       <c r="Q25">
-        <v>126.23958025</v>
+        <v>124.555912</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1096964842148993</v>
+        <v>0.1103655106446239</v>
       </c>
       <c r="T25">
-        <v>1.245461407811915</v>
+        <v>1.258501978185486</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.674143923978351</v>
+        <v>4.285642774587703</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09428178808991419</v>
+        <v>0.09412678333435592</v>
       </c>
       <c r="C26">
-        <v>1357.607388180502</v>
+        <v>1343.829573048136</v>
       </c>
       <c r="D26">
-        <v>1774.687388180502</v>
+        <v>1780.379573048136</v>
       </c>
       <c r="E26">
-        <v>-389.4200000000001</v>
+        <v>-369.95</v>
       </c>
       <c r="F26">
-        <v>467.28</v>
+        <v>486.75</v>
       </c>
       <c r="G26">
         <v>50.2</v>
@@ -3419,28 +3419,28 @@
         <v>115.75</v>
       </c>
       <c r="M26">
-        <v>27.008784</v>
+        <v>28.13415</v>
       </c>
       <c r="N26">
-        <v>88.74121599999999</v>
+        <v>87.61584999999999</v>
       </c>
       <c r="O26">
-        <v>22.185304</v>
+        <v>21.9039625</v>
       </c>
       <c r="P26">
-        <v>66.55591199999999</v>
+        <v>65.71188749999999</v>
       </c>
       <c r="Q26">
-        <v>124.555912</v>
+        <v>123.7118875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1103655106446239</v>
+        <v>0.1110523777791412</v>
       </c>
       <c r="T26">
-        <v>1.258501978185486</v>
+        <v>1.271890297102353</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.285642774587703</v>
+        <v>4.114217063604196</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09412678333435592</v>
+        <v>0.09465427857879763</v>
       </c>
       <c r="C27">
-        <v>1343.829573048136</v>
+        <v>1305.136246342589</v>
       </c>
       <c r="D27">
-        <v>1780.379573048136</v>
+        <v>1761.156246342589</v>
       </c>
       <c r="E27">
-        <v>-369.95</v>
+        <v>-350.48</v>
       </c>
       <c r="F27">
-        <v>486.75</v>
+        <v>506.22</v>
       </c>
       <c r="G27">
         <v>50.2</v>
@@ -3501,45 +3501,45 @@
         <v>115.75</v>
       </c>
       <c r="M27">
-        <v>28.13415</v>
+        <v>31.031286</v>
       </c>
       <c r="N27">
-        <v>87.61584999999999</v>
+        <v>84.71871400000001</v>
       </c>
       <c r="O27">
-        <v>21.9039625</v>
+        <v>21.1796785</v>
       </c>
       <c r="P27">
-        <v>65.71188749999999</v>
+        <v>63.5390355</v>
       </c>
       <c r="Q27">
-        <v>123.7118875</v>
+        <v>121.5390355</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1110523777791412</v>
+        <v>0.1117578088902671</v>
       </c>
       <c r="T27">
-        <v>1.271890297102353</v>
+        <v>1.285640462476433</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.25</v>
       </c>
       <c r="W27">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.114217063604196</v>
+        <v>3.730106448053748</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09465427857879763</v>
+        <v>0.09452552382323935</v>
       </c>
       <c r="C28">
-        <v>1305.136246342589</v>
+        <v>1290.32001348977</v>
       </c>
       <c r="D28">
-        <v>1761.156246342589</v>
+        <v>1765.81001348977</v>
       </c>
       <c r="E28">
-        <v>-350.48</v>
+        <v>-331.01</v>
       </c>
       <c r="F28">
-        <v>506.22</v>
+        <v>525.6900000000001</v>
       </c>
       <c r="G28">
         <v>50.2</v>
@@ -3583,28 +3583,28 @@
         <v>115.75</v>
       </c>
       <c r="M28">
-        <v>31.031286</v>
+        <v>32.224797</v>
       </c>
       <c r="N28">
-        <v>84.71871400000001</v>
+        <v>83.525203</v>
       </c>
       <c r="O28">
-        <v>21.1796785</v>
+        <v>20.88130075</v>
       </c>
       <c r="P28">
-        <v>63.5390355</v>
+        <v>62.64390225</v>
       </c>
       <c r="Q28">
-        <v>121.5390355</v>
+        <v>120.64390225</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1117578088902671</v>
+        <v>0.1124825668811498</v>
       </c>
       <c r="T28">
-        <v>1.285640462476433</v>
+        <v>1.299767344710076</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.730106448053748</v>
+        <v>3.591954357385091</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09452552382323935</v>
+        <v>0.09498476906768105</v>
       </c>
       <c r="C29">
-        <v>1290.32001348977</v>
+        <v>1254.362392084721</v>
       </c>
       <c r="D29">
-        <v>1765.81001348977</v>
+        <v>1749.322392084721</v>
       </c>
       <c r="E29">
-        <v>-331.01</v>
+        <v>-311.54</v>
       </c>
       <c r="F29">
-        <v>525.6900000000001</v>
+        <v>545.1600000000001</v>
       </c>
       <c r="G29">
         <v>50.2</v>
@@ -3665,45 +3665,45 @@
         <v>115.75</v>
       </c>
       <c r="M29">
-        <v>32.224797</v>
+        <v>34.94475600000001</v>
       </c>
       <c r="N29">
-        <v>83.525203</v>
+        <v>80.80524399999999</v>
       </c>
       <c r="O29">
-        <v>20.88130075</v>
+        <v>20.201311</v>
       </c>
       <c r="P29">
-        <v>62.64390225</v>
+        <v>60.60393299999999</v>
       </c>
       <c r="Q29">
-        <v>120.64390225</v>
+        <v>118.603933</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1124825668811498</v>
+        <v>0.1132274570384459</v>
       </c>
       <c r="T29">
-        <v>1.299767344710076</v>
+        <v>1.314286640339098</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.25</v>
       </c>
       <c r="W29">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.591954357385091</v>
+        <v>3.312371103692926</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09498476906768105</v>
+        <v>0.09487701431212277</v>
       </c>
       <c r="C30">
-        <v>1254.362392084721</v>
+        <v>1238.73324934537</v>
       </c>
       <c r="D30">
-        <v>1749.322392084721</v>
+        <v>1753.16324934537</v>
       </c>
       <c r="E30">
-        <v>-311.54</v>
+        <v>-292.0699999999999</v>
       </c>
       <c r="F30">
-        <v>545.1600000000001</v>
+        <v>564.6300000000001</v>
       </c>
       <c r="G30">
         <v>50.2</v>
@@ -3747,28 +3747,28 @@
         <v>115.75</v>
       </c>
       <c r="M30">
-        <v>34.94475600000001</v>
+        <v>36.19278300000001</v>
       </c>
       <c r="N30">
-        <v>80.80524399999999</v>
+        <v>79.55721699999998</v>
       </c>
       <c r="O30">
-        <v>20.201311</v>
+        <v>19.88930425</v>
       </c>
       <c r="P30">
-        <v>60.60393299999999</v>
+        <v>59.66791274999999</v>
       </c>
       <c r="Q30">
-        <v>118.603933</v>
+        <v>117.66791275</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1132274570384459</v>
+        <v>0.1139933300170743</v>
       </c>
       <c r="T30">
-        <v>1.314286640339098</v>
+        <v>1.329214930211192</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.312371103692926</v>
+        <v>3.198151410462134</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09487701431212277</v>
+        <v>0.0947692595565645</v>
       </c>
       <c r="C31">
-        <v>1238.73324934537</v>
+        <v>1223.121009889385</v>
       </c>
       <c r="D31">
-        <v>1753.16324934537</v>
+        <v>1757.021009889385</v>
       </c>
       <c r="E31">
-        <v>-292.0700000000001</v>
+        <v>-272.6</v>
       </c>
       <c r="F31">
-        <v>564.63</v>
+        <v>584.1</v>
       </c>
       <c r="G31">
         <v>50.2</v>
@@ -3829,28 +3829,28 @@
         <v>115.75</v>
       </c>
       <c r="M31">
-        <v>36.192783</v>
+        <v>37.44081000000001</v>
       </c>
       <c r="N31">
-        <v>79.55721700000001</v>
+        <v>78.30919</v>
       </c>
       <c r="O31">
-        <v>19.88930425</v>
+        <v>19.5772975</v>
       </c>
       <c r="P31">
-        <v>59.66791275000001</v>
+        <v>58.7318925</v>
       </c>
       <c r="Q31">
-        <v>117.66791275</v>
+        <v>116.7318925</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1139933300170743</v>
+        <v>0.1147810850808064</v>
       </c>
       <c r="T31">
-        <v>1.329214930211192</v>
+        <v>1.344569742651059</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.198151410462136</v>
+        <v>3.091546363446731</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0947692595565645</v>
+        <v>0.09647500480100622</v>
       </c>
       <c r="C32">
-        <v>1223.121009889385</v>
+        <v>1144.50883035192</v>
       </c>
       <c r="D32">
-        <v>1757.021009889385</v>
+        <v>1697.87883035192</v>
       </c>
       <c r="E32">
-        <v>-272.6</v>
+        <v>-253.13</v>
       </c>
       <c r="F32">
-        <v>584.1</v>
+        <v>603.5700000000001</v>
       </c>
       <c r="G32">
         <v>50.2</v>
@@ -3911,45 +3911,45 @@
         <v>115.75</v>
       </c>
       <c r="M32">
-        <v>37.44081000000001</v>
+        <v>43.39668300000001</v>
       </c>
       <c r="N32">
-        <v>78.30919</v>
+        <v>72.35331699999999</v>
       </c>
       <c r="O32">
-        <v>19.5772975</v>
+        <v>18.08832925</v>
       </c>
       <c r="P32">
-        <v>58.7318925</v>
+        <v>54.26498774999999</v>
       </c>
       <c r="Q32">
-        <v>116.7318925</v>
+        <v>112.26498775</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1147810850808064</v>
+        <v>0.1155916736246467</v>
       </c>
       <c r="T32">
-        <v>1.344569742651059</v>
+        <v>1.360369622118169</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.25</v>
       </c>
       <c r="W32">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.091546363446731</v>
+        <v>2.667254545698803</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09647500480100622</v>
+        <v>0.09642575004544793</v>
       </c>
       <c r="C33">
-        <v>1144.50883035192</v>
+        <v>1126.690728974292</v>
       </c>
       <c r="D33">
-        <v>1697.87883035192</v>
+        <v>1699.530728974292</v>
       </c>
       <c r="E33">
-        <v>-253.13</v>
+        <v>-233.6600000000001</v>
       </c>
       <c r="F33">
-        <v>603.5700000000001</v>
+        <v>623.04</v>
       </c>
       <c r="G33">
         <v>50.2</v>
@@ -3993,28 +3993,28 @@
         <v>115.75</v>
       </c>
       <c r="M33">
-        <v>43.39668300000001</v>
+        <v>44.796576</v>
       </c>
       <c r="N33">
-        <v>72.35331699999999</v>
+        <v>70.953424</v>
       </c>
       <c r="O33">
-        <v>18.08832925</v>
+        <v>17.738356</v>
       </c>
       <c r="P33">
-        <v>54.26498774999999</v>
+        <v>53.215068</v>
       </c>
       <c r="Q33">
-        <v>112.26498775</v>
+        <v>111.215068</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1155916736246467</v>
+        <v>0.1164261030080117</v>
       </c>
       <c r="T33">
-        <v>1.360369622118169</v>
+        <v>1.376634203922547</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.667254545698803</v>
+        <v>2.583902841145716</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09642575004544793</v>
+        <v>0.09637649528988963</v>
       </c>
       <c r="C34">
-        <v>1126.690728974292</v>
+        <v>1108.875845054195</v>
       </c>
       <c r="D34">
-        <v>1699.530728974292</v>
+        <v>1701.185845054194</v>
       </c>
       <c r="E34">
-        <v>-233.6600000000001</v>
+        <v>-214.1900000000001</v>
       </c>
       <c r="F34">
-        <v>623.04</v>
+        <v>642.51</v>
       </c>
       <c r="G34">
         <v>50.2</v>
@@ -4075,28 +4075,28 @@
         <v>115.75</v>
       </c>
       <c r="M34">
-        <v>44.796576</v>
+        <v>46.196469</v>
       </c>
       <c r="N34">
-        <v>70.953424</v>
+        <v>69.55353099999999</v>
       </c>
       <c r="O34">
-        <v>17.738356</v>
+        <v>17.38838275</v>
       </c>
       <c r="P34">
-        <v>53.215068</v>
+        <v>52.16514824999999</v>
       </c>
       <c r="Q34">
-        <v>111.215068</v>
+        <v>110.16514825</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1164261030080117</v>
+        <v>0.1172854407311786</v>
       </c>
       <c r="T34">
-        <v>1.376634203922547</v>
+        <v>1.393384295631533</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.583902841145716</v>
+        <v>2.505602755050391</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09637649528988963</v>
+        <v>0.09732174053433137</v>
       </c>
       <c r="C35">
-        <v>1108.875845054195</v>
+        <v>1058.194985070193</v>
       </c>
       <c r="D35">
-        <v>1701.185845054194</v>
+        <v>1669.974985070193</v>
       </c>
       <c r="E35">
-        <v>-214.1900000000001</v>
+        <v>-194.72</v>
       </c>
       <c r="F35">
-        <v>642.51</v>
+        <v>661.98</v>
       </c>
       <c r="G35">
         <v>50.2</v>
@@ -4157,45 +4157,45 @@
         <v>115.75</v>
       </c>
       <c r="M35">
-        <v>46.196469</v>
+        <v>50.17808400000001</v>
       </c>
       <c r="N35">
-        <v>69.55353099999999</v>
+        <v>65.57191599999999</v>
       </c>
       <c r="O35">
-        <v>17.38838275</v>
+        <v>16.392979</v>
       </c>
       <c r="P35">
-        <v>52.16514824999999</v>
+        <v>49.17893699999999</v>
       </c>
       <c r="Q35">
-        <v>110.16514825</v>
+        <v>107.178937</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1172854407311786</v>
+        <v>0.1181708189914112</v>
       </c>
       <c r="T35">
-        <v>1.393384295631533</v>
+        <v>1.410641965877156</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.25</v>
       </c>
       <c r="W35">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.505602755050391</v>
+        <v>2.306783973656706</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09732174053433137</v>
+        <v>0.09730173577877307</v>
       </c>
       <c r="C36">
-        <v>1058.194985070193</v>
+        <v>1039.373651389097</v>
       </c>
       <c r="D36">
-        <v>1669.974985070193</v>
+        <v>1670.623651389097</v>
       </c>
       <c r="E36">
-        <v>-194.72</v>
+        <v>-175.25</v>
       </c>
       <c r="F36">
-        <v>661.98</v>
+        <v>681.45</v>
       </c>
       <c r="G36">
         <v>50.2</v>
@@ -4239,28 +4239,28 @@
         <v>115.75</v>
       </c>
       <c r="M36">
-        <v>50.17808400000001</v>
+        <v>51.65391000000001</v>
       </c>
       <c r="N36">
-        <v>65.57191599999999</v>
+        <v>64.09608999999999</v>
       </c>
       <c r="O36">
-        <v>16.392979</v>
+        <v>16.0240225</v>
       </c>
       <c r="P36">
-        <v>49.17893699999999</v>
+        <v>48.07206749999999</v>
       </c>
       <c r="Q36">
-        <v>107.178937</v>
+        <v>106.0720675</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1181708189914112</v>
+        <v>0.1190834396596509</v>
       </c>
       <c r="T36">
-        <v>1.410641965877156</v>
+        <v>1.428430641361105</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.306783973656706</v>
+        <v>2.240875860123657</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09730173577877307</v>
+        <v>0.0972817310232148</v>
       </c>
       <c r="C37">
-        <v>1039.373651389097</v>
+        <v>1020.552821825127</v>
       </c>
       <c r="D37">
-        <v>1670.623651389097</v>
+        <v>1671.272821825127</v>
       </c>
       <c r="E37">
-        <v>-175.25</v>
+        <v>-155.78</v>
       </c>
       <c r="F37">
-        <v>681.45</v>
+        <v>700.9200000000001</v>
       </c>
       <c r="G37">
         <v>50.2</v>
@@ -4321,28 +4321,28 @@
         <v>115.75</v>
       </c>
       <c r="M37">
-        <v>51.65391000000001</v>
+        <v>53.12973600000001</v>
       </c>
       <c r="N37">
-        <v>64.09608999999999</v>
+        <v>62.62026399999999</v>
       </c>
       <c r="O37">
-        <v>16.0240225</v>
+        <v>15.655066</v>
       </c>
       <c r="P37">
-        <v>48.07206749999999</v>
+        <v>46.96519799999999</v>
       </c>
       <c r="Q37">
-        <v>106.0720675</v>
+        <v>104.965198</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1190834396596509</v>
+        <v>0.1200245797237731</v>
       </c>
       <c r="T37">
-        <v>1.428430641361105</v>
+        <v>1.446775212953927</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.240875860123657</v>
+        <v>2.178629308453556</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09728173102321482</v>
+        <v>0.09726172626765651</v>
       </c>
       <c r="C38">
-        <v>1020.552821825127</v>
+        <v>1001.732496966181</v>
       </c>
       <c r="D38">
-        <v>1671.272821825127</v>
+        <v>1671.922496966181</v>
       </c>
       <c r="E38">
-        <v>-155.7800000000001</v>
+        <v>-136.3100000000001</v>
       </c>
       <c r="F38">
-        <v>700.92</v>
+        <v>720.39</v>
       </c>
       <c r="G38">
         <v>50.2</v>
@@ -4403,28 +4403,28 @@
         <v>115.75</v>
       </c>
       <c r="M38">
-        <v>53.129736</v>
+        <v>54.60556200000001</v>
       </c>
       <c r="N38">
-        <v>62.620264</v>
+        <v>61.14443799999999</v>
       </c>
       <c r="O38">
-        <v>15.655066</v>
+        <v>15.2861095</v>
       </c>
       <c r="P38">
-        <v>46.965198</v>
+        <v>45.8583285</v>
       </c>
       <c r="Q38">
-        <v>104.965198</v>
+        <v>103.8583285</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1200245797237731</v>
+        <v>0.1209955972502484</v>
       </c>
       <c r="T38">
-        <v>1.446775212953927</v>
+        <v>1.465702151898902</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.178629308453556</v>
+        <v>2.119747435252108</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09726172626765651</v>
+        <v>0.09724172151209824</v>
       </c>
       <c r="C39">
-        <v>1001.732496966181</v>
+        <v>982.9126774010705</v>
       </c>
       <c r="D39">
-        <v>1671.922496966181</v>
+        <v>1672.57267740107</v>
       </c>
       <c r="E39">
-        <v>-136.3100000000001</v>
+        <v>-116.84</v>
       </c>
       <c r="F39">
-        <v>720.39</v>
+        <v>739.86</v>
       </c>
       <c r="G39">
         <v>50.2</v>
@@ -4485,28 +4485,28 @@
         <v>115.75</v>
       </c>
       <c r="M39">
-        <v>54.60556200000001</v>
+        <v>56.081388</v>
       </c>
       <c r="N39">
-        <v>61.14443799999999</v>
+        <v>59.668612</v>
       </c>
       <c r="O39">
-        <v>15.2861095</v>
+        <v>14.917153</v>
       </c>
       <c r="P39">
-        <v>45.8583285</v>
+        <v>44.751459</v>
       </c>
       <c r="Q39">
-        <v>103.8583285</v>
+        <v>102.751459</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1209955972502484</v>
+        <v>0.1219979379227391</v>
       </c>
       <c r="T39">
-        <v>1.465702151898902</v>
+        <v>1.485239637261458</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.119747435252108</v>
+        <v>2.063964608008632</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09724172151209824</v>
+        <v>0.09722171675653996</v>
       </c>
       <c r="C40">
-        <v>982.9126774010705</v>
+        <v>964.0933637195238</v>
       </c>
       <c r="D40">
-        <v>1672.57267740107</v>
+        <v>1673.223363719524</v>
       </c>
       <c r="E40">
-        <v>-116.84</v>
+        <v>-97.37</v>
       </c>
       <c r="F40">
-        <v>739.86</v>
+        <v>759.33</v>
       </c>
       <c r="G40">
         <v>50.2</v>
@@ -4567,28 +4567,28 @@
         <v>115.75</v>
       </c>
       <c r="M40">
-        <v>56.081388</v>
+        <v>57.55721400000001</v>
       </c>
       <c r="N40">
-        <v>59.668612</v>
+        <v>58.19278599999999</v>
       </c>
       <c r="O40">
-        <v>14.917153</v>
+        <v>14.5481965</v>
       </c>
       <c r="P40">
-        <v>44.751459</v>
+        <v>43.6445895</v>
       </c>
       <c r="Q40">
-        <v>102.751459</v>
+        <v>101.6445895</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1219979379227391</v>
+        <v>0.123033142223836</v>
       </c>
       <c r="T40">
-        <v>1.485239637261458</v>
+        <v>1.505417695914589</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.063964608008632</v>
+        <v>2.011042438572513</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09722171675653996</v>
+        <v>0.1014617120009817</v>
       </c>
       <c r="C41">
-        <v>964.0933637195238</v>
+        <v>817.166646165913</v>
       </c>
       <c r="D41">
-        <v>1673.223363719524</v>
+        <v>1545.766646165913</v>
       </c>
       <c r="E41">
-        <v>-97.37</v>
+        <v>-77.89999999999998</v>
       </c>
       <c r="F41">
-        <v>759.33</v>
+        <v>778.8000000000001</v>
       </c>
       <c r="G41">
         <v>50.2</v>
@@ -4649,45 +4649,45 @@
         <v>115.75</v>
       </c>
       <c r="M41">
-        <v>57.55721400000001</v>
+        <v>70.092</v>
       </c>
       <c r="N41">
-        <v>58.19278599999999</v>
+        <v>45.658</v>
       </c>
       <c r="O41">
-        <v>14.5481965</v>
+        <v>11.4145</v>
       </c>
       <c r="P41">
-        <v>43.6445895</v>
+        <v>34.2435</v>
       </c>
       <c r="Q41">
-        <v>101.6445895</v>
+        <v>92.2435</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.123033142223836</v>
+        <v>0.1241028533349695</v>
       </c>
       <c r="T41">
-        <v>1.505417695914589</v>
+        <v>1.526268356522824</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.25</v>
       </c>
       <c r="W41">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.011042438572513</v>
+        <v>1.651401015807795</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1014617120009817</v>
+        <v>0.1015482072454234</v>
       </c>
       <c r="C42">
-        <v>817.166646165913</v>
+        <v>795.2983365068889</v>
       </c>
       <c r="D42">
-        <v>1545.766646165913</v>
+        <v>1543.368336506889</v>
       </c>
       <c r="E42">
-        <v>-77.89999999999998</v>
+        <v>-58.42999999999995</v>
       </c>
       <c r="F42">
-        <v>778.8000000000001</v>
+        <v>798.2700000000001</v>
       </c>
       <c r="G42">
         <v>50.2</v>
@@ -4731,28 +4731,28 @@
         <v>115.75</v>
       </c>
       <c r="M42">
-        <v>70.092</v>
+        <v>71.8443</v>
       </c>
       <c r="N42">
-        <v>45.658</v>
+        <v>43.9057</v>
       </c>
       <c r="O42">
-        <v>11.4145</v>
+        <v>10.976425</v>
       </c>
       <c r="P42">
-        <v>34.2435</v>
+        <v>32.929275</v>
       </c>
       <c r="Q42">
-        <v>92.2435</v>
+        <v>90.92927499999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1241028533349695</v>
+        <v>0.1252088258397007</v>
       </c>
       <c r="T42">
-        <v>1.526268356522824</v>
+        <v>1.547825819185576</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.651401015807795</v>
+        <v>1.611122942251508</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1015482072454234</v>
+        <v>0.1016347024898651</v>
       </c>
       <c r="C43">
-        <v>795.2983365068889</v>
+        <v>773.4374574374784</v>
       </c>
       <c r="D43">
-        <v>1543.368336506889</v>
+        <v>1540.977457437479</v>
       </c>
       <c r="E43">
-        <v>-58.42999999999995</v>
+        <v>-38.95999999999992</v>
       </c>
       <c r="F43">
-        <v>798.2700000000001</v>
+        <v>817.7400000000001</v>
       </c>
       <c r="G43">
         <v>50.2</v>
@@ -4813,28 +4813,28 @@
         <v>115.75</v>
       </c>
       <c r="M43">
-        <v>71.8443</v>
+        <v>73.59660000000001</v>
       </c>
       <c r="N43">
-        <v>43.9057</v>
+        <v>42.15339999999999</v>
       </c>
       <c r="O43">
-        <v>10.976425</v>
+        <v>10.53835</v>
       </c>
       <c r="P43">
-        <v>32.929275</v>
+        <v>31.61504999999999</v>
       </c>
       <c r="Q43">
-        <v>90.92927499999999</v>
+        <v>89.61505</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1252088258397007</v>
+        <v>0.1263529353273536</v>
       </c>
       <c r="T43">
-        <v>1.547825819185576</v>
+        <v>1.570126642629802</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.611122942251508</v>
+        <v>1.5727628721979</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1016347024898651</v>
+        <v>0.1017211977343069</v>
       </c>
       <c r="C44">
-        <v>773.4374574374781</v>
+        <v>751.583974478234</v>
       </c>
       <c r="D44">
-        <v>1540.977457437478</v>
+        <v>1538.593974478234</v>
       </c>
       <c r="E44">
-        <v>-38.96000000000004</v>
+        <v>-19.49000000000001</v>
       </c>
       <c r="F44">
-        <v>817.74</v>
+        <v>837.21</v>
       </c>
       <c r="G44">
         <v>50.2</v>
@@ -4895,28 +4895,28 @@
         <v>115.75</v>
       </c>
       <c r="M44">
-        <v>73.5966</v>
+        <v>75.3489</v>
       </c>
       <c r="N44">
-        <v>42.1534</v>
+        <v>40.4011</v>
       </c>
       <c r="O44">
-        <v>10.53835</v>
+        <v>10.100275</v>
       </c>
       <c r="P44">
-        <v>31.61505</v>
+        <v>30.300825</v>
       </c>
       <c r="Q44">
-        <v>89.61505</v>
+        <v>88.300825</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1263529353273536</v>
+        <v>0.1275371890075558</v>
       </c>
       <c r="T44">
-        <v>1.570126642629802</v>
+        <v>1.593209951107158</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.572762872197901</v>
+        <v>1.536186991449112</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1017211977343069</v>
+        <v>0.1018076929787486</v>
       </c>
       <c r="C45">
-        <v>751.583974478234</v>
+        <v>729.7378533627021</v>
       </c>
       <c r="D45">
-        <v>1538.593974478234</v>
+        <v>1536.217853362702</v>
       </c>
       <c r="E45">
-        <v>-19.49000000000001</v>
+        <v>-0.0200000000000955</v>
       </c>
       <c r="F45">
-        <v>837.21</v>
+        <v>856.6799999999999</v>
       </c>
       <c r="G45">
         <v>50.2</v>
@@ -4977,28 +4977,28 @@
         <v>115.75</v>
       </c>
       <c r="M45">
-        <v>75.3489</v>
+        <v>77.10119999999999</v>
       </c>
       <c r="N45">
-        <v>40.4011</v>
+        <v>38.64880000000001</v>
       </c>
       <c r="O45">
-        <v>10.100275</v>
+        <v>9.662200000000002</v>
       </c>
       <c r="P45">
-        <v>30.300825</v>
+        <v>28.98660000000001</v>
       </c>
       <c r="Q45">
-        <v>88.300825</v>
+        <v>86.98660000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1275371890075558</v>
+        <v>0.128763737462051</v>
       </c>
       <c r="T45">
-        <v>1.593209951107158</v>
+        <v>1.617117663458706</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.536186991449112</v>
+        <v>1.50127365073436</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1018076929787486</v>
+        <v>0.1233041672688623</v>
       </c>
       <c r="C46">
-        <v>729.7378533627021</v>
+        <v>284.1840858374391</v>
       </c>
       <c r="D46">
-        <v>1536.217853362702</v>
+        <v>1110.134085837439</v>
       </c>
       <c r="E46">
-        <v>-0.0200000000000955</v>
+        <v>19.44999999999993</v>
       </c>
       <c r="F46">
-        <v>856.6799999999999</v>
+        <v>876.15</v>
       </c>
       <c r="G46">
         <v>50.2</v>
@@ -5059,45 +5059,45 @@
         <v>115.75</v>
       </c>
       <c r="M46">
-        <v>77.10119999999999</v>
+        <v>128.61882</v>
       </c>
       <c r="N46">
-        <v>38.64880000000001</v>
+        <v>-12.86882</v>
       </c>
       <c r="O46">
-        <v>9.662200000000002</v>
+        <v>-3.217205</v>
       </c>
       <c r="P46">
-        <v>28.98660000000001</v>
+        <v>-9.651615</v>
       </c>
       <c r="Q46">
-        <v>86.98660000000001</v>
+        <v>48.348385</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.128763737462051</v>
+        <v>0.1311032298384226</v>
       </c>
       <c r="T46">
-        <v>1.617117663458706</v>
+        <v>1.662718724369059</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.25</v>
+        <v>0.224986514415231</v>
       </c>
       <c r="W46">
-        <v>0.0675</v>
+        <v>0.1137719796838441</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.50127365073436</v>
+        <v>0.8999460576609239</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1233041672688623</v>
+        <v>0.1243141672688623</v>
       </c>
       <c r="C47">
-        <v>284.1840858374391</v>
+        <v>250.4334092958887</v>
       </c>
       <c r="D47">
-        <v>1110.134085837439</v>
+        <v>1095.853409295889</v>
       </c>
       <c r="E47">
-        <v>19.44999999999993</v>
+        <v>38.91999999999996</v>
       </c>
       <c r="F47">
-        <v>876.15</v>
+        <v>895.62</v>
       </c>
       <c r="G47">
         <v>50.2</v>
@@ -5141,37 +5141,37 @@
         <v>115.75</v>
       </c>
       <c r="M47">
-        <v>128.61882</v>
+        <v>131.477016</v>
       </c>
       <c r="N47">
-        <v>-12.86882</v>
+        <v>-15.72701600000002</v>
       </c>
       <c r="O47">
-        <v>-3.217205</v>
+        <v>-3.931754000000005</v>
       </c>
       <c r="P47">
-        <v>-9.651615</v>
+        <v>-11.79526200000002</v>
       </c>
       <c r="Q47">
-        <v>48.348385</v>
+        <v>46.20473799999998</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1311032298384226</v>
+        <v>0.1326829192798749</v>
       </c>
       <c r="T47">
-        <v>1.662718724369059</v>
+        <v>1.693509811857375</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.224986514415231</v>
+        <v>0.2200955032322912</v>
       </c>
       <c r="W47">
-        <v>0.1137719796838441</v>
+        <v>0.1144899801254997</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.8999460576609239</v>
+        <v>0.8803820129291646</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1243141672688623</v>
+        <v>0.1253241672688623</v>
       </c>
       <c r="C48">
-        <v>250.4334092958887</v>
+        <v>217.0454774092603</v>
       </c>
       <c r="D48">
-        <v>1095.853409295889</v>
+        <v>1081.93547740926</v>
       </c>
       <c r="E48">
-        <v>38.91999999999996</v>
+        <v>58.38999999999999</v>
       </c>
       <c r="F48">
-        <v>895.62</v>
+        <v>915.09</v>
       </c>
       <c r="G48">
         <v>50.2</v>
@@ -5223,37 +5223,37 @@
         <v>115.75</v>
       </c>
       <c r="M48">
-        <v>131.477016</v>
+        <v>134.335212</v>
       </c>
       <c r="N48">
-        <v>-15.72701600000002</v>
+        <v>-18.58521200000001</v>
       </c>
       <c r="O48">
-        <v>-3.931754000000005</v>
+        <v>-4.646303000000003</v>
       </c>
       <c r="P48">
-        <v>-11.79526200000002</v>
+        <v>-13.93890900000001</v>
       </c>
       <c r="Q48">
-        <v>46.20473799999998</v>
+        <v>44.06109099999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1326829192798749</v>
+        <v>0.1343222196436461</v>
       </c>
       <c r="T48">
-        <v>1.693509811857375</v>
+        <v>1.725462827175439</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2200955032322912</v>
+        <v>0.2154126201847956</v>
       </c>
       <c r="W48">
-        <v>0.1144899801254997</v>
+        <v>0.115177427356872</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8803820129291646</v>
+        <v>0.8616504807391825</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1253241672688623</v>
+        <v>0.1263341672688623</v>
       </c>
       <c r="C49">
-        <v>217.0454774092603</v>
+        <v>184.0066423515242</v>
       </c>
       <c r="D49">
-        <v>1081.93547740926</v>
+        <v>1068.366642351524</v>
       </c>
       <c r="E49">
-        <v>58.38999999999999</v>
+        <v>77.86000000000001</v>
       </c>
       <c r="F49">
-        <v>915.09</v>
+        <v>934.5600000000001</v>
       </c>
       <c r="G49">
         <v>50.2</v>
@@ -5305,37 +5305,37 @@
         <v>115.75</v>
       </c>
       <c r="M49">
-        <v>134.335212</v>
+        <v>137.193408</v>
       </c>
       <c r="N49">
-        <v>-18.58521200000001</v>
+        <v>-21.44340800000003</v>
       </c>
       <c r="O49">
-        <v>-4.646303000000003</v>
+        <v>-5.360852000000008</v>
       </c>
       <c r="P49">
-        <v>-13.93890900000001</v>
+        <v>-16.08255600000003</v>
       </c>
       <c r="Q49">
-        <v>44.06109099999999</v>
+        <v>41.91744399999997</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1343222196436461</v>
+        <v>0.1360245700214085</v>
       </c>
       <c r="T49">
-        <v>1.725462827175439</v>
+        <v>1.75864480462112</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2154126201847956</v>
+        <v>0.210924857264279</v>
       </c>
       <c r="W49">
-        <v>0.115177427356872</v>
+        <v>0.1158362309536038</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8616504807391825</v>
+        <v>0.843699429057116</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1263341672688623</v>
+        <v>0.1273441672688623</v>
       </c>
       <c r="C50">
-        <v>184.0066423515243</v>
+        <v>151.3039324604872</v>
       </c>
       <c r="D50">
-        <v>1068.366642351524</v>
+        <v>1055.133932460487</v>
       </c>
       <c r="E50">
-        <v>77.8599999999999</v>
+        <v>97.32999999999993</v>
       </c>
       <c r="F50">
-        <v>934.5599999999999</v>
+        <v>954.03</v>
       </c>
       <c r="G50">
         <v>50.2</v>
@@ -5387,37 +5387,37 @@
         <v>115.75</v>
       </c>
       <c r="M50">
-        <v>137.193408</v>
+        <v>140.051604</v>
       </c>
       <c r="N50">
-        <v>-21.44340800000001</v>
+        <v>-24.301604</v>
       </c>
       <c r="O50">
-        <v>-5.360852000000001</v>
+        <v>-6.075400999999999</v>
       </c>
       <c r="P50">
-        <v>-16.082556</v>
+        <v>-18.226203</v>
       </c>
       <c r="Q50">
-        <v>41.917444</v>
+        <v>39.773797</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1360245700214085</v>
+        <v>0.1377936792375146</v>
       </c>
       <c r="T50">
-        <v>1.75864480462112</v>
+        <v>1.79312803608428</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.210924857264279</v>
+        <v>0.2066202683405182</v>
       </c>
       <c r="W50">
-        <v>0.1158362309536038</v>
+        <v>0.1164681446076119</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8436994290571161</v>
+        <v>0.8264810733620731</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1273441672688623</v>
+        <v>0.1283541672688623</v>
       </c>
       <c r="C51">
-        <v>151.3039324604872</v>
+        <v>118.9250108755311</v>
       </c>
       <c r="D51">
-        <v>1055.133932460487</v>
+        <v>1042.225010875531</v>
       </c>
       <c r="E51">
-        <v>97.32999999999993</v>
+        <v>116.8</v>
       </c>
       <c r="F51">
-        <v>954.03</v>
+        <v>973.5</v>
       </c>
       <c r="G51">
         <v>50.2</v>
@@ -5469,37 +5469,37 @@
         <v>115.75</v>
       </c>
       <c r="M51">
-        <v>140.051604</v>
+        <v>142.9098</v>
       </c>
       <c r="N51">
-        <v>-24.301604</v>
+        <v>-27.15980000000002</v>
       </c>
       <c r="O51">
-        <v>-6.075400999999999</v>
+        <v>-6.789950000000005</v>
       </c>
       <c r="P51">
-        <v>-18.226203</v>
+        <v>-20.36985000000001</v>
       </c>
       <c r="Q51">
-        <v>39.773797</v>
+        <v>37.63014999999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1377936792375146</v>
+        <v>0.1396335528222648</v>
       </c>
       <c r="T51">
-        <v>1.79312803608428</v>
+        <v>1.828990596805965</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2066202683405182</v>
+        <v>0.2024878629737079</v>
       </c>
       <c r="W51">
-        <v>0.1164681446076119</v>
+        <v>0.1170747817154597</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8264810733620731</v>
+        <v>0.8099514518948314</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1283541672688623</v>
+        <v>0.1583254660430543</v>
       </c>
       <c r="C52">
-        <v>118.9250108755311</v>
+        <v>-178.1429257456269</v>
       </c>
       <c r="D52">
-        <v>1042.225010875531</v>
+        <v>764.627074254373</v>
       </c>
       <c r="E52">
-        <v>116.8</v>
+        <v>136.27</v>
       </c>
       <c r="F52">
-        <v>973.5</v>
+        <v>992.97</v>
       </c>
       <c r="G52">
         <v>50.2</v>
@@ -5551,45 +5551,45 @@
         <v>115.75</v>
       </c>
       <c r="M52">
-        <v>142.9098</v>
+        <v>199.388376</v>
       </c>
       <c r="N52">
-        <v>-27.15980000000002</v>
+        <v>-83.63837600000002</v>
       </c>
       <c r="O52">
-        <v>-6.789950000000005</v>
+        <v>-20.90959400000001</v>
       </c>
       <c r="P52">
-        <v>-20.36985000000001</v>
+        <v>-62.72878200000002</v>
       </c>
       <c r="Q52">
-        <v>37.63014999999999</v>
+        <v>-4.728782000000017</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1396335528222648</v>
+        <v>0.1444491330312743</v>
       </c>
       <c r="T52">
-        <v>1.828990596805965</v>
+        <v>1.922855218314289</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.2024878629737079</v>
+        <v>0.1451313290199023</v>
       </c>
       <c r="W52">
-        <v>0.1170747817154597</v>
+        <v>0.1716576291328036</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8099514518948314</v>
+        <v>0.5805253160796093</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1583254660430543</v>
+        <v>0.1598754660430542</v>
       </c>
       <c r="C53">
-        <v>-178.1429257456269</v>
+        <v>-208.0022934703835</v>
       </c>
       <c r="D53">
-        <v>764.627074254373</v>
+        <v>754.2377065296165</v>
       </c>
       <c r="E53">
-        <v>136.27</v>
+        <v>155.74</v>
       </c>
       <c r="F53">
-        <v>992.97</v>
+        <v>1012.44</v>
       </c>
       <c r="G53">
         <v>50.2</v>
@@ -5633,37 +5633,37 @@
         <v>115.75</v>
       </c>
       <c r="M53">
-        <v>199.388376</v>
+        <v>203.297952</v>
       </c>
       <c r="N53">
-        <v>-83.63837600000002</v>
+        <v>-87.54795200000001</v>
       </c>
       <c r="O53">
-        <v>-20.90959400000001</v>
+        <v>-21.886988</v>
       </c>
       <c r="P53">
-        <v>-62.72878200000002</v>
+        <v>-65.66096400000001</v>
       </c>
       <c r="Q53">
-        <v>-4.728782000000017</v>
+        <v>-7.660964000000007</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1444491330312743</v>
+        <v>0.1465043233027592</v>
       </c>
       <c r="T53">
-        <v>1.922855218314289</v>
+        <v>1.96291470202917</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1451313290199023</v>
+        <v>0.1423403419233658</v>
       </c>
       <c r="W53">
-        <v>0.1716576291328036</v>
+        <v>0.1722180593417882</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5805253160796093</v>
+        <v>0.569361367693463</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1598754660430542</v>
+        <v>0.1614254660430542</v>
       </c>
       <c r="C54">
-        <v>-208.0022934703835</v>
+        <v>-237.5831149453481</v>
       </c>
       <c r="D54">
-        <v>754.2377065296165</v>
+        <v>744.1268850546519</v>
       </c>
       <c r="E54">
-        <v>155.74</v>
+        <v>175.21</v>
       </c>
       <c r="F54">
-        <v>1012.44</v>
+        <v>1031.91</v>
       </c>
       <c r="G54">
         <v>50.2</v>
@@ -5715,37 +5715,37 @@
         <v>115.75</v>
       </c>
       <c r="M54">
-        <v>203.297952</v>
+        <v>207.207528</v>
       </c>
       <c r="N54">
-        <v>-87.54795200000001</v>
+        <v>-91.45752800000002</v>
       </c>
       <c r="O54">
-        <v>-21.886988</v>
+        <v>-22.86438200000001</v>
       </c>
       <c r="P54">
-        <v>-65.66096400000001</v>
+        <v>-68.59314600000002</v>
       </c>
       <c r="Q54">
-        <v>-7.660964000000007</v>
+        <v>-10.59314600000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1465043233027592</v>
+        <v>0.1486469684794136</v>
       </c>
       <c r="T54">
-        <v>1.96291470202917</v>
+        <v>2.004678844625535</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1423403419233658</v>
+        <v>0.139654675094623</v>
       </c>
       <c r="W54">
-        <v>0.1722180593417882</v>
+        <v>0.1727573412409997</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.569361367693463</v>
+        <v>0.5586187003784919</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1614254660430542</v>
+        <v>0.1629754660430542</v>
       </c>
       <c r="C55">
-        <v>-237.5831149453481</v>
+        <v>-266.8964440208298</v>
       </c>
       <c r="D55">
-        <v>744.1268850546519</v>
+        <v>734.2835559791703</v>
       </c>
       <c r="E55">
-        <v>175.21</v>
+        <v>194.6800000000001</v>
       </c>
       <c r="F55">
-        <v>1031.91</v>
+        <v>1051.38</v>
       </c>
       <c r="G55">
         <v>50.2</v>
@@ -5797,37 +5797,37 @@
         <v>115.75</v>
       </c>
       <c r="M55">
-        <v>207.207528</v>
+        <v>211.117104</v>
       </c>
       <c r="N55">
-        <v>-91.45752800000002</v>
+        <v>-95.36710400000004</v>
       </c>
       <c r="O55">
-        <v>-22.86438200000001</v>
+        <v>-23.84177600000001</v>
       </c>
       <c r="P55">
-        <v>-68.59314600000002</v>
+        <v>-71.52532800000003</v>
       </c>
       <c r="Q55">
-        <v>-10.59314600000002</v>
+        <v>-13.52532800000003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1486469684794136</v>
+        <v>0.1508827721420096</v>
       </c>
       <c r="T55">
-        <v>2.004678844625535</v>
+        <v>2.048258819508699</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.139654675094623</v>
+        <v>0.1370684774076855</v>
       </c>
       <c r="W55">
-        <v>0.1727573412409997</v>
+        <v>0.1732766497365368</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5586187003784919</v>
+        <v>0.5482739096307421</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1629754660430542</v>
+        <v>0.1645254660430542</v>
       </c>
       <c r="C56">
-        <v>-266.8964440208298</v>
+        <v>-295.9527573005349</v>
       </c>
       <c r="D56">
-        <v>734.2835559791703</v>
+        <v>724.6972426994652</v>
       </c>
       <c r="E56">
-        <v>194.6800000000001</v>
+        <v>214.1500000000001</v>
       </c>
       <c r="F56">
-        <v>1051.38</v>
+        <v>1070.85</v>
       </c>
       <c r="G56">
         <v>50.2</v>
@@ -5879,37 +5879,37 @@
         <v>115.75</v>
       </c>
       <c r="M56">
-        <v>211.117104</v>
+        <v>215.02668</v>
       </c>
       <c r="N56">
-        <v>-95.36710400000004</v>
+        <v>-99.27668000000003</v>
       </c>
       <c r="O56">
-        <v>-23.84177600000001</v>
+        <v>-24.81917000000001</v>
       </c>
       <c r="P56">
-        <v>-71.52532800000003</v>
+        <v>-74.45751000000001</v>
       </c>
       <c r="Q56">
-        <v>-13.52532800000003</v>
+        <v>-16.45751000000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1508827721420096</v>
+        <v>0.1532179448562765</v>
       </c>
       <c r="T56">
-        <v>2.048258819508699</v>
+        <v>2.093775682164448</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1370684774076855</v>
+        <v>0.1345763232730003</v>
       </c>
       <c r="W56">
-        <v>0.1732766497365368</v>
+        <v>0.1737770742867815</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5482739096307421</v>
+        <v>0.5383052930920014</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1645254660430542</v>
+        <v>0.1660754660430542</v>
       </c>
       <c r="C57">
-        <v>-295.9527573005349</v>
+        <v>-324.7619913366939</v>
       </c>
       <c r="D57">
-        <v>724.6972426994652</v>
+        <v>715.3580086633062</v>
       </c>
       <c r="E57">
-        <v>214.1500000000001</v>
+        <v>233.6200000000001</v>
       </c>
       <c r="F57">
-        <v>1070.85</v>
+        <v>1090.32</v>
       </c>
       <c r="G57">
         <v>50.2</v>
@@ -5961,37 +5961,37 @@
         <v>115.75</v>
       </c>
       <c r="M57">
-        <v>215.02668</v>
+        <v>218.936256</v>
       </c>
       <c r="N57">
-        <v>-99.27668000000003</v>
+        <v>-103.186256</v>
       </c>
       <c r="O57">
-        <v>-24.81917000000001</v>
+        <v>-25.79656400000001</v>
       </c>
       <c r="P57">
-        <v>-74.45751000000001</v>
+        <v>-77.38969200000003</v>
       </c>
       <c r="Q57">
-        <v>-16.45751000000001</v>
+        <v>-19.38969200000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1532179448562765</v>
+        <v>0.1556592617848282</v>
       </c>
       <c r="T57">
-        <v>2.093775682164448</v>
+        <v>2.141361493122731</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1345763232730003</v>
+        <v>0.1321731746431253</v>
       </c>
       <c r="W57">
-        <v>0.1737770742867815</v>
+        <v>0.1742596265316604</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5383052930920014</v>
+        <v>0.5286926985725013</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1660754660430542</v>
+        <v>0.1676254660430543</v>
       </c>
       <c r="C58">
-        <v>-324.7619913366939</v>
+        <v>-353.3335769857591</v>
       </c>
       <c r="D58">
-        <v>715.3580086633062</v>
+        <v>706.256423014241</v>
       </c>
       <c r="E58">
-        <v>233.6200000000001</v>
+        <v>253.0900000000001</v>
       </c>
       <c r="F58">
-        <v>1090.32</v>
+        <v>1109.79</v>
       </c>
       <c r="G58">
         <v>50.2</v>
@@ -6043,37 +6043,37 @@
         <v>115.75</v>
       </c>
       <c r="M58">
-        <v>218.936256</v>
+        <v>222.8458320000001</v>
       </c>
       <c r="N58">
-        <v>-103.186256</v>
+        <v>-107.0958320000001</v>
       </c>
       <c r="O58">
-        <v>-25.79656400000001</v>
+        <v>-26.77395800000001</v>
       </c>
       <c r="P58">
-        <v>-77.38969200000003</v>
+        <v>-80.32187400000004</v>
       </c>
       <c r="Q58">
-        <v>-19.38969200000003</v>
+        <v>-22.32187400000004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1556592617848282</v>
+        <v>0.1582141283379637</v>
       </c>
       <c r="T58">
-        <v>2.141361493122731</v>
+        <v>2.191160597613957</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1321731746431253</v>
+        <v>0.1298543470178073</v>
       </c>
       <c r="W58">
-        <v>0.1742596265316604</v>
+        <v>0.1747252471188243</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5286926985725013</v>
+        <v>0.5194173880712293</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1676254660430543</v>
+        <v>0.1691754660430543</v>
       </c>
       <c r="C59">
-        <v>-353.3335769857591</v>
+        <v>-381.6764711743821</v>
       </c>
       <c r="D59">
-        <v>706.256423014241</v>
+        <v>697.3835288256181</v>
       </c>
       <c r="E59">
-        <v>253.0900000000001</v>
+        <v>272.5600000000002</v>
       </c>
       <c r="F59">
-        <v>1109.79</v>
+        <v>1129.26</v>
       </c>
       <c r="G59">
         <v>50.2</v>
@@ -6125,37 +6125,37 @@
         <v>115.75</v>
       </c>
       <c r="M59">
-        <v>222.8458320000001</v>
+        <v>226.755408</v>
       </c>
       <c r="N59">
-        <v>-107.0958320000001</v>
+        <v>-111.005408</v>
       </c>
       <c r="O59">
-        <v>-26.77395800000001</v>
+        <v>-27.75135200000001</v>
       </c>
       <c r="P59">
-        <v>-80.32187400000004</v>
+        <v>-83.25405600000003</v>
       </c>
       <c r="Q59">
-        <v>-22.32187400000004</v>
+        <v>-25.25405600000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1582141283379637</v>
+        <v>0.1608906552031533</v>
       </c>
       <c r="T59">
-        <v>2.191160597613957</v>
+        <v>2.243331088033337</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1298543470178073</v>
+        <v>0.1276154789657762</v>
       </c>
       <c r="W59">
-        <v>0.1747252471188243</v>
+        <v>0.1751748118236721</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5194173880712293</v>
+        <v>0.5104619158631047</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1691754660430543</v>
+        <v>0.1707254660430542</v>
       </c>
       <c r="C60">
-        <v>-381.6764711743818</v>
+        <v>-409.7991863005931</v>
       </c>
       <c r="D60">
-        <v>697.3835288256181</v>
+        <v>688.7308136994069</v>
       </c>
       <c r="E60">
-        <v>272.5599999999999</v>
+        <v>292.03</v>
       </c>
       <c r="F60">
-        <v>1129.26</v>
+        <v>1148.73</v>
       </c>
       <c r="G60">
         <v>50.2</v>
@@ -6207,37 +6207,37 @@
         <v>115.75</v>
       </c>
       <c r="M60">
-        <v>226.755408</v>
+        <v>230.664984</v>
       </c>
       <c r="N60">
-        <v>-111.005408</v>
+        <v>-114.914984</v>
       </c>
       <c r="O60">
-        <v>-27.751352</v>
+        <v>-28.728746</v>
       </c>
       <c r="P60">
-        <v>-83.25405600000002</v>
+        <v>-86.186238</v>
       </c>
       <c r="Q60">
-        <v>-25.25405600000002</v>
+        <v>-28.186238</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1608906552031533</v>
+        <v>0.1636977443544498</v>
       </c>
       <c r="T60">
-        <v>2.243331088033337</v>
+        <v>2.298046480424394</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1276154789657762</v>
+        <v>0.1254525047460173</v>
       </c>
       <c r="W60">
-        <v>0.1751748118236721</v>
+        <v>0.1756091370469997</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5104619158631047</v>
+        <v>0.5018100189840691</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1707254660430542</v>
+        <v>0.1938489772658261</v>
       </c>
       <c r="C61">
-        <v>-409.7991863005931</v>
+        <v>-536.8408493689009</v>
       </c>
       <c r="D61">
-        <v>688.7308136994069</v>
+        <v>581.1591506310991</v>
       </c>
       <c r="E61">
-        <v>292.03</v>
+        <v>311.5</v>
       </c>
       <c r="F61">
-        <v>1148.73</v>
+        <v>1168.2</v>
       </c>
       <c r="G61">
         <v>50.2</v>
@@ -6289,45 +6289,45 @@
         <v>115.75</v>
       </c>
       <c r="M61">
-        <v>230.664984</v>
+        <v>275.46156</v>
       </c>
       <c r="N61">
-        <v>-114.914984</v>
+        <v>-159.71156</v>
       </c>
       <c r="O61">
-        <v>-28.728746</v>
+        <v>-39.92789</v>
       </c>
       <c r="P61">
-        <v>-86.186238</v>
+        <v>-119.78367</v>
       </c>
       <c r="Q61">
-        <v>-28.186238</v>
+        <v>-61.78367000000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1636977443544498</v>
+        <v>0.1680789660202406</v>
       </c>
       <c r="T61">
-        <v>2.298046480424394</v>
+        <v>2.383444645454256</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1254525047460173</v>
+        <v>0.1050509552040582</v>
       </c>
       <c r="W61">
-        <v>0.1756091370469997</v>
+        <v>0.2110289847628831</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5018100189840691</v>
+        <v>0.4202038208162329</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1938489772658261</v>
+        <v>0.1957489772658261</v>
       </c>
       <c r="C62">
-        <v>-536.8408493689009</v>
+        <v>-563.6747034366856</v>
       </c>
       <c r="D62">
-        <v>581.1591506310991</v>
+        <v>573.7952965633144</v>
       </c>
       <c r="E62">
-        <v>311.5</v>
+        <v>330.97</v>
       </c>
       <c r="F62">
-        <v>1168.2</v>
+        <v>1187.67</v>
       </c>
       <c r="G62">
         <v>50.2</v>
@@ -6371,37 +6371,37 @@
         <v>115.75</v>
       </c>
       <c r="M62">
-        <v>275.46156</v>
+        <v>280.052586</v>
       </c>
       <c r="N62">
-        <v>-159.71156</v>
+        <v>-164.302586</v>
       </c>
       <c r="O62">
-        <v>-39.92789</v>
+        <v>-41.0756465</v>
       </c>
       <c r="P62">
-        <v>-119.78367</v>
+        <v>-123.2269395</v>
       </c>
       <c r="Q62">
-        <v>-61.78367000000001</v>
+        <v>-65.22693950000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1680789660202406</v>
+        <v>0.1712143241233237</v>
       </c>
       <c r="T62">
-        <v>2.383444645454256</v>
+        <v>2.444558610722314</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.1050509552040582</v>
+        <v>0.1033288083974343</v>
       </c>
       <c r="W62">
-        <v>0.2110289847628831</v>
+        <v>0.211435066979885</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4202038208162329</v>
+        <v>0.4133152335897373</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1957489772658261</v>
+        <v>0.1976489772658261</v>
       </c>
       <c r="C63">
-        <v>-563.6747034366856</v>
+        <v>-590.324278058132</v>
       </c>
       <c r="D63">
-        <v>573.7952965633144</v>
+        <v>566.6157219418681</v>
       </c>
       <c r="E63">
-        <v>330.97</v>
+        <v>350.4400000000001</v>
       </c>
       <c r="F63">
-        <v>1187.67</v>
+        <v>1207.14</v>
       </c>
       <c r="G63">
         <v>50.2</v>
@@ -6453,37 +6453,37 @@
         <v>115.75</v>
       </c>
       <c r="M63">
-        <v>280.052586</v>
+        <v>284.643612</v>
       </c>
       <c r="N63">
-        <v>-164.302586</v>
+        <v>-168.893612</v>
       </c>
       <c r="O63">
-        <v>-41.0756465</v>
+        <v>-42.223403</v>
       </c>
       <c r="P63">
-        <v>-123.2269395</v>
+        <v>-126.670209</v>
       </c>
       <c r="Q63">
-        <v>-65.22693950000001</v>
+        <v>-68.67020900000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1712143241233237</v>
+        <v>0.1745147010739375</v>
       </c>
       <c r="T63">
-        <v>2.444558610722314</v>
+        <v>2.508889100478164</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1033288083974343</v>
+        <v>0.1016622147136047</v>
       </c>
       <c r="W63">
-        <v>0.211435066979885</v>
+        <v>0.211828049770532</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4133152335897373</v>
+        <v>0.4066488588544189</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1976489772658261</v>
+        <v>0.1995489772658261</v>
       </c>
       <c r="C64">
-        <v>-590.324278058132</v>
+        <v>-616.7964051020612</v>
       </c>
       <c r="D64">
-        <v>566.6157219418681</v>
+        <v>559.6135948979387</v>
       </c>
       <c r="E64">
-        <v>350.4400000000001</v>
+        <v>369.9099999999999</v>
       </c>
       <c r="F64">
-        <v>1207.14</v>
+        <v>1226.61</v>
       </c>
       <c r="G64">
         <v>50.2</v>
@@ -6535,37 +6535,37 @@
         <v>115.75</v>
       </c>
       <c r="M64">
-        <v>284.643612</v>
+        <v>289.234638</v>
       </c>
       <c r="N64">
-        <v>-168.893612</v>
+        <v>-173.484638</v>
       </c>
       <c r="O64">
-        <v>-42.223403</v>
+        <v>-43.37115949999999</v>
       </c>
       <c r="P64">
-        <v>-126.670209</v>
+        <v>-130.1134785</v>
       </c>
       <c r="Q64">
-        <v>-68.67020900000001</v>
+        <v>-72.11347849999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1745147010739375</v>
+        <v>0.1779934767786385</v>
       </c>
       <c r="T64">
-        <v>2.508889100478164</v>
+        <v>2.576696914004601</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1016622147136047</v>
+        <v>0.1000485287657698</v>
       </c>
       <c r="W64">
-        <v>0.211828049770532</v>
+        <v>0.2122085569170315</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4066488588544189</v>
+        <v>0.400194115063079</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1995489772658261</v>
+        <v>0.2014489772658261</v>
       </c>
       <c r="C65">
-        <v>-616.7964051020612</v>
+        <v>-643.0975828520454</v>
       </c>
       <c r="D65">
-        <v>559.6135948979387</v>
+        <v>552.7824171479544</v>
       </c>
       <c r="E65">
-        <v>369.9099999999999</v>
+        <v>389.3799999999999</v>
       </c>
       <c r="F65">
-        <v>1226.61</v>
+        <v>1246.08</v>
       </c>
       <c r="G65">
         <v>50.2</v>
@@ -6617,37 +6617,37 @@
         <v>115.75</v>
       </c>
       <c r="M65">
-        <v>289.234638</v>
+        <v>293.825664</v>
       </c>
       <c r="N65">
-        <v>-173.484638</v>
+        <v>-178.075664</v>
       </c>
       <c r="O65">
-        <v>-43.37115949999999</v>
+        <v>-44.518916</v>
       </c>
       <c r="P65">
-        <v>-130.1134785</v>
+        <v>-133.556748</v>
       </c>
       <c r="Q65">
-        <v>-72.11347849999999</v>
+        <v>-75.55674800000003</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1779934767786385</v>
+        <v>0.1816655178002674</v>
       </c>
       <c r="T65">
-        <v>2.576696914004601</v>
+        <v>2.648271828282506</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1000485287657698</v>
+        <v>0.0984852705038046</v>
       </c>
       <c r="W65">
-        <v>0.2122085569170315</v>
+        <v>0.2125771732152029</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.400194115063079</v>
+        <v>0.3939410820152184</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2014489772658261</v>
+        <v>0.2033489772658261</v>
       </c>
       <c r="C66">
-        <v>-643.0975828520454</v>
+        <v>-669.2339961211648</v>
       </c>
       <c r="D66">
-        <v>552.7824171479544</v>
+        <v>546.1160038788352</v>
       </c>
       <c r="E66">
-        <v>389.3799999999999</v>
+        <v>408.8499999999999</v>
       </c>
       <c r="F66">
-        <v>1246.08</v>
+        <v>1265.55</v>
       </c>
       <c r="G66">
         <v>50.2</v>
@@ -6699,37 +6699,37 @@
         <v>115.75</v>
       </c>
       <c r="M66">
-        <v>293.825664</v>
+        <v>298.41669</v>
       </c>
       <c r="N66">
-        <v>-178.075664</v>
+        <v>-182.66669</v>
       </c>
       <c r="O66">
-        <v>-44.518916</v>
+        <v>-45.6666725</v>
       </c>
       <c r="P66">
-        <v>-133.556748</v>
+        <v>-137.0000175</v>
       </c>
       <c r="Q66">
-        <v>-75.55674800000003</v>
+        <v>-79.00001750000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1816655178002674</v>
+        <v>0.1855473897374179</v>
       </c>
       <c r="T66">
-        <v>2.648271828282506</v>
+        <v>2.723936737662007</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.0984852705038046</v>
+        <v>0.09697011249605375</v>
       </c>
       <c r="W66">
-        <v>0.2125771732152029</v>
+        <v>0.2129344474734305</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3939410820152184</v>
+        <v>0.387880449984215</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2033489772658261</v>
+        <v>0.2052489772658261</v>
       </c>
       <c r="C67">
-        <v>-669.2339961211648</v>
+        <v>-695.2115349286414</v>
       </c>
       <c r="D67">
-        <v>546.1160038788352</v>
+        <v>539.6084650713585</v>
       </c>
       <c r="E67">
-        <v>408.8499999999999</v>
+        <v>428.3199999999999</v>
       </c>
       <c r="F67">
-        <v>1265.55</v>
+        <v>1285.02</v>
       </c>
       <c r="G67">
         <v>50.2</v>
@@ -6781,37 +6781,37 @@
         <v>115.75</v>
       </c>
       <c r="M67">
-        <v>298.41669</v>
+        <v>303.007716</v>
       </c>
       <c r="N67">
-        <v>-182.66669</v>
+        <v>-187.257716</v>
       </c>
       <c r="O67">
-        <v>-45.6666725</v>
+        <v>-46.814429</v>
       </c>
       <c r="P67">
-        <v>-137.0000175</v>
+        <v>-140.443287</v>
       </c>
       <c r="Q67">
-        <v>-79.00001750000001</v>
+        <v>-82.443287</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1855473897374179</v>
+        <v>0.189657607082636</v>
       </c>
       <c r="T67">
-        <v>2.723936737662007</v>
+        <v>2.80405252406383</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.09697011249605375</v>
+        <v>0.09550086836732566</v>
       </c>
       <c r="W67">
-        <v>0.2129344474734305</v>
+        <v>0.2132808952389846</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.387880449984215</v>
+        <v>0.3820034734693026</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2052489772658261</v>
+        <v>0.2071489772658261</v>
       </c>
       <c r="C68">
-        <v>-695.2115349286414</v>
+        <v>-721.0358118568827</v>
       </c>
       <c r="D68">
-        <v>539.6084650713585</v>
+        <v>533.2541881431173</v>
       </c>
       <c r="E68">
-        <v>428.3199999999999</v>
+        <v>447.79</v>
       </c>
       <c r="F68">
-        <v>1285.02</v>
+        <v>1304.49</v>
       </c>
       <c r="G68">
         <v>50.2</v>
@@ -6863,37 +6863,37 @@
         <v>115.75</v>
       </c>
       <c r="M68">
-        <v>303.007716</v>
+        <v>307.598742</v>
       </c>
       <c r="N68">
-        <v>-187.257716</v>
+        <v>-191.848742</v>
       </c>
       <c r="O68">
-        <v>-46.814429</v>
+        <v>-47.9621855</v>
       </c>
       <c r="P68">
-        <v>-140.443287</v>
+        <v>-143.8865565</v>
       </c>
       <c r="Q68">
-        <v>-82.443287</v>
+        <v>-85.88655650000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.189657607082636</v>
+        <v>0.1940169285093826</v>
       </c>
       <c r="T68">
-        <v>2.80405252406383</v>
+        <v>2.889023812671825</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09550086836732566</v>
+        <v>0.09407548227229096</v>
       </c>
       <c r="W68">
-        <v>0.2132808952389846</v>
+        <v>0.2136170012801938</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3820034734693026</v>
+        <v>0.3763019290891638</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2071489772658261</v>
+        <v>0.2090489772658261</v>
       </c>
       <c r="C69">
-        <v>-721.0358118568827</v>
+        <v>-746.7121781964532</v>
       </c>
       <c r="D69">
-        <v>533.2541881431173</v>
+        <v>527.0478218035468</v>
       </c>
       <c r="E69">
-        <v>447.79</v>
+        <v>467.26</v>
       </c>
       <c r="F69">
-        <v>1304.49</v>
+        <v>1323.96</v>
       </c>
       <c r="G69">
         <v>50.2</v>
@@ -6945,37 +6945,37 @@
         <v>115.75</v>
       </c>
       <c r="M69">
-        <v>307.598742</v>
+        <v>312.189768</v>
       </c>
       <c r="N69">
-        <v>-191.848742</v>
+        <v>-196.439768</v>
       </c>
       <c r="O69">
-        <v>-47.9621855</v>
+        <v>-49.109942</v>
       </c>
       <c r="P69">
-        <v>-143.8865565</v>
+        <v>-147.329826</v>
       </c>
       <c r="Q69">
-        <v>-85.88655650000001</v>
+        <v>-89.32982600000003</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1940169285093826</v>
+        <v>0.1986487075253008</v>
       </c>
       <c r="T69">
-        <v>2.889023812671825</v>
+        <v>2.97930580681782</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09407548227229096</v>
+        <v>0.09269201929769844</v>
       </c>
       <c r="W69">
-        <v>0.2136170012801938</v>
+        <v>0.2139432218496027</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3763019290891638</v>
+        <v>0.3707680771907937</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2090489772658261</v>
+        <v>0.2109489772658261</v>
       </c>
       <c r="C70">
-        <v>-746.7121781964532</v>
+        <v>-772.2457389765779</v>
       </c>
       <c r="D70">
-        <v>527.0478218035468</v>
+        <v>520.9842610234222</v>
       </c>
       <c r="E70">
-        <v>467.26</v>
+        <v>486.73</v>
       </c>
       <c r="F70">
-        <v>1323.96</v>
+        <v>1343.43</v>
       </c>
       <c r="G70">
         <v>50.2</v>
@@ -7027,37 +7027,37 @@
         <v>115.75</v>
       </c>
       <c r="M70">
-        <v>312.189768</v>
+        <v>316.780794</v>
       </c>
       <c r="N70">
-        <v>-196.439768</v>
+        <v>-201.030794</v>
       </c>
       <c r="O70">
-        <v>-49.109942</v>
+        <v>-50.2576985</v>
       </c>
       <c r="P70">
-        <v>-147.329826</v>
+        <v>-150.7730955</v>
       </c>
       <c r="Q70">
-        <v>-89.32982600000003</v>
+        <v>-92.77309550000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1986487075253008</v>
+        <v>0.2035793109938589</v>
       </c>
       <c r="T70">
-        <v>2.97930580681782</v>
+        <v>3.075412445747427</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09269201929769844</v>
+        <v>0.09134865669918107</v>
       </c>
       <c r="W70">
-        <v>0.2139432218496027</v>
+        <v>0.2142599867503331</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3707680771907937</v>
+        <v>0.3653946267967243</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2109489772658261</v>
+        <v>0.2128489772658261</v>
       </c>
       <c r="C71">
-        <v>-772.2457389765779</v>
+        <v>-797.6413669699136</v>
       </c>
       <c r="D71">
-        <v>520.9842610234222</v>
+        <v>515.0586330300864</v>
       </c>
       <c r="E71">
-        <v>486.73</v>
+        <v>506.2</v>
       </c>
       <c r="F71">
-        <v>1343.43</v>
+        <v>1362.9</v>
       </c>
       <c r="G71">
         <v>50.2</v>
@@ -7109,37 +7109,37 @@
         <v>115.75</v>
       </c>
       <c r="M71">
-        <v>316.780794</v>
+        <v>321.37182</v>
       </c>
       <c r="N71">
-        <v>-201.030794</v>
+        <v>-205.62182</v>
       </c>
       <c r="O71">
-        <v>-50.2576985</v>
+        <v>-51.405455</v>
       </c>
       <c r="P71">
-        <v>-150.7730955</v>
+        <v>-154.216365</v>
       </c>
       <c r="Q71">
-        <v>-92.77309550000001</v>
+        <v>-96.216365</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2035793109938589</v>
+        <v>0.2088386213603209</v>
       </c>
       <c r="T71">
-        <v>3.075412445747427</v>
+        <v>3.177926193939008</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09134865669918107</v>
+        <v>0.09004367588919276</v>
       </c>
       <c r="W71">
-        <v>0.2142599867503331</v>
+        <v>0.2145677012253284</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3653946267967243</v>
+        <v>0.3601747035567711</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2128489772658261</v>
+        <v>0.2147489772658261</v>
       </c>
       <c r="C72">
-        <v>-797.6413669699136</v>
+        <v>-822.9037157523358</v>
       </c>
       <c r="D72">
-        <v>515.0586330300864</v>
+        <v>509.2662842476644</v>
       </c>
       <c r="E72">
-        <v>506.2</v>
+        <v>525.6700000000001</v>
       </c>
       <c r="F72">
-        <v>1362.9</v>
+        <v>1382.37</v>
       </c>
       <c r="G72">
         <v>50.2</v>
@@ -7191,37 +7191,37 @@
         <v>115.75</v>
       </c>
       <c r="M72">
-        <v>321.37182</v>
+        <v>325.962846</v>
       </c>
       <c r="N72">
-        <v>-205.62182</v>
+        <v>-210.212846</v>
       </c>
       <c r="O72">
-        <v>-51.405455</v>
+        <v>-52.5532115</v>
       </c>
       <c r="P72">
-        <v>-154.216365</v>
+        <v>-157.6596345</v>
       </c>
       <c r="Q72">
-        <v>-96.216365</v>
+        <v>-99.65963450000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2088386213603209</v>
+        <v>0.2144606427865388</v>
       </c>
       <c r="T72">
-        <v>3.177926193939008</v>
+        <v>3.287509855798974</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09004367588919276</v>
+        <v>0.08877545510202105</v>
       </c>
       <c r="W72">
-        <v>0.2145677012253284</v>
+        <v>0.2148667476869434</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3601747035567711</v>
+        <v>0.3551018204080841</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2147489772658261</v>
+        <v>0.2166489772658261</v>
       </c>
       <c r="C73">
-        <v>-822.9037157523355</v>
+        <v>-848.0372318912997</v>
       </c>
       <c r="D73">
-        <v>509.2662842476644</v>
+        <v>503.6027681087002</v>
       </c>
       <c r="E73">
-        <v>525.6699999999998</v>
+        <v>545.1399999999999</v>
       </c>
       <c r="F73">
-        <v>1382.37</v>
+        <v>1401.84</v>
       </c>
       <c r="G73">
         <v>50.2</v>
@@ -7273,37 +7273,37 @@
         <v>115.75</v>
       </c>
       <c r="M73">
-        <v>325.962846</v>
+        <v>330.553872</v>
       </c>
       <c r="N73">
-        <v>-210.212846</v>
+        <v>-214.803872</v>
       </c>
       <c r="O73">
-        <v>-52.5532115</v>
+        <v>-53.700968</v>
       </c>
       <c r="P73">
-        <v>-157.6596345</v>
+        <v>-161.102904</v>
       </c>
       <c r="Q73">
-        <v>-99.65963450000001</v>
+        <v>-103.102904</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2144606427865388</v>
+        <v>0.2204842371717723</v>
       </c>
       <c r="T73">
-        <v>3.287509855798973</v>
+        <v>3.404920922077508</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.08877545510202105</v>
+        <v>0.08754246267004853</v>
       </c>
       <c r="W73">
-        <v>0.2148667476869434</v>
+        <v>0.2151574873024026</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3551018204080841</v>
+        <v>0.3501698506801941</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2166489772658261</v>
+        <v>0.2185489772658261</v>
       </c>
       <c r="C74">
-        <v>-848.0372318912997</v>
+        <v>-873.0461663298763</v>
       </c>
       <c r="D74">
-        <v>503.6027681087002</v>
+        <v>498.0638336701236</v>
       </c>
       <c r="E74">
-        <v>545.1399999999999</v>
+        <v>564.6099999999999</v>
       </c>
       <c r="F74">
-        <v>1401.84</v>
+        <v>1421.31</v>
       </c>
       <c r="G74">
         <v>50.2</v>
@@ -7355,37 +7355,37 @@
         <v>115.75</v>
       </c>
       <c r="M74">
-        <v>330.553872</v>
+        <v>335.144898</v>
       </c>
       <c r="N74">
-        <v>-214.803872</v>
+        <v>-219.394898</v>
       </c>
       <c r="O74">
-        <v>-53.700968</v>
+        <v>-54.8487245</v>
       </c>
       <c r="P74">
-        <v>-161.102904</v>
+        <v>-164.5461735</v>
       </c>
       <c r="Q74">
-        <v>-103.102904</v>
+        <v>-106.5461735</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2204842371717723</v>
+        <v>0.2269540237336898</v>
       </c>
       <c r="T74">
-        <v>3.404920922077508</v>
+        <v>3.531029104376675</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.08754246267004853</v>
+        <v>0.0863432508526506</v>
       </c>
       <c r="W74">
-        <v>0.2151574873024026</v>
+        <v>0.215440261448945</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3501698506801941</v>
+        <v>0.3453730034106024</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2185489772658261</v>
+        <v>0.2204489772658261</v>
       </c>
       <c r="C75">
-        <v>-873.0461663298763</v>
+        <v>-897.9345850277015</v>
       </c>
       <c r="D75">
-        <v>498.0638336701236</v>
+        <v>492.6454149722985</v>
       </c>
       <c r="E75">
-        <v>564.6099999999999</v>
+        <v>584.0799999999999</v>
       </c>
       <c r="F75">
-        <v>1421.31</v>
+        <v>1440.78</v>
       </c>
       <c r="G75">
         <v>50.2</v>
@@ -7437,37 +7437,37 @@
         <v>115.75</v>
       </c>
       <c r="M75">
-        <v>335.144898</v>
+        <v>339.735924</v>
       </c>
       <c r="N75">
-        <v>-219.394898</v>
+        <v>-223.985924</v>
       </c>
       <c r="O75">
-        <v>-54.8487245</v>
+        <v>-55.996481</v>
       </c>
       <c r="P75">
-        <v>-164.5461735</v>
+        <v>-167.989443</v>
       </c>
       <c r="Q75">
-        <v>-106.5461735</v>
+        <v>-109.989443</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2269540237336898</v>
+        <v>0.2339214861849855</v>
       </c>
       <c r="T75">
-        <v>3.531029104376675</v>
+        <v>3.66683791608347</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.0863432508526506</v>
+        <v>0.08517645016545262</v>
       </c>
       <c r="W75">
-        <v>0.215440261448945</v>
+        <v>0.2157153930509863</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3453730034106024</v>
+        <v>0.3407058006618104</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2204489772658261</v>
+        <v>0.2223489772658261</v>
       </c>
       <c r="C76">
-        <v>-897.9345850277015</v>
+        <v>-922.7063789148336</v>
       </c>
       <c r="D76">
-        <v>492.6454149722985</v>
+        <v>487.3436210851664</v>
       </c>
       <c r="E76">
-        <v>584.0799999999999</v>
+        <v>603.55</v>
       </c>
       <c r="F76">
-        <v>1440.78</v>
+        <v>1460.25</v>
       </c>
       <c r="G76">
         <v>50.2</v>
@@ -7519,37 +7519,37 @@
         <v>115.75</v>
       </c>
       <c r="M76">
-        <v>339.735924</v>
+        <v>344.32695</v>
       </c>
       <c r="N76">
-        <v>-223.985924</v>
+        <v>-228.57695</v>
       </c>
       <c r="O76">
-        <v>-55.996481</v>
+        <v>-57.1442375</v>
       </c>
       <c r="P76">
-        <v>-167.989443</v>
+        <v>-171.4327125</v>
       </c>
       <c r="Q76">
-        <v>-109.989443</v>
+        <v>-113.4327125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2339214861849855</v>
+        <v>0.241446345632385</v>
       </c>
       <c r="T76">
-        <v>3.66683791608347</v>
+        <v>3.813511432726809</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08517645016545262</v>
+        <v>0.08404076416324659</v>
       </c>
       <c r="W76">
-        <v>0.2157153930509863</v>
+        <v>0.2159831878103065</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3407058006618104</v>
+        <v>0.3361630566529863</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2223489772658261</v>
+        <v>0.2242489772658261</v>
       </c>
       <c r="C77">
-        <v>-922.7063789148336</v>
+        <v>-947.3652732097137</v>
       </c>
       <c r="D77">
-        <v>487.3436210851664</v>
+        <v>482.1547267902863</v>
       </c>
       <c r="E77">
-        <v>603.55</v>
+        <v>623.02</v>
       </c>
       <c r="F77">
-        <v>1460.25</v>
+        <v>1479.72</v>
       </c>
       <c r="G77">
         <v>50.2</v>
@@ -7601,37 +7601,37 @@
         <v>115.75</v>
       </c>
       <c r="M77">
-        <v>344.32695</v>
+        <v>348.917976</v>
       </c>
       <c r="N77">
-        <v>-228.57695</v>
+        <v>-233.167976</v>
       </c>
       <c r="O77">
-        <v>-57.1442375</v>
+        <v>-58.291994</v>
       </c>
       <c r="P77">
-        <v>-171.4327125</v>
+        <v>-174.875982</v>
       </c>
       <c r="Q77">
-        <v>-113.4327125</v>
+        <v>-116.875982</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.241446345632385</v>
+        <v>0.249598276700401</v>
       </c>
       <c r="T77">
-        <v>3.813511432726809</v>
+        <v>3.97240774242376</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08404076416324659</v>
+        <v>0.08293496463478281</v>
       </c>
       <c r="W77">
-        <v>0.2159831878103065</v>
+        <v>0.2162439353391182</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3361630566529863</v>
+        <v>0.3317398585391312</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2242489772658261</v>
+        <v>0.2261489772658261</v>
       </c>
       <c r="C78">
-        <v>-947.3652732097137</v>
+        <v>-971.9148361481342</v>
       </c>
       <c r="D78">
-        <v>482.1547267902863</v>
+        <v>477.0751638518658</v>
       </c>
       <c r="E78">
-        <v>623.02</v>
+        <v>642.49</v>
       </c>
       <c r="F78">
-        <v>1479.72</v>
+        <v>1499.19</v>
       </c>
       <c r="G78">
         <v>50.2</v>
@@ -7683,37 +7683,37 @@
         <v>115.75</v>
       </c>
       <c r="M78">
-        <v>348.917976</v>
+        <v>353.509002</v>
       </c>
       <c r="N78">
-        <v>-233.167976</v>
+        <v>-237.759002</v>
       </c>
       <c r="O78">
-        <v>-58.291994</v>
+        <v>-59.4397505</v>
       </c>
       <c r="P78">
-        <v>-174.875982</v>
+        <v>-178.3192515</v>
       </c>
       <c r="Q78">
-        <v>-116.875982</v>
+        <v>-120.3192515</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.249598276700401</v>
+        <v>0.2584590713395489</v>
       </c>
       <c r="T78">
-        <v>3.97240774242376</v>
+        <v>4.14512112252914</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08293496463478281</v>
+        <v>0.08185788717199342</v>
       </c>
       <c r="W78">
-        <v>0.2162439353391182</v>
+        <v>0.216497910204844</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3317398585391312</v>
+        <v>0.3274315486879738</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2261489772658261</v>
+        <v>0.2280489772658261</v>
       </c>
       <c r="C79">
-        <v>-971.9148361481342</v>
+        <v>-996.3584871661942</v>
       </c>
       <c r="D79">
-        <v>477.0751638518658</v>
+        <v>472.1015128338058</v>
       </c>
       <c r="E79">
-        <v>642.49</v>
+        <v>661.96</v>
       </c>
       <c r="F79">
-        <v>1499.19</v>
+        <v>1518.66</v>
       </c>
       <c r="G79">
         <v>50.2</v>
@@ -7765,37 +7765,37 @@
         <v>115.75</v>
       </c>
       <c r="M79">
-        <v>353.509002</v>
+        <v>358.100028</v>
       </c>
       <c r="N79">
-        <v>-237.759002</v>
+        <v>-242.350028</v>
       </c>
       <c r="O79">
-        <v>-59.4397505</v>
+        <v>-60.587507</v>
       </c>
       <c r="P79">
-        <v>-178.3192515</v>
+        <v>-181.762521</v>
       </c>
       <c r="Q79">
-        <v>-120.3192515</v>
+        <v>-123.762521</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2584590713395489</v>
+        <v>0.2681253927640739</v>
       </c>
       <c r="T79">
-        <v>4.14512112252914</v>
+        <v>4.333535719007738</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08185788717199342</v>
+        <v>0.08080842708004479</v>
       </c>
       <c r="W79">
-        <v>0.216497910204844</v>
+        <v>0.2167453728945254</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3274315486879738</v>
+        <v>0.3232337083201792</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2280489772658261</v>
+        <v>0.2299489772658261</v>
       </c>
       <c r="C80">
-        <v>-996.3584871661942</v>
+        <v>-1020.699504576676</v>
       </c>
       <c r="D80">
-        <v>472.1015128338058</v>
+        <v>467.230495423324</v>
       </c>
       <c r="E80">
-        <v>661.96</v>
+        <v>681.4300000000001</v>
       </c>
       <c r="F80">
-        <v>1518.66</v>
+        <v>1538.13</v>
       </c>
       <c r="G80">
         <v>50.2</v>
@@ -7847,37 +7847,37 @@
         <v>115.75</v>
       </c>
       <c r="M80">
-        <v>358.100028</v>
+        <v>362.6910540000001</v>
       </c>
       <c r="N80">
-        <v>-242.350028</v>
+        <v>-246.9410540000001</v>
       </c>
       <c r="O80">
-        <v>-60.587507</v>
+        <v>-61.73526350000002</v>
       </c>
       <c r="P80">
-        <v>-181.762521</v>
+        <v>-185.2057905</v>
       </c>
       <c r="Q80">
-        <v>-123.762521</v>
+        <v>-127.2057905</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2681253927640739</v>
+        <v>0.2787123162290298</v>
       </c>
       <c r="T80">
-        <v>4.333535719007738</v>
+        <v>4.539894562770011</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08080842708004479</v>
+        <v>0.0797855355980189</v>
       </c>
       <c r="W80">
-        <v>0.2167453728945254</v>
+        <v>0.2169865707059871</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3232337083201792</v>
+        <v>0.3191421423920756</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2299489772658261</v>
+        <v>0.2318489772658261</v>
       </c>
       <c r="C81">
-        <v>-1020.699504576676</v>
+        <v>-1044.94103277506</v>
       </c>
       <c r="D81">
-        <v>467.230495423324</v>
+        <v>462.4589672249404</v>
       </c>
       <c r="E81">
-        <v>681.4300000000001</v>
+        <v>700.9000000000001</v>
       </c>
       <c r="F81">
-        <v>1538.13</v>
+        <v>1557.6</v>
       </c>
       <c r="G81">
         <v>50.2</v>
@@ -7929,37 +7929,37 @@
         <v>115.75</v>
       </c>
       <c r="M81">
-        <v>362.6910540000001</v>
+        <v>367.2820800000001</v>
       </c>
       <c r="N81">
-        <v>-246.9410540000001</v>
+        <v>-251.5320800000001</v>
       </c>
       <c r="O81">
-        <v>-61.73526350000002</v>
+        <v>-62.88302000000002</v>
       </c>
       <c r="P81">
-        <v>-185.2057905</v>
+        <v>-188.64906</v>
       </c>
       <c r="Q81">
-        <v>-127.2057905</v>
+        <v>-130.64906</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2787123162290298</v>
+        <v>0.2903579320404813</v>
       </c>
       <c r="T81">
-        <v>4.539894562770011</v>
+        <v>4.766889290908513</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0797855355980189</v>
+        <v>0.07878821640304366</v>
       </c>
       <c r="W81">
-        <v>0.2169865707059871</v>
+        <v>0.2172217385721623</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3191421423920756</v>
+        <v>0.3151528656121747</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2318489772658261</v>
+        <v>0.2337489772658261</v>
       </c>
       <c r="C82">
-        <v>-1044.94103277506</v>
+        <v>-1069.086089008458</v>
       </c>
       <c r="D82">
-        <v>462.4589672249404</v>
+        <v>457.7839109915426</v>
       </c>
       <c r="E82">
-        <v>700.9000000000001</v>
+        <v>720.3700000000001</v>
       </c>
       <c r="F82">
-        <v>1557.6</v>
+        <v>1577.07</v>
       </c>
       <c r="G82">
         <v>50.2</v>
@@ -8011,37 +8011,37 @@
         <v>115.75</v>
       </c>
       <c r="M82">
-        <v>367.2820800000001</v>
+        <v>371.8731060000001</v>
       </c>
       <c r="N82">
-        <v>-251.5320800000001</v>
+        <v>-256.1231060000001</v>
       </c>
       <c r="O82">
-        <v>-62.88302000000002</v>
+        <v>-64.03077650000002</v>
       </c>
       <c r="P82">
-        <v>-188.64906</v>
+        <v>-192.0923295000001</v>
       </c>
       <c r="Q82">
-        <v>-130.64906</v>
+        <v>-134.0923295000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2903579320404813</v>
+        <v>0.3032294021478751</v>
       </c>
       <c r="T82">
-        <v>4.766889290908513</v>
+        <v>5.01777820095633</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.07878821640304366</v>
+        <v>0.07781552237337645</v>
       </c>
       <c r="W82">
-        <v>0.2172217385721623</v>
+        <v>0.2174510998243578</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3151528656121747</v>
+        <v>0.3112620894935059</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2337489772658261</v>
+        <v>0.2356489772658261</v>
       </c>
       <c r="C83">
-        <v>-1069.086089008458</v>
+        <v>-1093.137569738091</v>
       </c>
       <c r="D83">
-        <v>457.7839109915426</v>
+        <v>453.2024302619096</v>
       </c>
       <c r="E83">
-        <v>720.3700000000001</v>
+        <v>739.8400000000001</v>
       </c>
       <c r="F83">
-        <v>1577.07</v>
+        <v>1596.54</v>
       </c>
       <c r="G83">
         <v>50.2</v>
@@ -8093,37 +8093,37 @@
         <v>115.75</v>
       </c>
       <c r="M83">
-        <v>371.8731060000001</v>
+        <v>376.4641320000001</v>
       </c>
       <c r="N83">
-        <v>-256.1231060000001</v>
+        <v>-260.7141320000001</v>
       </c>
       <c r="O83">
-        <v>-64.03077650000002</v>
+        <v>-65.17853300000002</v>
       </c>
       <c r="P83">
-        <v>-192.0923295000001</v>
+        <v>-195.535599</v>
       </c>
       <c r="Q83">
-        <v>-134.0923295000001</v>
+        <v>-137.535599</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3032294021478751</v>
+        <v>0.3175310356005348</v>
       </c>
       <c r="T83">
-        <v>5.01777820095633</v>
+        <v>5.296543656565015</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.07781552237337645</v>
+        <v>0.07686655258833529</v>
       </c>
       <c r="W83">
-        <v>0.2174510998243578</v>
+        <v>0.2176748668996706</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3112620894935059</v>
+        <v>0.3074662103533411</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2356489772658261</v>
+        <v>0.2375489772658261</v>
       </c>
       <c r="C84">
-        <v>-1093.137569738091</v>
+        <v>-1117.098256623497</v>
       </c>
       <c r="D84">
-        <v>453.2024302619096</v>
+        <v>448.7117433765036</v>
       </c>
       <c r="E84">
-        <v>739.8400000000001</v>
+        <v>759.3100000000002</v>
       </c>
       <c r="F84">
-        <v>1596.54</v>
+        <v>1616.01</v>
       </c>
       <c r="G84">
         <v>50.2</v>
@@ -8175,37 +8175,37 @@
         <v>115.75</v>
       </c>
       <c r="M84">
-        <v>376.4641320000001</v>
+        <v>381.0551580000001</v>
       </c>
       <c r="N84">
-        <v>-260.7141320000001</v>
+        <v>-265.3051580000001</v>
       </c>
       <c r="O84">
-        <v>-65.17853300000002</v>
+        <v>-66.32628950000002</v>
       </c>
       <c r="P84">
-        <v>-195.535599</v>
+        <v>-198.9788685</v>
       </c>
       <c r="Q84">
-        <v>-137.535599</v>
+        <v>-140.9788685</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3175310356005348</v>
+        <v>0.3335152141652721</v>
       </c>
       <c r="T84">
-        <v>5.296543656565015</v>
+        <v>5.608105048127662</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.07686655258833529</v>
+        <v>0.07594044954510233</v>
       </c>
       <c r="W84">
-        <v>0.2176748668996706</v>
+        <v>0.2178932419972649</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3074662103533411</v>
+        <v>0.3037617981804093</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2375489772658261</v>
+        <v>0.2394489772658261</v>
       </c>
       <c r="C85">
-        <v>-1117.098256623497</v>
+        <v>-1140.970822154452</v>
       </c>
       <c r="D85">
-        <v>448.7117433765036</v>
+        <v>444.3091778455479</v>
       </c>
       <c r="E85">
-        <v>759.3100000000002</v>
+        <v>778.7800000000002</v>
       </c>
       <c r="F85">
-        <v>1616.01</v>
+        <v>1635.48</v>
       </c>
       <c r="G85">
         <v>50.2</v>
@@ -8257,37 +8257,37 @@
         <v>115.75</v>
       </c>
       <c r="M85">
-        <v>381.0551580000001</v>
+        <v>385.6461840000001</v>
       </c>
       <c r="N85">
-        <v>-265.3051580000001</v>
+        <v>-269.8961840000001</v>
       </c>
       <c r="O85">
-        <v>-66.32628950000002</v>
+        <v>-67.47404600000002</v>
       </c>
       <c r="P85">
-        <v>-198.9788685</v>
+        <v>-202.422138</v>
       </c>
       <c r="Q85">
-        <v>-140.9788685</v>
+        <v>-144.422138</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3335152141652721</v>
+        <v>0.3514974150506017</v>
       </c>
       <c r="T85">
-        <v>5.608105048127662</v>
+        <v>5.958611613635643</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07594044954510233</v>
+        <v>0.0750363965743273</v>
       </c>
       <c r="W85">
-        <v>0.2178932419972649</v>
+        <v>0.2181064176877736</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3037617981804093</v>
+        <v>0.3001455862973093</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2394489772658261</v>
+        <v>0.2413489772658261</v>
       </c>
       <c r="C86">
-        <v>-1140.970822154452</v>
+        <v>-1164.75783495457</v>
       </c>
       <c r="D86">
-        <v>444.3091778455477</v>
+        <v>439.9921650454299</v>
       </c>
       <c r="E86">
-        <v>778.78</v>
+        <v>798.25</v>
       </c>
       <c r="F86">
-        <v>1635.48</v>
+        <v>1654.95</v>
       </c>
       <c r="G86">
         <v>50.2</v>
@@ -8339,37 +8339,37 @@
         <v>115.75</v>
       </c>
       <c r="M86">
-        <v>385.646184</v>
+        <v>390.23721</v>
       </c>
       <c r="N86">
-        <v>-269.896184</v>
+        <v>-274.48721</v>
       </c>
       <c r="O86">
-        <v>-67.474046</v>
+        <v>-68.6218025</v>
       </c>
       <c r="P86">
-        <v>-202.422138</v>
+        <v>-205.8654075</v>
       </c>
       <c r="Q86">
-        <v>-144.422138</v>
+        <v>-147.8654075</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3514974150506016</v>
+        <v>0.3718772427206415</v>
       </c>
       <c r="T86">
-        <v>5.95861161363564</v>
+        <v>6.355852387878014</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07503639657432731</v>
+        <v>0.07415361543815875</v>
       </c>
       <c r="W86">
-        <v>0.2181064176877736</v>
+        <v>0.2183145774796822</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3001455862973093</v>
+        <v>0.2966144617526351</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2413489772658261</v>
+        <v>0.2432489772658261</v>
       </c>
       <c r="C87">
-        <v>-1164.75783495457</v>
+        <v>-1188.461764778683</v>
       </c>
       <c r="D87">
-        <v>439.9921650454299</v>
+        <v>435.7582352213173</v>
       </c>
       <c r="E87">
-        <v>798.25</v>
+        <v>817.72</v>
       </c>
       <c r="F87">
-        <v>1654.95</v>
+        <v>1674.42</v>
       </c>
       <c r="G87">
         <v>50.2</v>
@@ -8421,37 +8421,37 @@
         <v>115.75</v>
       </c>
       <c r="M87">
-        <v>390.23721</v>
+        <v>394.8282360000001</v>
       </c>
       <c r="N87">
-        <v>-274.48721</v>
+        <v>-279.0782360000001</v>
       </c>
       <c r="O87">
-        <v>-68.6218025</v>
+        <v>-69.76955900000002</v>
       </c>
       <c r="P87">
-        <v>-205.8654075</v>
+        <v>-209.308677</v>
       </c>
       <c r="Q87">
-        <v>-147.8654075</v>
+        <v>-151.308677</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3718772427206415</v>
+        <v>0.3951684743435446</v>
       </c>
       <c r="T87">
-        <v>6.355852387878014</v>
+        <v>6.809841844155016</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07415361543815875</v>
+        <v>0.07329136409585457</v>
       </c>
       <c r="W87">
-        <v>0.2183145774796822</v>
+        <v>0.2185178963461975</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2966144617526351</v>
+        <v>0.2931654563834183</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2432489772658261</v>
+        <v>0.2451489772658261</v>
       </c>
       <c r="C88">
-        <v>-1188.461764778683</v>
+        <v>-1212.084987224447</v>
       </c>
       <c r="D88">
-        <v>435.7582352213173</v>
+        <v>431.6050127755533</v>
       </c>
       <c r="E88">
-        <v>817.72</v>
+        <v>837.1900000000001</v>
       </c>
       <c r="F88">
-        <v>1674.42</v>
+        <v>1693.89</v>
       </c>
       <c r="G88">
         <v>50.2</v>
@@ -8503,37 +8503,37 @@
         <v>115.75</v>
       </c>
       <c r="M88">
-        <v>394.8282360000001</v>
+        <v>399.4192620000001</v>
       </c>
       <c r="N88">
-        <v>-279.0782360000001</v>
+        <v>-283.6692620000001</v>
       </c>
       <c r="O88">
-        <v>-69.76955900000002</v>
+        <v>-70.91731550000002</v>
       </c>
       <c r="P88">
-        <v>-209.308677</v>
+        <v>-212.7519465</v>
       </c>
       <c r="Q88">
-        <v>-151.308677</v>
+        <v>-154.7519465</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3951684743435446</v>
+        <v>0.4220429723699711</v>
       </c>
       <c r="T88">
-        <v>6.809841844155016</v>
+        <v>7.33367583216694</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07329136409585457</v>
+        <v>0.07244893462348843</v>
       </c>
       <c r="W88">
-        <v>0.2185178963461975</v>
+        <v>0.2187165412157814</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2931654563834183</v>
+        <v>0.2897957384939537</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2451489772658261</v>
+        <v>0.2470489772658261</v>
       </c>
       <c r="C89">
-        <v>-1212.084987224447</v>
+        <v>-1235.629788177051</v>
       </c>
       <c r="D89">
-        <v>431.6050127755533</v>
+        <v>427.5302118229486</v>
       </c>
       <c r="E89">
-        <v>837.1900000000001</v>
+        <v>856.6599999999999</v>
       </c>
       <c r="F89">
-        <v>1693.89</v>
+        <v>1713.36</v>
       </c>
       <c r="G89">
         <v>50.2</v>
@@ -8585,37 +8585,37 @@
         <v>115.75</v>
       </c>
       <c r="M89">
-        <v>399.4192620000001</v>
+        <v>404.010288</v>
       </c>
       <c r="N89">
-        <v>-283.6692620000001</v>
+        <v>-288.260288</v>
       </c>
       <c r="O89">
-        <v>-70.91731550000002</v>
+        <v>-72.065072</v>
       </c>
       <c r="P89">
-        <v>-212.7519465</v>
+        <v>-216.195216</v>
       </c>
       <c r="Q89">
-        <v>-154.7519465</v>
+        <v>-158.195216</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4220429723699711</v>
+        <v>0.453396553400802</v>
       </c>
       <c r="T89">
-        <v>7.33367583216694</v>
+        <v>7.94481548484752</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07244893462348843</v>
+        <v>0.07162565127549425</v>
       </c>
       <c r="W89">
-        <v>0.2187165412157814</v>
+        <v>0.2189106714292385</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2897957384939537</v>
+        <v>0.286502605101977</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2470489772658261</v>
+        <v>0.2489489772658261</v>
       </c>
       <c r="C90">
-        <v>-1235.629788177051</v>
+        <v>-1259.098368004508</v>
       </c>
       <c r="D90">
-        <v>427.5302118229486</v>
+        <v>423.5316319954919</v>
       </c>
       <c r="E90">
-        <v>856.6599999999999</v>
+        <v>876.1299999999999</v>
       </c>
       <c r="F90">
-        <v>1713.36</v>
+        <v>1732.83</v>
       </c>
       <c r="G90">
         <v>50.2</v>
@@ -8667,37 +8667,37 @@
         <v>115.75</v>
       </c>
       <c r="M90">
-        <v>404.010288</v>
+        <v>408.601314</v>
       </c>
       <c r="N90">
-        <v>-288.260288</v>
+        <v>-292.851314</v>
       </c>
       <c r="O90">
-        <v>-72.065072</v>
+        <v>-73.2128285</v>
       </c>
       <c r="P90">
-        <v>-216.195216</v>
+        <v>-219.6384855</v>
       </c>
       <c r="Q90">
-        <v>-158.195216</v>
+        <v>-161.6384855</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.453396553400802</v>
+        <v>0.4904507855281477</v>
       </c>
       <c r="T90">
-        <v>7.94481548484752</v>
+        <v>8.667071438015476</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07162565127549425</v>
+        <v>0.07082086867689319</v>
       </c>
       <c r="W90">
-        <v>0.2189106714292385</v>
+        <v>0.2191004391659886</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.286502605101977</v>
+        <v>0.2832834747075728</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2489489772658261</v>
+        <v>0.2508489772658261</v>
       </c>
       <c r="C91">
-        <v>-1259.098368004508</v>
+        <v>-1282.492845519693</v>
       </c>
       <c r="D91">
-        <v>423.5316319954919</v>
+        <v>419.6071544803067</v>
       </c>
       <c r="E91">
-        <v>876.1299999999999</v>
+        <v>895.5999999999999</v>
       </c>
       <c r="F91">
-        <v>1732.83</v>
+        <v>1752.3</v>
       </c>
       <c r="G91">
         <v>50.2</v>
@@ -8749,37 +8749,37 @@
         <v>115.75</v>
       </c>
       <c r="M91">
-        <v>408.601314</v>
+        <v>413.19234</v>
       </c>
       <c r="N91">
-        <v>-292.851314</v>
+        <v>-297.44234</v>
       </c>
       <c r="O91">
-        <v>-73.2128285</v>
+        <v>-74.360585</v>
       </c>
       <c r="P91">
-        <v>-219.6384855</v>
+        <v>-223.081755</v>
       </c>
       <c r="Q91">
-        <v>-161.6384855</v>
+        <v>-165.081755</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4904507855281477</v>
+        <v>0.5349158640809625</v>
       </c>
       <c r="T91">
-        <v>8.667071438015476</v>
+        <v>9.533778581817025</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07082086867689319</v>
+        <v>0.07003397013603882</v>
       </c>
       <c r="W91">
-        <v>0.2191004391659886</v>
+        <v>0.219285989841922</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2832834747075728</v>
+        <v>0.2801358805441553</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2508489772658261</v>
+        <v>0.2527489772658261</v>
       </c>
       <c r="C92">
-        <v>-1282.492845519693</v>
+        <v>-1305.81526172414</v>
       </c>
       <c r="D92">
-        <v>419.6071544803067</v>
+        <v>415.7547382758598</v>
       </c>
       <c r="E92">
-        <v>895.5999999999999</v>
+        <v>915.0699999999999</v>
       </c>
       <c r="F92">
-        <v>1752.3</v>
+        <v>1771.77</v>
       </c>
       <c r="G92">
         <v>50.2</v>
@@ -8831,37 +8831,37 @@
         <v>115.75</v>
       </c>
       <c r="M92">
-        <v>413.19234</v>
+        <v>417.783366</v>
       </c>
       <c r="N92">
-        <v>-297.44234</v>
+        <v>-302.033366</v>
       </c>
       <c r="O92">
-        <v>-74.360585</v>
+        <v>-75.5083415</v>
       </c>
       <c r="P92">
-        <v>-223.081755</v>
+        <v>-226.5250245</v>
       </c>
       <c r="Q92">
-        <v>-165.081755</v>
+        <v>-168.5250245</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5349158640809625</v>
+        <v>0.5892620712010695</v>
       </c>
       <c r="T92">
-        <v>9.533778581817025</v>
+        <v>10.59308731313003</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07003397013603882</v>
+        <v>0.06926436606860982</v>
       </c>
       <c r="W92">
-        <v>0.219285989841922</v>
+        <v>0.2194674624810218</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2801358805441553</v>
+        <v>0.2770574642744393</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2527489772658261</v>
+        <v>0.2546489772658261</v>
       </c>
       <c r="C93">
-        <v>-1305.81526172414</v>
+        <v>-1329.067583347476</v>
       </c>
       <c r="D93">
-        <v>415.7547382758598</v>
+        <v>411.9724166525237</v>
       </c>
       <c r="E93">
-        <v>915.0699999999999</v>
+        <v>934.54</v>
       </c>
       <c r="F93">
-        <v>1771.77</v>
+        <v>1791.24</v>
       </c>
       <c r="G93">
         <v>50.2</v>
@@ -8913,37 +8913,37 @@
         <v>115.75</v>
       </c>
       <c r="M93">
-        <v>417.783366</v>
+        <v>422.374392</v>
       </c>
       <c r="N93">
-        <v>-302.033366</v>
+        <v>-306.624392</v>
       </c>
       <c r="O93">
-        <v>-75.5083415</v>
+        <v>-76.656098</v>
       </c>
       <c r="P93">
-        <v>-226.5250245</v>
+        <v>-229.968294</v>
       </c>
       <c r="Q93">
-        <v>-168.5250245</v>
+        <v>-171.968294</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5892620712010695</v>
+        <v>0.6571948301012034</v>
       </c>
       <c r="T93">
-        <v>10.59308731313003</v>
+        <v>11.91722322727129</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.06926436606860982</v>
+        <v>0.06851149252438581</v>
       </c>
       <c r="W93">
-        <v>0.2194674624810218</v>
+        <v>0.2196449900627498</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2770574642744393</v>
+        <v>0.2740459700975433</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2546489772658261</v>
+        <v>0.2565489772658261</v>
       </c>
       <c r="C94">
-        <v>-1329.067583347476</v>
+        <v>-1352.251706195401</v>
       </c>
       <c r="D94">
-        <v>411.9724166525237</v>
+        <v>408.2582938045991</v>
       </c>
       <c r="E94">
-        <v>934.54</v>
+        <v>954.01</v>
       </c>
       <c r="F94">
-        <v>1791.24</v>
+        <v>1810.71</v>
       </c>
       <c r="G94">
         <v>50.2</v>
@@ -8995,37 +8995,37 @@
         <v>115.75</v>
       </c>
       <c r="M94">
-        <v>422.374392</v>
+        <v>426.965418</v>
       </c>
       <c r="N94">
-        <v>-306.624392</v>
+        <v>-311.215418</v>
       </c>
       <c r="O94">
-        <v>-76.656098</v>
+        <v>-77.8038545</v>
       </c>
       <c r="P94">
-        <v>-229.968294</v>
+        <v>-233.4115635</v>
       </c>
       <c r="Q94">
-        <v>-171.968294</v>
+        <v>-175.4115635</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6571948301012034</v>
+        <v>0.7445369486870896</v>
       </c>
       <c r="T94">
-        <v>11.91722322727129</v>
+        <v>13.61968368831004</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.06851149252438581</v>
+        <v>0.06777480980906983</v>
       </c>
       <c r="W94">
-        <v>0.2196449900627498</v>
+        <v>0.2198186998470213</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2740459700975433</v>
+        <v>0.2710992392362793</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2565489772658261</v>
+        <v>0.2584489772658261</v>
       </c>
       <c r="C95">
-        <v>-1352.251706195401</v>
+        <v>-1375.369458318182</v>
       </c>
       <c r="D95">
-        <v>408.2582938045991</v>
+        <v>404.6105416818178</v>
       </c>
       <c r="E95">
-        <v>954.01</v>
+        <v>973.48</v>
       </c>
       <c r="F95">
-        <v>1810.71</v>
+        <v>1830.18</v>
       </c>
       <c r="G95">
         <v>50.2</v>
@@ -9077,37 +9077,37 @@
         <v>115.75</v>
       </c>
       <c r="M95">
-        <v>426.965418</v>
+        <v>431.5564440000001</v>
       </c>
       <c r="N95">
-        <v>-311.215418</v>
+        <v>-315.8064440000001</v>
       </c>
       <c r="O95">
-        <v>-77.8038545</v>
+        <v>-78.95161100000001</v>
       </c>
       <c r="P95">
-        <v>-233.4115635</v>
+        <v>-236.854833</v>
       </c>
       <c r="Q95">
-        <v>-175.4115635</v>
+        <v>-178.854833</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7445369486870896</v>
+        <v>0.8609931068016047</v>
       </c>
       <c r="T95">
-        <v>13.61968368831004</v>
+        <v>15.88963096969505</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.06777480980906983</v>
+        <v>0.06705380119407972</v>
       </c>
       <c r="W95">
-        <v>0.2198186998470213</v>
+        <v>0.219988713678436</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2710992392362793</v>
+        <v>0.2682152047763189</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2584489772658261</v>
+        <v>0.2603489772658261</v>
       </c>
       <c r="C96">
-        <v>-1375.369458318182</v>
+        <v>-1398.422603010795</v>
       </c>
       <c r="D96">
-        <v>404.6105416818178</v>
+        <v>401.0273969892052</v>
       </c>
       <c r="E96">
-        <v>973.48</v>
+        <v>992.95</v>
       </c>
       <c r="F96">
-        <v>1830.18</v>
+        <v>1849.65</v>
       </c>
       <c r="G96">
         <v>50.2</v>
@@ -9159,37 +9159,37 @@
         <v>115.75</v>
       </c>
       <c r="M96">
-        <v>431.5564440000001</v>
+        <v>436.1474700000001</v>
       </c>
       <c r="N96">
-        <v>-315.8064440000001</v>
+        <v>-320.3974700000001</v>
       </c>
       <c r="O96">
-        <v>-78.95161100000001</v>
+        <v>-80.09936750000001</v>
       </c>
       <c r="P96">
-        <v>-236.854833</v>
+        <v>-240.2981025</v>
       </c>
       <c r="Q96">
-        <v>-178.854833</v>
+        <v>-182.2981025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8609931068016047</v>
+        <v>1.024031728161926</v>
       </c>
       <c r="T96">
-        <v>15.88963096969505</v>
+        <v>19.06755716363407</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.06705380119407972</v>
+        <v>0.06634797170782625</v>
       </c>
       <c r="W96">
-        <v>0.219988713678436</v>
+        <v>0.2201551482712946</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2682152047763189</v>
+        <v>0.265391886831305</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2603489772658261</v>
+        <v>0.2622489772658261</v>
       </c>
       <c r="C97">
-        <v>-1398.422603010795</v>
+        <v>-1421.412841655045</v>
       </c>
       <c r="D97">
-        <v>401.0273969892052</v>
+        <v>397.5071583449555</v>
       </c>
       <c r="E97">
-        <v>992.95</v>
+        <v>1012.42</v>
       </c>
       <c r="F97">
-        <v>1849.65</v>
+        <v>1869.12</v>
       </c>
       <c r="G97">
         <v>50.2</v>
@@ -9241,37 +9241,37 @@
         <v>115.75</v>
       </c>
       <c r="M97">
-        <v>436.1474700000001</v>
+        <v>440.7384960000001</v>
       </c>
       <c r="N97">
-        <v>-320.3974700000001</v>
+        <v>-324.9884960000001</v>
       </c>
       <c r="O97">
-        <v>-80.09936750000001</v>
+        <v>-81.24712400000001</v>
       </c>
       <c r="P97">
-        <v>-240.2981025</v>
+        <v>-243.741372</v>
       </c>
       <c r="Q97">
-        <v>-182.2981025</v>
+        <v>-185.741372</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.024031728161926</v>
+        <v>1.268589660202408</v>
       </c>
       <c r="T97">
-        <v>19.06755716363407</v>
+        <v>23.8344464545426</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06634797170782625</v>
+        <v>0.06565684700253639</v>
       </c>
       <c r="W97">
-        <v>0.2201551482712946</v>
+        <v>0.2203181154768019</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.265391886831305</v>
+        <v>0.2626273880101455</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2622489772658261</v>
+        <v>0.2641489772658261</v>
       </c>
       <c r="C98">
-        <v>-1421.412841655044</v>
+        <v>-1444.341816413309</v>
       </c>
       <c r="D98">
-        <v>397.5071583449555</v>
+        <v>394.0481835866909</v>
       </c>
       <c r="E98">
-        <v>1012.42</v>
+        <v>1031.89</v>
       </c>
       <c r="F98">
-        <v>1869.12</v>
+        <v>1888.59</v>
       </c>
       <c r="G98">
         <v>50.2</v>
@@ -9323,37 +9323,37 @@
         <v>115.75</v>
       </c>
       <c r="M98">
-        <v>440.738496</v>
+        <v>445.329522</v>
       </c>
       <c r="N98">
-        <v>-324.988496</v>
+        <v>-329.579522</v>
       </c>
       <c r="O98">
-        <v>-81.247124</v>
+        <v>-82.3948805</v>
       </c>
       <c r="P98">
-        <v>-243.741372</v>
+        <v>-247.1846415</v>
       </c>
       <c r="Q98">
-        <v>-185.741372</v>
+        <v>-189.1846415</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.268589660202405</v>
+        <v>1.676186213603207</v>
       </c>
       <c r="T98">
-        <v>23.83444645454254</v>
+        <v>31.77926193939005</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06565684700253639</v>
+        <v>0.06497997229117004</v>
       </c>
       <c r="W98">
-        <v>0.2203181154768019</v>
+        <v>0.2204777225337421</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2626273880101456</v>
+        <v>0.2599198891646801</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2641489772658261</v>
+        <v>0.2660489772658261</v>
       </c>
       <c r="C99">
-        <v>-1444.341816413309</v>
+        <v>-1467.21111278285</v>
       </c>
       <c r="D99">
-        <v>394.0481835866909</v>
+        <v>390.6488872171503</v>
       </c>
       <c r="E99">
-        <v>1031.89</v>
+        <v>1051.36</v>
       </c>
       <c r="F99">
-        <v>1888.59</v>
+        <v>1908.06</v>
       </c>
       <c r="G99">
         <v>50.2</v>
@@ -9405,37 +9405,37 @@
         <v>115.75</v>
       </c>
       <c r="M99">
-        <v>445.329522</v>
+        <v>449.920548</v>
       </c>
       <c r="N99">
-        <v>-329.579522</v>
+        <v>-334.170548</v>
       </c>
       <c r="O99">
-        <v>-82.3948805</v>
+        <v>-83.542637</v>
       </c>
       <c r="P99">
-        <v>-247.1846415</v>
+        <v>-250.627911</v>
       </c>
       <c r="Q99">
-        <v>-189.1846415</v>
+        <v>-192.627911</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.676186213603207</v>
+        <v>2.49137932040481</v>
       </c>
       <c r="T99">
-        <v>31.77926193939005</v>
+        <v>47.66889290908507</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06497997229117004</v>
+        <v>0.06431691134942341</v>
       </c>
       <c r="W99">
-        <v>0.2204777225337421</v>
+        <v>0.220634072303806</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2599198891646801</v>
+        <v>0.2572676453976936</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2660489772658261</v>
+        <v>0.2679489772658261</v>
       </c>
       <c r="C100">
-        <v>-1467.21111278285</v>
+        <v>-1490.022262019042</v>
       </c>
       <c r="D100">
-        <v>390.6488872171503</v>
+        <v>387.3077379809582</v>
       </c>
       <c r="E100">
-        <v>1051.36</v>
+        <v>1070.83</v>
       </c>
       <c r="F100">
-        <v>1908.06</v>
+        <v>1927.53</v>
       </c>
       <c r="G100">
         <v>50.2</v>
@@ -9487,37 +9487,37 @@
         <v>115.75</v>
       </c>
       <c r="M100">
-        <v>449.920548</v>
+        <v>454.511574</v>
       </c>
       <c r="N100">
-        <v>-334.170548</v>
+        <v>-338.761574</v>
       </c>
       <c r="O100">
-        <v>-83.542637</v>
+        <v>-84.6903935</v>
       </c>
       <c r="P100">
-        <v>-250.627911</v>
+        <v>-254.0711805</v>
       </c>
       <c r="Q100">
-        <v>-192.627911</v>
+        <v>-196.0711805</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.49137932040481</v>
+        <v>4.93695864080962</v>
       </c>
       <c r="T100">
-        <v>47.66889290908507</v>
+        <v>95.33778581817015</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06431691134942341</v>
+        <v>0.06366724557821711</v>
       </c>
       <c r="W100">
-        <v>0.220634072303806</v>
+        <v>0.2207872634926564</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2572676453976936</v>
+        <v>0.2546689823128685</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2679489772658261</v>
-      </c>
-      <c r="C101">
-        <v>-1490.022262019042</v>
-      </c>
-      <c r="D101">
-        <v>387.3077379809582</v>
-      </c>
-      <c r="E101">
-        <v>1070.83</v>
-      </c>
-      <c r="F101">
-        <v>1927.53</v>
-      </c>
-      <c r="G101">
-        <v>50.2</v>
-      </c>
-      <c r="H101">
-        <v>1090.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>173.75</v>
-      </c>
-      <c r="K101">
-        <v>58</v>
-      </c>
-      <c r="L101">
-        <v>115.75</v>
-      </c>
-      <c r="M101">
-        <v>454.511574</v>
-      </c>
-      <c r="N101">
-        <v>-338.761574</v>
-      </c>
-      <c r="O101">
-        <v>-84.6903935</v>
-      </c>
-      <c r="P101">
-        <v>-254.0711805</v>
-      </c>
-      <c r="Q101">
-        <v>-196.0711805</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.93695864080962</v>
-      </c>
-      <c r="T101">
-        <v>95.33778581817015</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06366724557821711</v>
-      </c>
-      <c r="W101">
-        <v>0.2207872634926564</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2546689823128685</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
